--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="담당자별 현황" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유형별 현황" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용 안내" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="담당자별 요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유형별 현황" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용 안내" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'상세'!$A$1:$R$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상세'!$A$1:$R$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -83,6 +84,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1190,6 +1197,1023 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>담당자별 요약 — 요청 내용·진행 상태·다음 조치</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>건수·상태·다음 조치는 '상세' 시트 입력에 따라 자동 갱신됩니다. SQ NO 목록은 요청 시점(2026-10-08) 기준입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>발송 메시지</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>판단 보류</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>미비</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>보완 필요</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>보유 확인</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>총 건수</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>미발송</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>미회신(회신 완료 제외)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>회신 완료</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>지연</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>최근 발송일</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>가장 이른 미회신 기한</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>다음 조치</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>판단 보류 SQ NO</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>미비 SQ NO</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>보유 확인 SQ NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>지성규</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>메시지_지성규.txt</t>
+        </is>
+      </c>
+      <c r="C5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L5" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A5,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A5))</f>
+        <v/>
+      </c>
+      <c r="M5" s="8">
+        <f>IF(I5=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N5" s="7">
+        <f>IF(G5=J5,"회신 완료 — 조치 완료 여부 확인",IF(K5&gt;0,"지연 — 재촉 필요",IF(H5=G5,"발송 필요",IF(H5&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>7, 45, 71, 123, 126, 133, 135, 170, 197, 230</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>22, 113</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>4, 115, 140</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>이광재</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>메시지_이광재.txt</t>
+        </is>
+      </c>
+      <c r="C6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L6" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A6,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A6))</f>
+        <v/>
+      </c>
+      <c r="M6" s="8">
+        <f>IF(I6=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N6" s="7">
+        <f>IF(G6=J6,"회신 완료 — 조치 완료 여부 확인",IF(K6&gt;0,"지연 — 재촉 필요",IF(H6=G6,"발송 필요",IF(H6&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>14, 15, 41, 185</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>47, 48, 65, 66, 67, 69, 70, 190</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>김명용</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>메시지_김명용.txt</t>
+        </is>
+      </c>
+      <c r="C7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L7" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A7,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A7))</f>
+        <v/>
+      </c>
+      <c r="M7" s="8">
+        <f>IF(I7=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N7" s="7">
+        <f>IF(G7=J7,"회신 완료 — 조치 완료 여부 확인",IF(K7&gt;0,"지연 — 재촉 필요",IF(H7=G7,"발송 필요",IF(H7&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>51, 75, 76, 77, 224</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>이은주</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>메시지_이은주.txt</t>
+        </is>
+      </c>
+      <c r="C8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L8" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A8,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A8))</f>
+        <v/>
+      </c>
+      <c r="M8" s="8">
+        <f>IF(I8=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N8" s="7">
+        <f>IF(G8=J8,"회신 완료 — 조치 완료 여부 확인",IF(K8&gt;0,"지연 — 재촉 필요",IF(H8=G8,"발송 필요",IF(H8&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>142, 143, 145, 155</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>황지환</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>메시지_황지환.txt</t>
+        </is>
+      </c>
+      <c r="C9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L9" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A9,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A9))</f>
+        <v/>
+      </c>
+      <c r="M9" s="8">
+        <f>IF(I9=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N9" s="7">
+        <f>IF(G9=J9,"회신 완료 — 조치 완료 여부 확인",IF(K9&gt;0,"지연 — 재촉 필요",IF(H9=G9,"발송 필요",IF(H9&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>25, 26, 106, 107, 108</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>한상돈</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>메시지_한상돈.txt</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L10" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A10,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A10))</f>
+        <v/>
+      </c>
+      <c r="M10" s="8">
+        <f>IF(I10=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N10" s="7">
+        <f>IF(G10=J10,"회신 완료 — 조치 완료 여부 확인",IF(K10&gt;0,"지연 — 재촉 필요",IF(H10=G10,"발송 필요",IF(H10&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>83, 84, 88</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>김주태</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>메시지_김주태.txt</t>
+        </is>
+      </c>
+      <c r="C11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L11" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A11,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A11))</f>
+        <v/>
+      </c>
+      <c r="M11" s="8">
+        <f>IF(I11=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N11" s="7">
+        <f>IF(G11=J11,"회신 완료 — 조치 완료 여부 확인",IF(K11&gt;0,"지연 — 재촉 필요",IF(H11=G11,"발송 필요",IF(H11&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>박철호</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>메시지_박철호.txt</t>
+        </is>
+      </c>
+      <c r="C12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L12" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A12,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A12))</f>
+        <v/>
+      </c>
+      <c r="M12" s="8">
+        <f>IF(I12=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N12" s="7">
+        <f>IF(G12=J12,"회신 완료 — 조치 완료 여부 확인",IF(K12&gt;0,"지연 — 재촉 필요",IF(H12=G12,"발송 필요",IF(H12&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>김운주</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>메시지_김운주.txt</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L13" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A13,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A13))</f>
+        <v/>
+      </c>
+      <c r="M13" s="8">
+        <f>IF(I13=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N13" s="7">
+        <f>IF(G13=J13,"회신 완료 — 조치 완료 여부 확인",IF(K13&gt;0,"지연 — 재촉 필요",IF(H13=G13,"발송 필요",IF(H13&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>100, 101</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>안종명</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>메시지_안종명.txt</t>
+        </is>
+      </c>
+      <c r="C14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L14" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A14,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A14))</f>
+        <v/>
+      </c>
+      <c r="M14" s="8">
+        <f>IF(I14=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N14" s="7">
+        <f>IF(G14=J14,"회신 완료 — 조치 완료 여부 확인",IF(K14&gt;0,"지연 — 재촉 필요",IF(H14=G14,"발송 필요",IF(H14&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>이은주·박철호(공동)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>메시지_이은주_박철호공동.txt</t>
+        </is>
+      </c>
+      <c r="C15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="D15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="E15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="F15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="G15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="J15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="K15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="L15" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A15,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A15))</f>
+        <v/>
+      </c>
+      <c r="M15" s="8">
+        <f>IF(I15=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="N15" s="7">
+        <f>IF(G15=J15,"회신 완료 — 조치 완료 여부 확인",IF(K15&gt;0,"지연 — 재촉 필요",IF(H15=G15,"발송 필요",IF(H15&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr"/>
+      <c r="C16" s="9">
+        <f>SUM(C5:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="9">
+        <f>SUM(D5:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="9">
+        <f>SUM(E5:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="9">
+        <f>SUM(F5:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="9">
+        <f>SUM(G5:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>SUM(H5:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="9">
+        <f>SUM(I5:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="9">
+        <f>SUM(J5:J15)</f>
+        <v/>
+      </c>
+      <c r="K16" s="9">
+        <f>SUM(K5:K15)</f>
+        <v/>
+      </c>
+      <c r="L16" s="10" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr"/>
+      <c r="N16" s="9" t="inlineStr"/>
+      <c r="O16" s="9" t="inlineStr"/>
+      <c r="P16" s="9" t="inlineStr"/>
+      <c r="Q16" s="9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A5:Q15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$K5&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>AND($G5&gt;0,$G5=$J5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1458,7 +2482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17924,7 +18948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17943,9 +18967,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -17967,9 +18988,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -18004,9 +19022,6 @@
           <t>4. 기한 2026-10-15 가 지났는데 회신 완료가 아닌 건은 행이 붉게 표시되고 '담당자별 현황'의 지연에 집계됩니다.</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -8,13 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="담당자별 현황" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="담당자별 요약" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유형별 현황" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용 안내" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유형별 현황" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용 안내" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상세'!$A$1:$R$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'상세'!$A$1:$R$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -70,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -90,6 +89,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -473,21 +478,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>'상세' 시트의 발송일·회신 상태를 입력하면 자동 집계됩니다. 지연 = 발송했으나 회신 완료가 아니고 기한이 지난 건(오늘 기준).</t>
+          <t>'상세' 시트의 발송일·회신 상태를 입력하면 자동 집계됩니다. 지연 = 발송했으나 회신 완료가 아니고 기한이 지난 건(오늘 기준). SQ NO 목록은 요청 시점(2026-10-08) 기준이며, 보완 필요 건은 건수가 많아 '상세' 시트에서 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -512,811 +528,112 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>발송 메시지</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>총 건수</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>(그중) 보유 확인</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>판단 보류</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>미비</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>보완 필요</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>보유 확인</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>미발송</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>발송(회신 대기)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>일부 회신</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>재요청</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>회신 완료</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>회신율</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>미회신(회신 완료 제외)</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>지연</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>조치 완료</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>최근 발송일</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>가장 이른 미회신 기한</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>다음 조치</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>판단 보류 SQ NO</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>미비 SQ NO</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>보유 확인 SQ NO</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>한 통 묶음 여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>지성규</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>COUNTIFS(상세!$H:$H,$A5)</f>
-        <v/>
-      </c>
-      <c r="C5">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E5">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I5" s="3">
-        <f>IF(B5=0,0,H5/B5)</f>
-        <v/>
-      </c>
-      <c r="J5">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K5">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>보유 확인 합쳐 한 통</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>이광재</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>COUNTIFS(상세!$H:$H,$A6)</f>
-        <v/>
-      </c>
-      <c r="C6">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I6" s="3">
-        <f>IF(B6=0,0,H6/B6)</f>
-        <v/>
-      </c>
-      <c r="J6">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K6">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>보유 확인 합쳐 한 통</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>김명용</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>COUNTIFS(상세!$H:$H,$A7)</f>
-        <v/>
-      </c>
-      <c r="C7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I7" s="3">
-        <f>IF(B7=0,0,H7/B7)</f>
-        <v/>
-      </c>
-      <c r="J7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>요청만</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>이은주</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>COUNTIFS(상세!$H:$H,$A8)</f>
-        <v/>
-      </c>
-      <c r="C8">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I8" s="3">
-        <f>IF(B8=0,0,H8/B8)</f>
-        <v/>
-      </c>
-      <c r="J8">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K8">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>보유 확인 합쳐 한 통</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>황지환</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>COUNTIFS(상세!$H:$H,$A9)</f>
-        <v/>
-      </c>
-      <c r="C9">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F9">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I9" s="3">
-        <f>IF(B9=0,0,H9/B9)</f>
-        <v/>
-      </c>
-      <c r="J9">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K9">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>요청만</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>한상돈</t>
-        </is>
-      </c>
-      <c r="B10">
-        <f>COUNTIFS(상세!$H:$H,$A10)</f>
-        <v/>
-      </c>
-      <c r="C10">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I10" s="3">
-        <f>IF(B10=0,0,H10/B10)</f>
-        <v/>
-      </c>
-      <c r="J10">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K10">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>요청만</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>김주태</t>
-        </is>
-      </c>
-      <c r="B11">
-        <f>COUNTIFS(상세!$H:$H,$A11)</f>
-        <v/>
-      </c>
-      <c r="C11">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I11" s="3">
-        <f>IF(B11=0,0,H11/B11)</f>
-        <v/>
-      </c>
-      <c r="J11">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K11">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>요청만</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>박철호</t>
-        </is>
-      </c>
-      <c r="B12">
-        <f>COUNTIFS(상세!$H:$H,$A12)</f>
-        <v/>
-      </c>
-      <c r="C12">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I12" s="3">
-        <f>IF(B12=0,0,H12/B12)</f>
-        <v/>
-      </c>
-      <c r="J12">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K12">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>요청만</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>김운주</t>
-        </is>
-      </c>
-      <c r="B13">
-        <f>COUNTIFS(상세!$H:$H,$A13)</f>
-        <v/>
-      </c>
-      <c r="C13">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I13" s="3">
-        <f>IF(B13=0,0,H13/B13)</f>
-        <v/>
-      </c>
-      <c r="J13">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K13">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>요청만</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>안종명</t>
-        </is>
-      </c>
-      <c r="B14">
-        <f>COUNTIFS(상세!$H:$H,$A14)</f>
-        <v/>
-      </c>
-      <c r="C14">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I14" s="3">
-        <f>IF(B14=0,0,H14/B14)</f>
-        <v/>
-      </c>
-      <c r="J14">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K14">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>요청만</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>이은주·박철호(공동)</t>
-        </is>
-      </c>
-      <c r="B15">
-        <f>COUNTIFS(상세!$H:$H,$A15)</f>
-        <v/>
-      </c>
-      <c r="C15">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"미발송")</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"발송(회신 대기)")</f>
-        <v/>
-      </c>
-      <c r="F15">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"일부 회신")</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"재요청")</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="I15" s="3">
-        <f>IF(B15=0,0,H15/B15)</f>
-        <v/>
-      </c>
-      <c r="J15">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-      <c r="K15">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$Q:$Q,"완료")</f>
-        <v/>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>요청만</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B16" s="4">
-        <f>SUM(B5:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="4">
-        <f>SUM(C5:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="4">
-        <f>SUM(D5:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="4">
-        <f>SUM(E5:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="4">
-        <f>SUM(F5:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="4">
-        <f>SUM(G5:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="4">
-        <f>SUM(H5:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="5">
-        <f>IF(B16=0,0,H16/B16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="4">
-        <f>SUM(J5:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="4">
-        <f>SUM(K5:K15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>담당자별 요약 — 요청 내용·진행 상태·다음 조치</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>건수·상태·다음 조치는 '상세' 시트 입력에 따라 자동 갱신됩니다. SQ NO 목록은 요청 시점(2026-10-08) 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>담당자</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>발송 메시지</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>판단 보류</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>미비</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>보완 필요</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>보유 확인</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>총 건수</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>미발송</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>미회신(회신 완료 제외)</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>회신 완료</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>지연</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>최근 발송일</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>가장 이른 미회신 기한</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>다음 조치</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>판단 보류 SQ NO</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>미비 SQ NO</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>보유 확인 SQ NO</t>
         </is>
       </c>
     </row>
@@ -1332,23 +649,23 @@
         </is>
       </c>
       <c r="C5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="7">
         <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D5" s="7">
+      <c r="E5" s="7">
         <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E5" s="7">
+      <c r="F5" s="7">
         <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F5" s="7">
+      <c r="G5" s="7">
         <f>COUNTIFS(상세!$H:$H,$A5,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G5" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A5)</f>
         <v/>
       </c>
       <c r="H5" s="7">
@@ -1356,42 +673,67 @@
         <v/>
       </c>
       <c r="I5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M5" s="11">
+        <f>IF(C5=0,0,L5/C5)</f>
+        <v/>
+      </c>
+      <c r="N5" s="7">
         <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J5" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K5" s="7">
+      <c r="O5" s="7">
         <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L5" s="8">
+      <c r="P5" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A5,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A5))</f>
         <v/>
       </c>
-      <c r="M5" s="8">
-        <f>IF(I5=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N5" s="7">
-        <f>IF(G5=J5,"회신 완료 — 조치 완료 여부 확인",IF(K5&gt;0,"지연 — 재촉 필요",IF(H5=G5,"발송 필요",IF(H5&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="R5" s="8">
+        <f>IF(N5=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S5" s="7">
+        <f>IF(C5=L5,"회신 완료 — 조치 완료 여부 확인",IF(O5&gt;0,"지연 — 재촉 필요",IF(H5=C5,"발송 필요",IF(H5&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
         <is>
           <t>7, 45, 71, 123, 126, 133, 135, 170, 197, 230</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>22, 113</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="V5" s="7" t="inlineStr">
         <is>
           <t>4, 115, 140</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>보유 확인 합쳐 한 통</t>
         </is>
       </c>
     </row>
@@ -1407,23 +749,23 @@
         </is>
       </c>
       <c r="C6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="7">
         <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="E6" s="7">
         <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="F6" s="7">
         <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="G6" s="7">
         <f>COUNTIFS(상세!$H:$H,$A6,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G6" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A6)</f>
         <v/>
       </c>
       <c r="H6" s="7">
@@ -1431,42 +773,67 @@
         <v/>
       </c>
       <c r="I6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M6" s="11">
+        <f>IF(C6=0,0,L6/C6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="7">
         <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J6" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K6" s="7">
+      <c r="O6" s="7">
         <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="P6" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A6,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A6))</f>
         <v/>
       </c>
-      <c r="M6" s="8">
-        <f>IF(I6=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N6" s="7">
-        <f>IF(G6=J6,"회신 완료 — 조치 완료 여부 확인",IF(K6&gt;0,"지연 — 재촉 필요",IF(H6=G6,"발송 필요",IF(H6&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="R6" s="8">
+        <f>IF(N6=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S6" s="7">
+        <f>IF(C6=L6,"회신 완료 — 조치 완료 여부 확인",IF(O6&gt;0,"지연 — 재촉 필요",IF(H6=C6,"발송 필요",IF(H6&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
         <is>
           <t>14, 15, 41, 185</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>47, 48, 65, 66, 67, 69, 70, 190</t>
         </is>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="V6" s="7" t="inlineStr">
         <is>
           <t>19</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>보유 확인 합쳐 한 통</t>
         </is>
       </c>
     </row>
@@ -1482,23 +849,23 @@
         </is>
       </c>
       <c r="C7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
         <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="E7" s="7">
         <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="F7" s="7">
         <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="G7" s="7">
         <f>COUNTIFS(상세!$H:$H,$A7,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G7" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A7)</f>
         <v/>
       </c>
       <c r="H7" s="7">
@@ -1506,42 +873,67 @@
         <v/>
       </c>
       <c r="I7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M7" s="11">
+        <f>IF(C7=0,0,L7/C7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="7">
         <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J7" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K7" s="7">
+      <c r="O7" s="7">
         <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L7" s="8">
+      <c r="P7" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A7,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A7))</f>
         <v/>
       </c>
-      <c r="M7" s="8">
-        <f>IF(I7=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N7" s="7">
-        <f>IF(G7=J7,"회신 완료 — 조치 완료 여부 확인",IF(K7&gt;0,"지연 — 재촉 필요",IF(H7=G7,"발송 필요",IF(H7&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="R7" s="8">
+        <f>IF(N7=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S7" s="7">
+        <f>IF(C7=L7,"회신 완료 — 조치 완료 여부 확인",IF(O7&gt;0,"지연 — 재촉 필요",IF(H7=C7,"발송 필요",IF(H7&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
         <is>
           <t>51, 75, 76, 77, 224</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="U7" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="V7" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>요청만</t>
         </is>
       </c>
     </row>
@@ -1557,23 +949,23 @@
         </is>
       </c>
       <c r="C8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="7">
         <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="E8" s="7">
         <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="F8" s="7">
         <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="G8" s="7">
         <f>COUNTIFS(상세!$H:$H,$A8,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G8" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A8)</f>
         <v/>
       </c>
       <c r="H8" s="7">
@@ -1581,42 +973,67 @@
         <v/>
       </c>
       <c r="I8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M8" s="11">
+        <f>IF(C8=0,0,L8/C8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="7">
         <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J8" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K8" s="7">
+      <c r="O8" s="7">
         <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L8" s="8">
+      <c r="P8" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A8,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A8))</f>
         <v/>
       </c>
-      <c r="M8" s="8">
-        <f>IF(I8=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N8" s="7">
-        <f>IF(G8=J8,"회신 완료 — 조치 완료 여부 확인",IF(K8&gt;0,"지연 — 재촉 필요",IF(H8=G8,"발송 필요",IF(H8&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="R8" s="8">
+        <f>IF(N8=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S8" s="7">
+        <f>IF(C8=L8,"회신 완료 — 조치 완료 여부 확인",IF(O8&gt;0,"지연 — 재촉 필요",IF(H8=C8,"발송 필요",IF(H8&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
         <is>
           <t>142, 143, 145, 155</t>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="U8" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="V8" s="7" t="inlineStr">
         <is>
           <t>147</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>보유 확인 합쳐 한 통</t>
         </is>
       </c>
     </row>
@@ -1632,23 +1049,23 @@
         </is>
       </c>
       <c r="C9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
         <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="E9" s="7">
         <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="F9" s="7">
         <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F9" s="7">
+      <c r="G9" s="7">
         <f>COUNTIFS(상세!$H:$H,$A9,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G9" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A9)</f>
         <v/>
       </c>
       <c r="H9" s="7">
@@ -1656,42 +1073,67 @@
         <v/>
       </c>
       <c r="I9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M9" s="11">
+        <f>IF(C9=0,0,L9/C9)</f>
+        <v/>
+      </c>
+      <c r="N9" s="7">
         <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J9" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K9" s="7">
+      <c r="O9" s="7">
         <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L9" s="8">
+      <c r="P9" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q9" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A9,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A9))</f>
         <v/>
       </c>
-      <c r="M9" s="8">
-        <f>IF(I9=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N9" s="7">
-        <f>IF(G9=J9,"회신 완료 — 조치 완료 여부 확인",IF(K9&gt;0,"지연 — 재촉 필요",IF(H9=G9,"발송 필요",IF(H9&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="R9" s="8">
+        <f>IF(N9=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S9" s="7">
+        <f>IF(C9=L9,"회신 완료 — 조치 완료 여부 확인",IF(O9&gt;0,"지연 — 재촉 필요",IF(H9=C9,"발송 필요",IF(H9&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="U9" s="7" t="inlineStr">
         <is>
           <t>25, 26, 106, 107, 108</t>
         </is>
       </c>
-      <c r="Q9" s="7" t="inlineStr">
+      <c r="V9" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>요청만</t>
         </is>
       </c>
     </row>
@@ -1707,23 +1149,23 @@
         </is>
       </c>
       <c r="C10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
         <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D10" s="7">
+      <c r="E10" s="7">
         <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="F10" s="7">
         <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="G10" s="7">
         <f>COUNTIFS(상세!$H:$H,$A10,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G10" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A10)</f>
         <v/>
       </c>
       <c r="H10" s="7">
@@ -1731,42 +1173,67 @@
         <v/>
       </c>
       <c r="I10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M10" s="11">
+        <f>IF(C10=0,0,L10/C10)</f>
+        <v/>
+      </c>
+      <c r="N10" s="7">
         <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J10" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K10" s="7">
+      <c r="O10" s="7">
         <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L10" s="8">
+      <c r="P10" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A10,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A10))</f>
         <v/>
       </c>
-      <c r="M10" s="8">
-        <f>IF(I10=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N10" s="7">
-        <f>IF(G10=J10,"회신 완료 — 조치 완료 여부 확인",IF(K10&gt;0,"지연 — 재촉 필요",IF(H10=G10,"발송 필요",IF(H10&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="R10" s="8">
+        <f>IF(N10=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S10" s="7">
+        <f>IF(C10=L10,"회신 완료 — 조치 완료 여부 확인",IF(O10&gt;0,"지연 — 재촉 필요",IF(H10=C10,"발송 필요",IF(H10&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
         <is>
           <t>83, 84, 88</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="U10" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="V10" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>요청만</t>
         </is>
       </c>
     </row>
@@ -1782,23 +1249,23 @@
         </is>
       </c>
       <c r="C11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
         <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="E11" s="7">
         <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="F11" s="7">
         <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="G11" s="7">
         <f>COUNTIFS(상세!$H:$H,$A11,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G11" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A11)</f>
         <v/>
       </c>
       <c r="H11" s="7">
@@ -1806,42 +1273,67 @@
         <v/>
       </c>
       <c r="I11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M11" s="11">
+        <f>IF(C11=0,0,L11/C11)</f>
+        <v/>
+      </c>
+      <c r="N11" s="7">
         <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J11" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K11" s="7">
+      <c r="O11" s="7">
         <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L11" s="8">
+      <c r="P11" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A11,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A11))</f>
         <v/>
       </c>
-      <c r="M11" s="8">
-        <f>IF(I11=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N11" s="7">
-        <f>IF(G11=J11,"회신 완료 — 조치 완료 여부 확인",IF(K11&gt;0,"지연 — 재촉 필요",IF(H11=G11,"발송 필요",IF(H11&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="R11" s="8">
+        <f>IF(N11=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S11" s="7">
+        <f>IF(C11=L11,"회신 완료 — 조치 완료 여부 확인",IF(O11&gt;0,"지연 — 재촉 필요",IF(H11=C11,"발송 필요",IF(H11&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="7" t="inlineStr">
+      <c r="U11" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q11" s="7" t="inlineStr">
+      <c r="V11" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
+        <is>
+          <t>요청만</t>
         </is>
       </c>
     </row>
@@ -1857,23 +1349,23 @@
         </is>
       </c>
       <c r="C12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
         <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="E12" s="7">
         <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="F12" s="7">
         <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F12" s="7">
+      <c r="G12" s="7">
         <f>COUNTIFS(상세!$H:$H,$A12,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G12" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A12)</f>
         <v/>
       </c>
       <c r="H12" s="7">
@@ -1881,42 +1373,67 @@
         <v/>
       </c>
       <c r="I12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M12" s="11">
+        <f>IF(C12=0,0,L12/C12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="7">
         <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J12" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K12" s="7">
+      <c r="O12" s="7">
         <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L12" s="8">
+      <c r="P12" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A12,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A12))</f>
         <v/>
       </c>
-      <c r="M12" s="8">
-        <f>IF(I12=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N12" s="7">
-        <f>IF(G12=J12,"회신 완료 — 조치 완료 여부 확인",IF(K12&gt;0,"지연 — 재촉 필요",IF(H12=G12,"발송 필요",IF(H12&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="R12" s="8">
+        <f>IF(N12=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S12" s="7">
+        <f>IF(C12=L12,"회신 완료 — 조치 완료 여부 확인",IF(O12&gt;0,"지연 — 재촉 필요",IF(H12=C12,"발송 필요",IF(H12&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="V12" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>요청만</t>
         </is>
       </c>
     </row>
@@ -1932,23 +1449,23 @@
         </is>
       </c>
       <c r="C13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
         <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D13" s="7">
+      <c r="E13" s="7">
         <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E13" s="7">
+      <c r="F13" s="7">
         <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F13" s="7">
+      <c r="G13" s="7">
         <f>COUNTIFS(상세!$H:$H,$A13,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G13" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A13)</f>
         <v/>
       </c>
       <c r="H13" s="7">
@@ -1956,42 +1473,67 @@
         <v/>
       </c>
       <c r="I13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M13" s="11">
+        <f>IF(C13=0,0,L13/C13)</f>
+        <v/>
+      </c>
+      <c r="N13" s="7">
         <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J13" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K13" s="7">
+      <c r="O13" s="7">
         <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L13" s="8">
+      <c r="P13" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A13,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A13))</f>
         <v/>
       </c>
-      <c r="M13" s="8">
-        <f>IF(I13=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N13" s="7">
-        <f>IF(G13=J13,"회신 완료 — 조치 완료 여부 확인",IF(K13&gt;0,"지연 — 재촉 필요",IF(H13=G13,"발송 필요",IF(H13&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="R13" s="8">
+        <f>IF(N13=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S13" s="7">
+        <f>IF(C13=L13,"회신 완료 — 조치 완료 여부 확인",IF(O13&gt;0,"지연 — 재촉 필요",IF(H13=C13,"발송 필요",IF(H13&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="U13" s="7" t="inlineStr">
         <is>
           <t>100, 101</t>
         </is>
       </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="V13" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>요청만</t>
         </is>
       </c>
     </row>
@@ -2007,23 +1549,23 @@
         </is>
       </c>
       <c r="C14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="7">
         <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D14" s="7">
+      <c r="E14" s="7">
         <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E14" s="7">
+      <c r="F14" s="7">
         <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F14" s="7">
+      <c r="G14" s="7">
         <f>COUNTIFS(상세!$H:$H,$A14,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G14" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A14)</f>
         <v/>
       </c>
       <c r="H14" s="7">
@@ -2031,42 +1573,67 @@
         <v/>
       </c>
       <c r="I14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M14" s="11">
+        <f>IF(C14=0,0,L14/C14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="7">
         <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J14" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K14" s="7">
+      <c r="O14" s="7">
         <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="P14" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A14,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A14))</f>
         <v/>
       </c>
-      <c r="M14" s="8">
-        <f>IF(I14=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N14" s="7">
-        <f>IF(G14=J14,"회신 완료 — 조치 완료 여부 확인",IF(K14&gt;0,"지연 — 재촉 필요",IF(H14=G14,"발송 필요",IF(H14&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="R14" s="8">
+        <f>IF(N14=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S14" s="7">
+        <f>IF(C14=L14,"회신 완료 — 조치 완료 여부 확인",IF(O14&gt;0,"지연 — 재촉 필요",IF(H14=C14,"발송 필요",IF(H14&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
         <is>
           <t>233</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="V14" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>요청만</t>
         </is>
       </c>
     </row>
@@ -2082,23 +1649,23 @@
         </is>
       </c>
       <c r="C15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="7">
         <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"판단 보류")</f>
         <v/>
       </c>
-      <c r="D15" s="7">
+      <c r="E15" s="7">
         <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"미비")</f>
         <v/>
       </c>
-      <c r="E15" s="7">
+      <c r="F15" s="7">
         <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"보완 필요")</f>
         <v/>
       </c>
-      <c r="F15" s="7">
+      <c r="G15" s="7">
         <f>COUNTIFS(상세!$H:$H,$A15,상세!$E:$E,"보유 확인")</f>
-        <v/>
-      </c>
-      <c r="G15" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A15)</f>
         <v/>
       </c>
       <c r="H15" s="7">
@@ -2106,42 +1673,67 @@
         <v/>
       </c>
       <c r="I15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M15" s="11">
+        <f>IF(C15=0,0,L15/C15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="7">
         <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료")</f>
         <v/>
       </c>
-      <c r="J15" s="7">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"회신 완료")</f>
-        <v/>
-      </c>
-      <c r="K15" s="7">
+      <c r="O15" s="7">
         <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="P15" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="8">
         <f>IF(COUNTIFS(상세!$H:$H,$A15,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A15))</f>
         <v/>
       </c>
-      <c r="M15" s="8">
-        <f>IF(I15=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
-        <v/>
-      </c>
-      <c r="N15" s="7">
-        <f>IF(G15=J15,"회신 완료 — 조치 완료 여부 확인",IF(K15&gt;0,"지연 — 재촉 필요",IF(H15=G15,"발송 필요",IF(H15&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
-        <v/>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="R15" s="8">
+        <f>IF(N15=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S15" s="7">
+        <f>IF(C15=L15,"회신 완료 — 조치 완료 여부 확인",IF(O15&gt;0,"지연 — 재촉 필요",IF(H15=C15,"발송 필요",IF(H15&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T15" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="U15" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="V15" s="7" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>요청만</t>
         </is>
       </c>
     </row>
@@ -2188,27 +1780,48 @@
         <f>SUM(K5:K15)</f>
         <v/>
       </c>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" s="9" t="inlineStr"/>
-      <c r="O16" s="9" t="inlineStr"/>
-      <c r="P16" s="9" t="inlineStr"/>
-      <c r="Q16" s="9" t="inlineStr"/>
+      <c r="L16" s="9">
+        <f>SUM(L5:L15)</f>
+        <v/>
+      </c>
+      <c r="M16" s="12">
+        <f>IF(C16=0,0,L16/C16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="9">
+        <f>SUM(N5:N15)</f>
+        <v/>
+      </c>
+      <c r="O16" s="9">
+        <f>SUM(O5:O15)</f>
+        <v/>
+      </c>
+      <c r="P16" s="9">
+        <f>SUM(P5:P15)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="10" t="inlineStr"/>
+      <c r="R16" s="10" t="inlineStr"/>
+      <c r="S16" s="9" t="inlineStr"/>
+      <c r="T16" s="9" t="inlineStr"/>
+      <c r="U16" s="9" t="inlineStr"/>
+      <c r="V16" s="9" t="inlineStr"/>
+      <c r="W16" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:Q15">
+  <conditionalFormatting sqref="A5:W15">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$K5&gt;0</formula>
+      <formula>$O5&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND($G5&gt;0,$G5=$J5)</formula>
+      <formula>AND($C5&gt;0,$C5=$L5)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2482,7 +2095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18948,7 +18561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18967,6 +18580,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -18988,6 +18602,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -19023,6 +18638,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -69,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +99,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -18567,103 +18577,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="130" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>회신 현황 체크리스트 사용 안내 (2026-10-08)</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr"/>
+    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>대상: 판단 보류 29 + 미비 17 + 보완 필요 189 = 235건 + 보유 확인 5건 = 240행(‘상세’). 담당자 11명(이은주·박철호 공동 1건 포함).</t>
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>■ 개요</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>발송용 메시지: 99_산출물/발송용_최종_20261008/ (담당자 1명당 1통, 지성규·이광재·이은주는 보유 확인 포함).</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>대상: 판단 보류 29 + 미비 17 + 보완 필요 189 = 235건 + 보유 확인 5건 = 240행. 담당자 11명(이은주·박철호 공동 1건 포함).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>회신 기한: 2026-10-15 (사용자 지정; 보유 확인은 같은 날짜 적용).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>발송용 메시지: 99_산출물/발송용_최종_20261008/ (담당자 1명당 1통, 지성규·이광재·이은주는 보유 확인 포함). 근거 자료는 99_산출물의 근거 정리 문서를 참고합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>회신 기한: 2026-10-15 (사용자 지정, 보유 확인에도 같은 날짜 적용).</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>입력 순서</t>
-        </is>
-      </c>
+      <c r="A7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1. 메시지를 보낸 뒤 '상세'의 발송일을 입력하고 회신 상태를 '발송(회신 대기)'로 바꿉니다(담당자별 일괄 필터 사용).</t>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>■ 시트 구성</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2. 회신이 오면 회신일·회신 내용 요약·확인자를 적고 회신 상태를 '일부 회신' 또는 '회신 완료'로 바꿉니다.</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>1. 담당자별 현황: 담당자 1명당 1행. 요청 건수(유형별), 회신 진행(미발송·발송·일부 회신·재요청·회신 완료·회신율·미회신·지연·조치 완료), 최근 발송일, 가장 이른 미회신 기한, 다음 조치, 판단 보류·미비·보유 확인의 SQ NO를 한 줄에 보여줍니다. 직접 입력하지 않고 '상세' 입력에 따라 자동 집계됩니다(보완 필요 SQ NO는 상세에서 확인).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3. 회신 내용에 따른 조치('회신 후 필요한 조치' 열)를 처리한 뒤 조치 완료를 '완료'로 바꿉니다.</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2. 유형별 현황: 판단 보류·미비·보완 필요·보유 확인별 총 건수와 회신 진행 집계(자동).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4. 기한 2026-10-15 가 지났는데 회신 완료가 아닌 건은 행이 붉게 표시되고 '담당자별 현황'의 지연에 집계됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>3. 상세: 240행 건별 기록. 여기에만 입력합니다(아래 입력 순서 참고).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>4. 사용 안내: 이 시트.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>주의</t>
-        </is>
-      </c>
+      <c r="A13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- 회신 내용은 사람이 확인해 확정하기 전에는 FM 번호·문서 상태를 바꾸지 않습니다.</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>■ 입력 순서 (상세 시트)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>- 이 체크리스트는 기록용이며 회신 상태는 직접 입력해야 합니다(자동 수집하지 않습니다).</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>1. 메시지를 보낸 뒤 '발송일'을 입력하고 '회신 상태'를 '발송(회신 대기)'로 바꿉니다. 담당자 열 필터로 해당 담당자 행을 한꺼번에 선택하면 편합니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>- 집계는 수식입니다. 엑셀에서 열면 자동 계산됩니다.</t>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2. 회신이 오면 '회신일'·'회신 내용 요약'·'확인자'를 적고 회신 상태를 '일부 회신' 또는 '회신 완료'로 바꿉니다. 보완이 필요하면 '재요청'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>3. '회신 후 필요한 조치' 열의 후속 작업을 처리한 뒤 '조치 완료'를 '완료'(진행 중이면 '진행 중')로 바꿉니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>■ 자동 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>- 지연: 발송일이 있고 회신 상태가 '회신 완료'가 아니며 회신 기한이 오늘보다 앞이면 상세 행이 붉게 표시되고 담당자별 현황의 '지연'에 집계됩니다. 회신 완료 행은 초록으로 표시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>- 다음 조치(담당자별 현황): 발송 필요 / 일부 미발송 — 확인 / 회신 대기 / 지연 — 재촉 필요 / 회신 완료 — 조치 완료 여부 확인 중 하나가 자동으로 나옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>- 담당자별 현황 행의 색: 지연이 있으면 붉게, 담당자의 모든 건이 회신 완료면 초록으로 표시됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>■ 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>- 회신 내용은 사람이 확인해 확정하기 전에는 FM 번호·문서 상태를 바꾸지 않습니다. 조치 후 증빙 매핑표·FM Master 갱신은 별도로 진행합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>- 이 체크리스트는 기록용이며 발송·회신 상태는 직접 입력해야 합니다(자동 수집하지 않습니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>- 집계는 수식(COUNTIFS, MAXIFS/MINIFS)입니다. 엑셀(MAXIFS는 2019 이상)에서 열면 자동 계산됩니다. '상세' 열 순서나 이름을 바꾸면 집계가 깨집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>- 담당자별 현황의 SQ NO 목록은 요청 시점(2026-10-08) 값입니다. 담당자·건이 바뀌면 상세 시트를 고치고 이 목록은 직접 수정하세요.</t>
         </is>
       </c>
     </row>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -2273,10 +2273,12 @@
       <c r="J2" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K2" s="8" t="n"/>
+      <c r="K2" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M2" s="8" t="n"/>
@@ -2341,10 +2343,12 @@
       <c r="J3" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K3" s="8" t="n"/>
+      <c r="K3" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M3" s="8" t="n"/>
@@ -2409,10 +2413,12 @@
       <c r="J4" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K4" s="8" t="n"/>
+      <c r="K4" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M4" s="8" t="n"/>
@@ -2477,10 +2483,12 @@
       <c r="J5" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K5" s="8" t="n"/>
+      <c r="K5" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M5" s="8" t="n"/>
@@ -2545,10 +2553,12 @@
       <c r="J6" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K6" s="8" t="n"/>
+      <c r="K6" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M6" s="8" t="n"/>
@@ -2613,10 +2623,12 @@
       <c r="J7" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K7" s="8" t="n"/>
+      <c r="K7" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M7" s="8" t="n"/>
@@ -2681,10 +2693,12 @@
       <c r="J8" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K8" s="8" t="n"/>
+      <c r="K8" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M8" s="8" t="n"/>
@@ -2749,10 +2763,12 @@
       <c r="J9" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K9" s="8" t="n"/>
+      <c r="K9" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M9" s="8" t="n"/>
@@ -2817,10 +2833,12 @@
       <c r="J10" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K10" s="8" t="n"/>
+      <c r="K10" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M10" s="8" t="n"/>
@@ -2885,10 +2903,12 @@
       <c r="J11" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K11" s="8" t="n"/>
+      <c r="K11" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M11" s="8" t="n"/>
@@ -2953,10 +2973,12 @@
       <c r="J12" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K12" s="8" t="n"/>
+      <c r="K12" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M12" s="8" t="n"/>
@@ -3021,10 +3043,12 @@
       <c r="J13" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K13" s="8" t="n"/>
+      <c r="K13" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M13" s="8" t="n"/>
@@ -3089,10 +3113,12 @@
       <c r="J14" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K14" s="8" t="n"/>
+      <c r="K14" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M14" s="8" t="n"/>
@@ -3157,10 +3183,12 @@
       <c r="J15" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K15" s="8" t="n"/>
+      <c r="K15" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M15" s="8" t="n"/>
@@ -3225,10 +3253,12 @@
       <c r="J16" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K16" s="8" t="n"/>
+      <c r="K16" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M16" s="8" t="n"/>
@@ -3293,10 +3323,12 @@
       <c r="J17" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K17" s="8" t="n"/>
+      <c r="K17" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M17" s="8" t="n"/>
@@ -3361,10 +3393,12 @@
       <c r="J18" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K18" s="8" t="n"/>
+      <c r="K18" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M18" s="8" t="n"/>
@@ -3429,10 +3463,12 @@
       <c r="J19" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K19" s="8" t="n"/>
+      <c r="K19" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M19" s="8" t="n"/>
@@ -3497,10 +3533,12 @@
       <c r="J20" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K20" s="8" t="n"/>
+      <c r="K20" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M20" s="8" t="n"/>
@@ -3565,10 +3603,12 @@
       <c r="J21" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K21" s="8" t="n"/>
+      <c r="K21" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M21" s="8" t="n"/>
@@ -3633,10 +3673,12 @@
       <c r="J22" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K22" s="8" t="n"/>
+      <c r="K22" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M22" s="8" t="n"/>
@@ -3701,10 +3743,12 @@
       <c r="J23" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K23" s="8" t="n"/>
+      <c r="K23" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M23" s="8" t="n"/>
@@ -3769,10 +3813,12 @@
       <c r="J24" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K24" s="8" t="n"/>
+      <c r="K24" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M24" s="8" t="n"/>
@@ -3837,10 +3883,12 @@
       <c r="J25" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K25" s="8" t="n"/>
+      <c r="K25" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M25" s="8" t="n"/>
@@ -3905,10 +3953,12 @@
       <c r="J26" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K26" s="8" t="n"/>
+      <c r="K26" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M26" s="8" t="n"/>
@@ -3973,10 +4023,12 @@
       <c r="J27" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K27" s="8" t="n"/>
+      <c r="K27" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M27" s="8" t="n"/>
@@ -4041,10 +4093,12 @@
       <c r="J28" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K28" s="8" t="n"/>
+      <c r="K28" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M28" s="8" t="n"/>
@@ -4109,10 +4163,12 @@
       <c r="J29" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K29" s="8" t="n"/>
+      <c r="K29" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M29" s="8" t="n"/>
@@ -4177,10 +4233,12 @@
       <c r="J30" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K30" s="8" t="n"/>
+      <c r="K30" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M30" s="8" t="n"/>
@@ -4245,10 +4303,12 @@
       <c r="J31" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K31" s="8" t="n"/>
+      <c r="K31" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M31" s="8" t="n"/>
@@ -4313,10 +4373,12 @@
       <c r="J32" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K32" s="8" t="n"/>
+      <c r="K32" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M32" s="8" t="n"/>
@@ -4381,10 +4443,12 @@
       <c r="J33" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K33" s="8" t="n"/>
+      <c r="K33" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M33" s="8" t="n"/>
@@ -4449,10 +4513,12 @@
       <c r="J34" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K34" s="8" t="n"/>
+      <c r="K34" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M34" s="8" t="n"/>
@@ -4517,10 +4583,12 @@
       <c r="J35" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K35" s="8" t="n"/>
+      <c r="K35" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M35" s="8" t="n"/>
@@ -4585,10 +4653,12 @@
       <c r="J36" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K36" s="8" t="n"/>
+      <c r="K36" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M36" s="8" t="n"/>
@@ -4653,10 +4723,12 @@
       <c r="J37" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K37" s="8" t="n"/>
+      <c r="K37" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M37" s="8" t="n"/>
@@ -4721,10 +4793,12 @@
       <c r="J38" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K38" s="8" t="n"/>
+      <c r="K38" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M38" s="8" t="n"/>
@@ -4789,10 +4863,12 @@
       <c r="J39" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K39" s="8" t="n"/>
+      <c r="K39" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M39" s="8" t="n"/>
@@ -4857,10 +4933,12 @@
       <c r="J40" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K40" s="8" t="n"/>
+      <c r="K40" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M40" s="8" t="n"/>
@@ -4925,10 +5003,12 @@
       <c r="J41" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K41" s="8" t="n"/>
+      <c r="K41" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M41" s="8" t="n"/>
@@ -4993,10 +5073,12 @@
       <c r="J42" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K42" s="8" t="n"/>
+      <c r="K42" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M42" s="8" t="n"/>
@@ -5061,10 +5143,12 @@
       <c r="J43" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K43" s="8" t="n"/>
+      <c r="K43" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M43" s="8" t="n"/>
@@ -5129,10 +5213,12 @@
       <c r="J44" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K44" s="8" t="n"/>
+      <c r="K44" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M44" s="8" t="n"/>
@@ -5197,10 +5283,12 @@
       <c r="J45" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K45" s="8" t="n"/>
+      <c r="K45" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M45" s="8" t="n"/>
@@ -5265,10 +5353,12 @@
       <c r="J46" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K46" s="8" t="n"/>
+      <c r="K46" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M46" s="8" t="n"/>
@@ -5333,10 +5423,12 @@
       <c r="J47" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K47" s="8" t="n"/>
+      <c r="K47" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M47" s="8" t="n"/>
@@ -5401,10 +5493,12 @@
       <c r="J48" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K48" s="8" t="n"/>
+      <c r="K48" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M48" s="8" t="n"/>
@@ -5469,10 +5563,12 @@
       <c r="J49" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K49" s="8" t="n"/>
+      <c r="K49" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M49" s="8" t="n"/>
@@ -5537,10 +5633,12 @@
       <c r="J50" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K50" s="8" t="n"/>
+      <c r="K50" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M50" s="8" t="n"/>
@@ -5605,10 +5703,12 @@
       <c r="J51" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K51" s="8" t="n"/>
+      <c r="K51" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M51" s="8" t="n"/>
@@ -5673,10 +5773,12 @@
       <c r="J52" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K52" s="8" t="n"/>
+      <c r="K52" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M52" s="8" t="n"/>
@@ -5741,10 +5843,12 @@
       <c r="J53" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K53" s="8" t="n"/>
+      <c r="K53" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M53" s="8" t="n"/>
@@ -5809,10 +5913,12 @@
       <c r="J54" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K54" s="8" t="n"/>
+      <c r="K54" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M54" s="8" t="n"/>
@@ -5877,10 +5983,12 @@
       <c r="J55" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K55" s="8" t="n"/>
+      <c r="K55" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M55" s="8" t="n"/>
@@ -5945,10 +6053,12 @@
       <c r="J56" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K56" s="8" t="n"/>
+      <c r="K56" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M56" s="8" t="n"/>
@@ -6013,10 +6123,12 @@
       <c r="J57" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K57" s="8" t="n"/>
+      <c r="K57" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M57" s="8" t="n"/>
@@ -6081,10 +6193,12 @@
       <c r="J58" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K58" s="8" t="n"/>
+      <c r="K58" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M58" s="8" t="n"/>
@@ -6149,10 +6263,12 @@
       <c r="J59" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K59" s="8" t="n"/>
+      <c r="K59" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M59" s="8" t="n"/>
@@ -6217,10 +6333,12 @@
       <c r="J60" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K60" s="8" t="n"/>
+      <c r="K60" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M60" s="8" t="n"/>
@@ -6285,10 +6403,12 @@
       <c r="J61" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K61" s="8" t="n"/>
+      <c r="K61" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M61" s="8" t="n"/>
@@ -6353,10 +6473,12 @@
       <c r="J62" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K62" s="8" t="n"/>
+      <c r="K62" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M62" s="8" t="n"/>
@@ -6421,10 +6543,12 @@
       <c r="J63" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K63" s="8" t="n"/>
+      <c r="K63" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M63" s="8" t="n"/>
@@ -6489,10 +6613,12 @@
       <c r="J64" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K64" s="8" t="n"/>
+      <c r="K64" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M64" s="8" t="n"/>
@@ -6557,10 +6683,12 @@
       <c r="J65" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K65" s="8" t="n"/>
+      <c r="K65" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M65" s="8" t="n"/>
@@ -6625,10 +6753,12 @@
       <c r="J66" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K66" s="8" t="n"/>
+      <c r="K66" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M66" s="8" t="n"/>
@@ -6693,10 +6823,12 @@
       <c r="J67" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K67" s="8" t="n"/>
+      <c r="K67" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M67" s="8" t="n"/>
@@ -6761,10 +6893,12 @@
       <c r="J68" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K68" s="8" t="n"/>
+      <c r="K68" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M68" s="8" t="n"/>
@@ -6829,10 +6963,12 @@
       <c r="J69" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K69" s="8" t="n"/>
+      <c r="K69" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M69" s="8" t="n"/>
@@ -6897,10 +7033,12 @@
       <c r="J70" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K70" s="8" t="n"/>
+      <c r="K70" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M70" s="8" t="n"/>
@@ -6965,10 +7103,12 @@
       <c r="J71" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K71" s="8" t="n"/>
+      <c r="K71" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M71" s="8" t="n"/>
@@ -7033,10 +7173,12 @@
       <c r="J72" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K72" s="8" t="n"/>
+      <c r="K72" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M72" s="8" t="n"/>
@@ -7101,10 +7243,12 @@
       <c r="J73" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K73" s="8" t="n"/>
+      <c r="K73" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M73" s="8" t="n"/>
@@ -7169,10 +7313,12 @@
       <c r="J74" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K74" s="8" t="n"/>
+      <c r="K74" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M74" s="8" t="n"/>
@@ -7237,10 +7383,12 @@
       <c r="J75" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K75" s="8" t="n"/>
+      <c r="K75" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M75" s="8" t="n"/>
@@ -7305,10 +7453,12 @@
       <c r="J76" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K76" s="8" t="n"/>
+      <c r="K76" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M76" s="8" t="n"/>
@@ -7373,10 +7523,12 @@
       <c r="J77" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K77" s="8" t="n"/>
+      <c r="K77" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M77" s="8" t="n"/>
@@ -7441,10 +7593,12 @@
       <c r="J78" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K78" s="8" t="n"/>
+      <c r="K78" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M78" s="8" t="n"/>
@@ -7509,10 +7663,12 @@
       <c r="J79" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K79" s="8" t="n"/>
+      <c r="K79" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M79" s="8" t="n"/>
@@ -7577,10 +7733,12 @@
       <c r="J80" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K80" s="8" t="n"/>
+      <c r="K80" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M80" s="8" t="n"/>
@@ -7645,10 +7803,12 @@
       <c r="J81" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K81" s="8" t="n"/>
+      <c r="K81" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M81" s="8" t="n"/>
@@ -7713,10 +7873,12 @@
       <c r="J82" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K82" s="8" t="n"/>
+      <c r="K82" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M82" s="8" t="n"/>
@@ -7781,10 +7943,12 @@
       <c r="J83" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K83" s="8" t="n"/>
+      <c r="K83" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M83" s="8" t="n"/>
@@ -7849,10 +8013,12 @@
       <c r="J84" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K84" s="8" t="n"/>
+      <c r="K84" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M84" s="8" t="n"/>
@@ -7917,10 +8083,12 @@
       <c r="J85" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K85" s="8" t="n"/>
+      <c r="K85" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M85" s="8" t="n"/>
@@ -7985,10 +8153,12 @@
       <c r="J86" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K86" s="8" t="n"/>
+      <c r="K86" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M86" s="8" t="n"/>
@@ -8053,10 +8223,12 @@
       <c r="J87" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K87" s="8" t="n"/>
+      <c r="K87" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M87" s="8" t="n"/>
@@ -8121,10 +8293,12 @@
       <c r="J88" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K88" s="8" t="n"/>
+      <c r="K88" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M88" s="8" t="n"/>
@@ -8189,10 +8363,12 @@
       <c r="J89" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K89" s="8" t="n"/>
+      <c r="K89" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M89" s="8" t="n"/>
@@ -8257,10 +8433,12 @@
       <c r="J90" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K90" s="8" t="n"/>
+      <c r="K90" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M90" s="8" t="n"/>
@@ -8325,10 +8503,12 @@
       <c r="J91" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K91" s="8" t="n"/>
+      <c r="K91" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M91" s="8" t="n"/>
@@ -8393,10 +8573,12 @@
       <c r="J92" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K92" s="8" t="n"/>
+      <c r="K92" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M92" s="8" t="n"/>
@@ -8461,10 +8643,12 @@
       <c r="J93" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K93" s="8" t="n"/>
+      <c r="K93" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M93" s="8" t="n"/>
@@ -8529,10 +8713,12 @@
       <c r="J94" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K94" s="8" t="n"/>
+      <c r="K94" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M94" s="8" t="n"/>
@@ -8597,10 +8783,12 @@
       <c r="J95" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K95" s="8" t="n"/>
+      <c r="K95" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M95" s="8" t="n"/>
@@ -8665,10 +8853,12 @@
       <c r="J96" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K96" s="8" t="n"/>
+      <c r="K96" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M96" s="8" t="n"/>
@@ -8733,10 +8923,12 @@
       <c r="J97" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K97" s="8" t="n"/>
+      <c r="K97" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M97" s="8" t="n"/>
@@ -8801,10 +8993,12 @@
       <c r="J98" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K98" s="8" t="n"/>
+      <c r="K98" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M98" s="8" t="n"/>
@@ -8869,10 +9063,12 @@
       <c r="J99" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K99" s="8" t="n"/>
+      <c r="K99" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M99" s="8" t="n"/>
@@ -8937,10 +9133,12 @@
       <c r="J100" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K100" s="8" t="n"/>
+      <c r="K100" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M100" s="8" t="n"/>
@@ -9005,10 +9203,12 @@
       <c r="J101" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K101" s="8" t="n"/>
+      <c r="K101" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M101" s="8" t="n"/>
@@ -9073,10 +9273,12 @@
       <c r="J102" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K102" s="8" t="n"/>
+      <c r="K102" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M102" s="8" t="n"/>
@@ -9141,10 +9343,12 @@
       <c r="J103" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K103" s="8" t="n"/>
+      <c r="K103" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M103" s="8" t="n"/>
@@ -9209,10 +9413,12 @@
       <c r="J104" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K104" s="8" t="n"/>
+      <c r="K104" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M104" s="8" t="n"/>
@@ -9277,10 +9483,12 @@
       <c r="J105" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K105" s="8" t="n"/>
+      <c r="K105" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M105" s="8" t="n"/>
@@ -9345,10 +9553,12 @@
       <c r="J106" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K106" s="8" t="n"/>
+      <c r="K106" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M106" s="8" t="n"/>
@@ -9413,10 +9623,12 @@
       <c r="J107" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K107" s="8" t="n"/>
+      <c r="K107" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M107" s="8" t="n"/>
@@ -9481,10 +9693,12 @@
       <c r="J108" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K108" s="8" t="n"/>
+      <c r="K108" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M108" s="8" t="n"/>
@@ -9549,10 +9763,12 @@
       <c r="J109" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K109" s="8" t="n"/>
+      <c r="K109" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M109" s="8" t="n"/>
@@ -9617,10 +9833,12 @@
       <c r="J110" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K110" s="8" t="n"/>
+      <c r="K110" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M110" s="8" t="n"/>
@@ -9685,10 +9903,12 @@
       <c r="J111" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K111" s="8" t="n"/>
+      <c r="K111" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M111" s="8" t="n"/>
@@ -9753,10 +9973,12 @@
       <c r="J112" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K112" s="8" t="n"/>
+      <c r="K112" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M112" s="8" t="n"/>
@@ -9821,10 +10043,12 @@
       <c r="J113" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K113" s="8" t="n"/>
+      <c r="K113" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M113" s="8" t="n"/>
@@ -9889,10 +10113,12 @@
       <c r="J114" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K114" s="8" t="n"/>
+      <c r="K114" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M114" s="8" t="n"/>
@@ -9957,10 +10183,12 @@
       <c r="J115" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K115" s="8" t="n"/>
+      <c r="K115" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M115" s="8" t="n"/>
@@ -10025,10 +10253,12 @@
       <c r="J116" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K116" s="8" t="n"/>
+      <c r="K116" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M116" s="8" t="n"/>
@@ -10093,10 +10323,12 @@
       <c r="J117" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K117" s="8" t="n"/>
+      <c r="K117" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M117" s="8" t="n"/>
@@ -10161,10 +10393,12 @@
       <c r="J118" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K118" s="8" t="n"/>
+      <c r="K118" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M118" s="8" t="n"/>
@@ -10229,10 +10463,12 @@
       <c r="J119" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K119" s="8" t="n"/>
+      <c r="K119" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M119" s="8" t="n"/>
@@ -10297,10 +10533,12 @@
       <c r="J120" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K120" s="8" t="n"/>
+      <c r="K120" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M120" s="8" t="n"/>
@@ -10365,10 +10603,12 @@
       <c r="J121" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K121" s="8" t="n"/>
+      <c r="K121" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M121" s="8" t="n"/>
@@ -10433,10 +10673,12 @@
       <c r="J122" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K122" s="8" t="n"/>
+      <c r="K122" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M122" s="8" t="n"/>
@@ -10501,10 +10743,12 @@
       <c r="J123" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K123" s="8" t="n"/>
+      <c r="K123" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M123" s="8" t="n"/>
@@ -10569,10 +10813,12 @@
       <c r="J124" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K124" s="8" t="n"/>
+      <c r="K124" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M124" s="8" t="n"/>
@@ -10637,10 +10883,12 @@
       <c r="J125" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K125" s="8" t="n"/>
+      <c r="K125" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M125" s="8" t="n"/>
@@ -10705,10 +10953,12 @@
       <c r="J126" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K126" s="8" t="n"/>
+      <c r="K126" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M126" s="8" t="n"/>
@@ -10773,10 +11023,12 @@
       <c r="J127" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K127" s="8" t="n"/>
+      <c r="K127" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M127" s="8" t="n"/>
@@ -10841,10 +11093,12 @@
       <c r="J128" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K128" s="8" t="n"/>
+      <c r="K128" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M128" s="8" t="n"/>
@@ -10909,10 +11163,12 @@
       <c r="J129" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K129" s="8" t="n"/>
+      <c r="K129" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M129" s="8" t="n"/>
@@ -10977,10 +11233,12 @@
       <c r="J130" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K130" s="8" t="n"/>
+      <c r="K130" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M130" s="8" t="n"/>
@@ -11045,10 +11303,12 @@
       <c r="J131" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K131" s="8" t="n"/>
+      <c r="K131" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M131" s="8" t="n"/>
@@ -11113,10 +11373,12 @@
       <c r="J132" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K132" s="8" t="n"/>
+      <c r="K132" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M132" s="8" t="n"/>
@@ -11181,10 +11443,12 @@
       <c r="J133" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K133" s="8" t="n"/>
+      <c r="K133" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M133" s="8" t="n"/>
@@ -11249,10 +11513,12 @@
       <c r="J134" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K134" s="8" t="n"/>
+      <c r="K134" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M134" s="8" t="n"/>
@@ -11317,10 +11583,12 @@
       <c r="J135" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K135" s="8" t="n"/>
+      <c r="K135" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M135" s="8" t="n"/>
@@ -11385,10 +11653,12 @@
       <c r="J136" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K136" s="8" t="n"/>
+      <c r="K136" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M136" s="8" t="n"/>
@@ -11453,10 +11723,12 @@
       <c r="J137" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K137" s="8" t="n"/>
+      <c r="K137" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M137" s="8" t="n"/>
@@ -11521,10 +11793,12 @@
       <c r="J138" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K138" s="8" t="n"/>
+      <c r="K138" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M138" s="8" t="n"/>
@@ -11589,10 +11863,12 @@
       <c r="J139" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K139" s="8" t="n"/>
+      <c r="K139" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M139" s="8" t="n"/>
@@ -11657,10 +11933,12 @@
       <c r="J140" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K140" s="8" t="n"/>
+      <c r="K140" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M140" s="8" t="n"/>
@@ -11725,10 +12003,12 @@
       <c r="J141" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K141" s="8" t="n"/>
+      <c r="K141" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M141" s="8" t="n"/>
@@ -11793,10 +12073,12 @@
       <c r="J142" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K142" s="8" t="n"/>
+      <c r="K142" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M142" s="8" t="n"/>
@@ -11861,10 +12143,12 @@
       <c r="J143" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K143" s="8" t="n"/>
+      <c r="K143" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M143" s="8" t="n"/>
@@ -11929,10 +12213,12 @@
       <c r="J144" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K144" s="8" t="n"/>
+      <c r="K144" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M144" s="8" t="n"/>
@@ -11997,10 +12283,12 @@
       <c r="J145" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K145" s="8" t="n"/>
+      <c r="K145" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M145" s="8" t="n"/>
@@ -12065,10 +12353,12 @@
       <c r="J146" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K146" s="8" t="n"/>
+      <c r="K146" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M146" s="8" t="n"/>
@@ -12133,10 +12423,12 @@
       <c r="J147" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K147" s="8" t="n"/>
+      <c r="K147" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M147" s="8" t="n"/>
@@ -12201,10 +12493,12 @@
       <c r="J148" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K148" s="8" t="n"/>
+      <c r="K148" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M148" s="8" t="n"/>
@@ -12269,10 +12563,12 @@
       <c r="J149" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K149" s="8" t="n"/>
+      <c r="K149" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M149" s="8" t="n"/>
@@ -12337,10 +12633,12 @@
       <c r="J150" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K150" s="8" t="n"/>
+      <c r="K150" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M150" s="8" t="n"/>
@@ -12405,10 +12703,12 @@
       <c r="J151" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K151" s="8" t="n"/>
+      <c r="K151" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M151" s="8" t="n"/>
@@ -12473,10 +12773,12 @@
       <c r="J152" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K152" s="8" t="n"/>
+      <c r="K152" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M152" s="8" t="n"/>
@@ -12541,10 +12843,12 @@
       <c r="J153" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K153" s="8" t="n"/>
+      <c r="K153" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M153" s="8" t="n"/>
@@ -12609,10 +12913,12 @@
       <c r="J154" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K154" s="8" t="n"/>
+      <c r="K154" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M154" s="8" t="n"/>
@@ -12677,10 +12983,12 @@
       <c r="J155" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K155" s="8" t="n"/>
+      <c r="K155" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M155" s="8" t="n"/>
@@ -12745,10 +13053,12 @@
       <c r="J156" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K156" s="8" t="n"/>
+      <c r="K156" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M156" s="8" t="n"/>
@@ -12813,10 +13123,12 @@
       <c r="J157" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K157" s="8" t="n"/>
+      <c r="K157" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M157" s="8" t="n"/>
@@ -12881,10 +13193,12 @@
       <c r="J158" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K158" s="8" t="n"/>
+      <c r="K158" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M158" s="8" t="n"/>
@@ -12949,10 +13263,12 @@
       <c r="J159" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K159" s="8" t="n"/>
+      <c r="K159" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M159" s="8" t="n"/>
@@ -13017,10 +13333,12 @@
       <c r="J160" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K160" s="8" t="n"/>
+      <c r="K160" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M160" s="8" t="n"/>
@@ -13085,10 +13403,12 @@
       <c r="J161" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K161" s="8" t="n"/>
+      <c r="K161" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M161" s="8" t="n"/>
@@ -13153,10 +13473,12 @@
       <c r="J162" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K162" s="8" t="n"/>
+      <c r="K162" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M162" s="8" t="n"/>
@@ -13221,10 +13543,12 @@
       <c r="J163" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K163" s="8" t="n"/>
+      <c r="K163" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M163" s="8" t="n"/>
@@ -13289,10 +13613,12 @@
       <c r="J164" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K164" s="8" t="n"/>
+      <c r="K164" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M164" s="8" t="n"/>
@@ -13357,10 +13683,12 @@
       <c r="J165" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K165" s="8" t="n"/>
+      <c r="K165" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M165" s="8" t="n"/>
@@ -13425,10 +13753,12 @@
       <c r="J166" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K166" s="8" t="n"/>
+      <c r="K166" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M166" s="8" t="n"/>
@@ -13493,10 +13823,12 @@
       <c r="J167" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K167" s="8" t="n"/>
+      <c r="K167" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M167" s="8" t="n"/>
@@ -13561,10 +13893,12 @@
       <c r="J168" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K168" s="8" t="n"/>
+      <c r="K168" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M168" s="8" t="n"/>
@@ -13629,10 +13963,12 @@
       <c r="J169" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K169" s="8" t="n"/>
+      <c r="K169" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M169" s="8" t="n"/>
@@ -13697,10 +14033,12 @@
       <c r="J170" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K170" s="8" t="n"/>
+      <c r="K170" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M170" s="8" t="n"/>
@@ -13765,10 +14103,12 @@
       <c r="J171" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K171" s="8" t="n"/>
+      <c r="K171" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M171" s="8" t="n"/>
@@ -13833,10 +14173,12 @@
       <c r="J172" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K172" s="8" t="n"/>
+      <c r="K172" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M172" s="8" t="n"/>
@@ -13901,10 +14243,12 @@
       <c r="J173" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K173" s="8" t="n"/>
+      <c r="K173" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M173" s="8" t="n"/>
@@ -13969,10 +14313,12 @@
       <c r="J174" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K174" s="8" t="n"/>
+      <c r="K174" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M174" s="8" t="n"/>
@@ -14037,10 +14383,12 @@
       <c r="J175" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K175" s="8" t="n"/>
+      <c r="K175" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M175" s="8" t="n"/>
@@ -14105,10 +14453,12 @@
       <c r="J176" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K176" s="8" t="n"/>
+      <c r="K176" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M176" s="8" t="n"/>
@@ -14173,10 +14523,12 @@
       <c r="J177" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K177" s="8" t="n"/>
+      <c r="K177" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M177" s="8" t="n"/>
@@ -14241,10 +14593,12 @@
       <c r="J178" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K178" s="8" t="n"/>
+      <c r="K178" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M178" s="8" t="n"/>
@@ -14309,10 +14663,12 @@
       <c r="J179" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K179" s="8" t="n"/>
+      <c r="K179" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M179" s="8" t="n"/>
@@ -14377,10 +14733,12 @@
       <c r="J180" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K180" s="8" t="n"/>
+      <c r="K180" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M180" s="8" t="n"/>
@@ -14445,10 +14803,12 @@
       <c r="J181" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K181" s="8" t="n"/>
+      <c r="K181" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M181" s="8" t="n"/>
@@ -14513,10 +14873,12 @@
       <c r="J182" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K182" s="8" t="n"/>
+      <c r="K182" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M182" s="8" t="n"/>
@@ -14581,10 +14943,12 @@
       <c r="J183" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K183" s="8" t="n"/>
+      <c r="K183" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M183" s="8" t="n"/>
@@ -14649,10 +15013,12 @@
       <c r="J184" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K184" s="8" t="n"/>
+      <c r="K184" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M184" s="8" t="n"/>
@@ -14717,10 +15083,12 @@
       <c r="J185" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K185" s="8" t="n"/>
+      <c r="K185" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M185" s="8" t="n"/>
@@ -14785,10 +15153,12 @@
       <c r="J186" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K186" s="8" t="n"/>
+      <c r="K186" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M186" s="8" t="n"/>
@@ -14853,10 +15223,12 @@
       <c r="J187" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K187" s="8" t="n"/>
+      <c r="K187" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M187" s="8" t="n"/>
@@ -14921,10 +15293,12 @@
       <c r="J188" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K188" s="8" t="n"/>
+      <c r="K188" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M188" s="8" t="n"/>
@@ -14989,10 +15363,12 @@
       <c r="J189" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K189" s="8" t="n"/>
+      <c r="K189" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M189" s="8" t="n"/>
@@ -15057,10 +15433,12 @@
       <c r="J190" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K190" s="8" t="n"/>
+      <c r="K190" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M190" s="8" t="n"/>
@@ -15125,10 +15503,12 @@
       <c r="J191" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K191" s="8" t="n"/>
+      <c r="K191" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M191" s="8" t="n"/>
@@ -15193,10 +15573,12 @@
       <c r="J192" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K192" s="8" t="n"/>
+      <c r="K192" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M192" s="8" t="n"/>
@@ -15261,10 +15643,12 @@
       <c r="J193" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K193" s="8" t="n"/>
+      <c r="K193" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M193" s="8" t="n"/>
@@ -15329,10 +15713,12 @@
       <c r="J194" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K194" s="8" t="n"/>
+      <c r="K194" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M194" s="8" t="n"/>
@@ -15397,10 +15783,12 @@
       <c r="J195" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K195" s="8" t="n"/>
+      <c r="K195" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M195" s="8" t="n"/>
@@ -15465,10 +15853,12 @@
       <c r="J196" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K196" s="8" t="n"/>
+      <c r="K196" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M196" s="8" t="n"/>
@@ -15533,10 +15923,12 @@
       <c r="J197" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K197" s="8" t="n"/>
+      <c r="K197" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M197" s="8" t="n"/>
@@ -15601,10 +15993,12 @@
       <c r="J198" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K198" s="8" t="n"/>
+      <c r="K198" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M198" s="8" t="n"/>
@@ -15669,10 +16063,12 @@
       <c r="J199" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K199" s="8" t="n"/>
+      <c r="K199" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M199" s="8" t="n"/>
@@ -15737,10 +16133,12 @@
       <c r="J200" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K200" s="8" t="n"/>
+      <c r="K200" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M200" s="8" t="n"/>
@@ -15805,10 +16203,12 @@
       <c r="J201" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K201" s="8" t="n"/>
+      <c r="K201" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M201" s="8" t="n"/>
@@ -15873,10 +16273,12 @@
       <c r="J202" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K202" s="8" t="n"/>
+      <c r="K202" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L202" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M202" s="8" t="n"/>
@@ -15941,10 +16343,12 @@
       <c r="J203" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K203" s="8" t="n"/>
+      <c r="K203" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M203" s="8" t="n"/>
@@ -16009,10 +16413,12 @@
       <c r="J204" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K204" s="8" t="n"/>
+      <c r="K204" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M204" s="8" t="n"/>
@@ -16077,10 +16483,12 @@
       <c r="J205" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K205" s="8" t="n"/>
+      <c r="K205" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M205" s="8" t="n"/>
@@ -16145,10 +16553,12 @@
       <c r="J206" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K206" s="8" t="n"/>
+      <c r="K206" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L206" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M206" s="8" t="n"/>
@@ -16213,10 +16623,12 @@
       <c r="J207" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K207" s="8" t="n"/>
+      <c r="K207" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M207" s="8" t="n"/>
@@ -16281,10 +16693,12 @@
       <c r="J208" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K208" s="8" t="n"/>
+      <c r="K208" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L208" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M208" s="8" t="n"/>
@@ -16349,10 +16763,12 @@
       <c r="J209" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K209" s="8" t="n"/>
+      <c r="K209" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M209" s="8" t="n"/>
@@ -16417,10 +16833,12 @@
       <c r="J210" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K210" s="8" t="n"/>
+      <c r="K210" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L210" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M210" s="8" t="n"/>
@@ -16485,10 +16903,12 @@
       <c r="J211" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K211" s="8" t="n"/>
+      <c r="K211" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M211" s="8" t="n"/>
@@ -16553,10 +16973,12 @@
       <c r="J212" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K212" s="8" t="n"/>
+      <c r="K212" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L212" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M212" s="8" t="n"/>
@@ -16621,10 +17043,12 @@
       <c r="J213" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K213" s="8" t="n"/>
+      <c r="K213" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M213" s="8" t="n"/>
@@ -16689,10 +17113,12 @@
       <c r="J214" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K214" s="8" t="n"/>
+      <c r="K214" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L214" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M214" s="8" t="n"/>
@@ -16757,10 +17183,12 @@
       <c r="J215" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K215" s="8" t="n"/>
+      <c r="K215" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M215" s="8" t="n"/>
@@ -16825,10 +17253,12 @@
       <c r="J216" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K216" s="8" t="n"/>
+      <c r="K216" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L216" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M216" s="8" t="n"/>
@@ -16893,10 +17323,12 @@
       <c r="J217" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K217" s="8" t="n"/>
+      <c r="K217" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M217" s="8" t="n"/>
@@ -16961,10 +17393,12 @@
       <c r="J218" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K218" s="8" t="n"/>
+      <c r="K218" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L218" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M218" s="8" t="n"/>
@@ -17029,10 +17463,12 @@
       <c r="J219" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K219" s="8" t="n"/>
+      <c r="K219" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M219" s="8" t="n"/>
@@ -17097,10 +17533,12 @@
       <c r="J220" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K220" s="8" t="n"/>
+      <c r="K220" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L220" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M220" s="8" t="n"/>
@@ -17165,10 +17603,12 @@
       <c r="J221" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K221" s="8" t="n"/>
+      <c r="K221" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M221" s="8" t="n"/>
@@ -17233,10 +17673,12 @@
       <c r="J222" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K222" s="8" t="n"/>
+      <c r="K222" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L222" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M222" s="8" t="n"/>
@@ -17301,10 +17743,12 @@
       <c r="J223" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K223" s="8" t="n"/>
+      <c r="K223" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M223" s="8" t="n"/>
@@ -17369,10 +17813,12 @@
       <c r="J224" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K224" s="8" t="n"/>
+      <c r="K224" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L224" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M224" s="8" t="n"/>
@@ -17437,10 +17883,12 @@
       <c r="J225" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K225" s="8" t="n"/>
+      <c r="K225" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M225" s="8" t="n"/>
@@ -17505,10 +17953,12 @@
       <c r="J226" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K226" s="8" t="n"/>
+      <c r="K226" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L226" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M226" s="8" t="n"/>
@@ -17573,10 +18023,12 @@
       <c r="J227" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K227" s="8" t="n"/>
+      <c r="K227" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M227" s="8" t="n"/>
@@ -17641,10 +18093,12 @@
       <c r="J228" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K228" s="8" t="n"/>
+      <c r="K228" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L228" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M228" s="8" t="n"/>
@@ -17709,10 +18163,12 @@
       <c r="J229" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K229" s="8" t="n"/>
+      <c r="K229" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M229" s="8" t="n"/>
@@ -17777,10 +18233,12 @@
       <c r="J230" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K230" s="8" t="n"/>
+      <c r="K230" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L230" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M230" s="8" t="n"/>
@@ -17845,10 +18303,12 @@
       <c r="J231" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K231" s="8" t="n"/>
+      <c r="K231" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M231" s="8" t="n"/>
@@ -17913,10 +18373,12 @@
       <c r="J232" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K232" s="8" t="n"/>
+      <c r="K232" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L232" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M232" s="8" t="n"/>
@@ -17981,10 +18443,12 @@
       <c r="J233" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K233" s="8" t="n"/>
+      <c r="K233" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M233" s="8" t="n"/>
@@ -18049,10 +18513,12 @@
       <c r="J234" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K234" s="8" t="n"/>
+      <c r="K234" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L234" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M234" s="8" t="n"/>
@@ -18117,10 +18583,12 @@
       <c r="J235" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K235" s="8" t="n"/>
+      <c r="K235" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M235" s="8" t="n"/>
@@ -18185,10 +18653,12 @@
       <c r="J236" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K236" s="8" t="n"/>
+      <c r="K236" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L236" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M236" s="8" t="n"/>
@@ -18253,10 +18723,12 @@
       <c r="J237" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K237" s="8" t="n"/>
+      <c r="K237" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M237" s="8" t="n"/>
@@ -18321,10 +18793,12 @@
       <c r="J238" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K238" s="8" t="n"/>
+      <c r="K238" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L238" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M238" s="8" t="n"/>
@@ -18389,10 +18863,12 @@
       <c r="J239" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K239" s="8" t="n"/>
+      <c r="K239" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M239" s="8" t="n"/>
@@ -18457,10 +18933,12 @@
       <c r="J240" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K240" s="8" t="n"/>
+      <c r="K240" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L240" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M240" s="8" t="n"/>
@@ -18525,10 +19003,12 @@
       <c r="J241" s="8" t="n">
         <v>46310</v>
       </c>
-      <c r="K241" s="8" t="n"/>
+      <c r="K241" s="8" t="n">
+        <v>46303</v>
+      </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>미발송</t>
+          <t>발송(회신 대기)</t>
         </is>
       </c>
       <c r="M241" s="8" t="n"/>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용 안내" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'상세'!$A$1:$R$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'상세'!$A$1:$T$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,7 +48,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C65911"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,11 +112,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -123,6 +141,20 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00F8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -488,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -514,6 +546,8 @@
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,6 +680,16 @@
           <t>한 통 묶음 여부</t>
         </is>
       </c>
+      <c r="X4" s="15" t="inlineStr">
+        <is>
+          <t>임박(D-3 이내) 미회신</t>
+        </is>
+      </c>
+      <c r="Y4" s="15" t="inlineStr">
+        <is>
+          <t>기한까지 남은 일수(최소)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -746,6 +790,14 @@
           <t>보유 확인 합쳐 한 통</t>
         </is>
       </c>
+      <c r="X5" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y5" s="18">
+        <f>IF(N5=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -846,6 +898,14 @@
           <t>보유 확인 합쳐 한 통</t>
         </is>
       </c>
+      <c r="X6" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y6" s="18">
+        <f>IF(N6=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -946,6 +1006,14 @@
           <t>요청만</t>
         </is>
       </c>
+      <c r="X7" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y7" s="18">
+        <f>IF(N7=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1046,6 +1114,14 @@
           <t>보유 확인 합쳐 한 통</t>
         </is>
       </c>
+      <c r="X8" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="18">
+        <f>IF(N8=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1146,6 +1222,14 @@
           <t>요청만</t>
         </is>
       </c>
+      <c r="X9" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="18">
+        <f>IF(N9=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1246,6 +1330,14 @@
           <t>요청만</t>
         </is>
       </c>
+      <c r="X10" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="18">
+        <f>IF(N10=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1346,6 +1438,14 @@
           <t>요청만</t>
         </is>
       </c>
+      <c r="X11" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="18">
+        <f>IF(N11=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1446,6 +1546,14 @@
           <t>요청만</t>
         </is>
       </c>
+      <c r="X12" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="18">
+        <f>IF(N12=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1546,6 +1654,14 @@
           <t>요청만</t>
         </is>
       </c>
+      <c r="X13" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="18">
+        <f>IF(N13=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1646,6 +1762,14 @@
           <t>요청만</t>
         </is>
       </c>
+      <c r="X14" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="18">
+        <f>IF(N14=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1745,6 +1869,14 @@
         <is>
           <t>요청만</t>
         </is>
+      </c>
+      <c r="X15" s="18">
+        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="18">
+        <f>IF(N15=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1817,6 +1949,11 @@
       <c r="U16" s="9" t="inlineStr"/>
       <c r="V16" s="9" t="inlineStr"/>
       <c r="W16" s="9" t="inlineStr"/>
+      <c r="X16" s="19">
+        <f>SUM(X5:X15)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="18" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:W15">
@@ -1825,6 +1962,11 @@
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($C5&gt;0,$C5=$L5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:Y15">
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>AND($X5&gt;0,$O5=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2111,7 +2253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R241"/>
+  <dimension ref="A1:T241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2132,6 +2274,8 @@
     <col width="46" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2225,6 +2369,16 @@
           <t>메모</t>
         </is>
       </c>
+      <c r="S1" s="16" t="inlineStr">
+        <is>
+          <t>기한까지 남은 일수</t>
+        </is>
+      </c>
+      <c r="T1" s="16" t="inlineStr">
+        <is>
+          <t>기한 상태</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
@@ -2295,6 +2449,14 @@
         </is>
       </c>
       <c r="R2" s="7" t="n"/>
+      <c r="S2">
+        <f>IF(L2="회신 완료","",J2-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T2">
+        <f>IF(L2="회신 완료","완료",IF(J2&lt;TODAY(),"지연",IF(J2-TODAY()&lt;=1,"임박(D-1 이내)",IF(J2-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -2365,6 +2527,14 @@
         </is>
       </c>
       <c r="R3" s="7" t="n"/>
+      <c r="S3">
+        <f>IF(L3="회신 완료","",J3-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T3">
+        <f>IF(L3="회신 완료","완료",IF(J3&lt;TODAY(),"지연",IF(J3-TODAY()&lt;=1,"임박(D-1 이내)",IF(J3-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -2435,6 +2605,14 @@
         </is>
       </c>
       <c r="R4" s="7" t="n"/>
+      <c r="S4">
+        <f>IF(L4="회신 완료","",J4-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T4">
+        <f>IF(L4="회신 완료","완료",IF(J4&lt;TODAY(),"지연",IF(J4-TODAY()&lt;=1,"임박(D-1 이내)",IF(J4-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -2505,6 +2683,14 @@
         </is>
       </c>
       <c r="R5" s="7" t="n"/>
+      <c r="S5">
+        <f>IF(L5="회신 완료","",J5-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T5">
+        <f>IF(L5="회신 완료","완료",IF(J5&lt;TODAY(),"지연",IF(J5-TODAY()&lt;=1,"임박(D-1 이내)",IF(J5-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2575,6 +2761,14 @@
         </is>
       </c>
       <c r="R6" s="7" t="n"/>
+      <c r="S6">
+        <f>IF(L6="회신 완료","",J6-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T6">
+        <f>IF(L6="회신 완료","완료",IF(J6&lt;TODAY(),"지연",IF(J6-TODAY()&lt;=1,"임박(D-1 이내)",IF(J6-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -2645,6 +2839,14 @@
         </is>
       </c>
       <c r="R7" s="7" t="n"/>
+      <c r="S7">
+        <f>IF(L7="회신 완료","",J7-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T7">
+        <f>IF(L7="회신 완료","완료",IF(J7&lt;TODAY(),"지연",IF(J7-TODAY()&lt;=1,"임박(D-1 이내)",IF(J7-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -2715,6 +2917,14 @@
         </is>
       </c>
       <c r="R8" s="7" t="n"/>
+      <c r="S8">
+        <f>IF(L8="회신 완료","",J8-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T8">
+        <f>IF(L8="회신 완료","완료",IF(J8&lt;TODAY(),"지연",IF(J8-TODAY()&lt;=1,"임박(D-1 이내)",IF(J8-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -2785,6 +2995,14 @@
         </is>
       </c>
       <c r="R9" s="7" t="n"/>
+      <c r="S9">
+        <f>IF(L9="회신 완료","",J9-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T9">
+        <f>IF(L9="회신 완료","완료",IF(J9&lt;TODAY(),"지연",IF(J9-TODAY()&lt;=1,"임박(D-1 이내)",IF(J9-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2855,6 +3073,14 @@
         </is>
       </c>
       <c r="R10" s="7" t="n"/>
+      <c r="S10">
+        <f>IF(L10="회신 완료","",J10-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T10">
+        <f>IF(L10="회신 완료","완료",IF(J10&lt;TODAY(),"지연",IF(J10-TODAY()&lt;=1,"임박(D-1 이내)",IF(J10-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -2925,6 +3151,14 @@
         </is>
       </c>
       <c r="R11" s="7" t="n"/>
+      <c r="S11">
+        <f>IF(L11="회신 완료","",J11-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T11">
+        <f>IF(L11="회신 완료","완료",IF(J11&lt;TODAY(),"지연",IF(J11-TODAY()&lt;=1,"임박(D-1 이내)",IF(J11-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2995,6 +3229,14 @@
         </is>
       </c>
       <c r="R12" s="7" t="n"/>
+      <c r="S12">
+        <f>IF(L12="회신 완료","",J12-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T12">
+        <f>IF(L12="회신 완료","완료",IF(J12&lt;TODAY(),"지연",IF(J12-TODAY()&lt;=1,"임박(D-1 이내)",IF(J12-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -3065,6 +3307,14 @@
         </is>
       </c>
       <c r="R13" s="7" t="n"/>
+      <c r="S13">
+        <f>IF(L13="회신 완료","",J13-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T13">
+        <f>IF(L13="회신 완료","완료",IF(J13&lt;TODAY(),"지연",IF(J13-TODAY()&lt;=1,"임박(D-1 이내)",IF(J13-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -3135,6 +3385,14 @@
         </is>
       </c>
       <c r="R14" s="7" t="n"/>
+      <c r="S14">
+        <f>IF(L14="회신 완료","",J14-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T14">
+        <f>IF(L14="회신 완료","완료",IF(J14&lt;TODAY(),"지연",IF(J14-TODAY()&lt;=1,"임박(D-1 이내)",IF(J14-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -3205,6 +3463,14 @@
         </is>
       </c>
       <c r="R15" s="7" t="n"/>
+      <c r="S15">
+        <f>IF(L15="회신 완료","",J15-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T15">
+        <f>IF(L15="회신 완료","완료",IF(J15&lt;TODAY(),"지연",IF(J15-TODAY()&lt;=1,"임박(D-1 이내)",IF(J15-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -3275,6 +3541,14 @@
         </is>
       </c>
       <c r="R16" s="7" t="n"/>
+      <c r="S16">
+        <f>IF(L16="회신 완료","",J16-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T16">
+        <f>IF(L16="회신 완료","완료",IF(J16&lt;TODAY(),"지연",IF(J16-TODAY()&lt;=1,"임박(D-1 이내)",IF(J16-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -3345,6 +3619,14 @@
         </is>
       </c>
       <c r="R17" s="7" t="n"/>
+      <c r="S17">
+        <f>IF(L17="회신 완료","",J17-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T17">
+        <f>IF(L17="회신 완료","완료",IF(J17&lt;TODAY(),"지연",IF(J17-TODAY()&lt;=1,"임박(D-1 이내)",IF(J17-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3415,6 +3697,14 @@
         </is>
       </c>
       <c r="R18" s="7" t="n"/>
+      <c r="S18">
+        <f>IF(L18="회신 완료","",J18-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T18">
+        <f>IF(L18="회신 완료","완료",IF(J18&lt;TODAY(),"지연",IF(J18-TODAY()&lt;=1,"임박(D-1 이내)",IF(J18-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -3485,6 +3775,14 @@
         </is>
       </c>
       <c r="R19" s="7" t="n"/>
+      <c r="S19">
+        <f>IF(L19="회신 완료","",J19-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T19">
+        <f>IF(L19="회신 완료","완료",IF(J19&lt;TODAY(),"지연",IF(J19-TODAY()&lt;=1,"임박(D-1 이내)",IF(J19-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -3555,6 +3853,14 @@
         </is>
       </c>
       <c r="R20" s="7" t="n"/>
+      <c r="S20">
+        <f>IF(L20="회신 완료","",J20-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T20">
+        <f>IF(L20="회신 완료","완료",IF(J20&lt;TODAY(),"지연",IF(J20-TODAY()&lt;=1,"임박(D-1 이내)",IF(J20-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -3625,6 +3931,14 @@
         </is>
       </c>
       <c r="R21" s="7" t="n"/>
+      <c r="S21">
+        <f>IF(L21="회신 완료","",J21-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T21">
+        <f>IF(L21="회신 완료","완료",IF(J21&lt;TODAY(),"지연",IF(J21-TODAY()&lt;=1,"임박(D-1 이내)",IF(J21-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -3695,6 +4009,14 @@
         </is>
       </c>
       <c r="R22" s="7" t="n"/>
+      <c r="S22">
+        <f>IF(L22="회신 완료","",J22-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T22">
+        <f>IF(L22="회신 완료","완료",IF(J22&lt;TODAY(),"지연",IF(J22-TODAY()&lt;=1,"임박(D-1 이내)",IF(J22-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -3765,6 +4087,14 @@
         </is>
       </c>
       <c r="R23" s="7" t="n"/>
+      <c r="S23">
+        <f>IF(L23="회신 완료","",J23-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T23">
+        <f>IF(L23="회신 완료","완료",IF(J23&lt;TODAY(),"지연",IF(J23-TODAY()&lt;=1,"임박(D-1 이내)",IF(J23-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -3835,6 +4165,14 @@
         </is>
       </c>
       <c r="R24" s="7" t="n"/>
+      <c r="S24">
+        <f>IF(L24="회신 완료","",J24-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T24">
+        <f>IF(L24="회신 완료","완료",IF(J24&lt;TODAY(),"지연",IF(J24-TODAY()&lt;=1,"임박(D-1 이내)",IF(J24-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -3905,6 +4243,14 @@
         </is>
       </c>
       <c r="R25" s="7" t="n"/>
+      <c r="S25">
+        <f>IF(L25="회신 완료","",J25-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T25">
+        <f>IF(L25="회신 완료","완료",IF(J25&lt;TODAY(),"지연",IF(J25-TODAY()&lt;=1,"임박(D-1 이내)",IF(J25-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -3975,6 +4321,14 @@
         </is>
       </c>
       <c r="R26" s="7" t="n"/>
+      <c r="S26">
+        <f>IF(L26="회신 완료","",J26-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T26">
+        <f>IF(L26="회신 완료","완료",IF(J26&lt;TODAY(),"지연",IF(J26-TODAY()&lt;=1,"임박(D-1 이내)",IF(J26-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -4045,6 +4399,14 @@
         </is>
       </c>
       <c r="R27" s="7" t="n"/>
+      <c r="S27">
+        <f>IF(L27="회신 완료","",J27-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T27">
+        <f>IF(L27="회신 완료","완료",IF(J27&lt;TODAY(),"지연",IF(J27-TODAY()&lt;=1,"임박(D-1 이내)",IF(J27-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -4115,6 +4477,14 @@
         </is>
       </c>
       <c r="R28" s="7" t="n"/>
+      <c r="S28">
+        <f>IF(L28="회신 완료","",J28-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T28">
+        <f>IF(L28="회신 완료","완료",IF(J28&lt;TODAY(),"지연",IF(J28-TODAY()&lt;=1,"임박(D-1 이내)",IF(J28-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -4185,6 +4555,14 @@
         </is>
       </c>
       <c r="R29" s="7" t="n"/>
+      <c r="S29">
+        <f>IF(L29="회신 완료","",J29-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T29">
+        <f>IF(L29="회신 완료","완료",IF(J29&lt;TODAY(),"지연",IF(J29-TODAY()&lt;=1,"임박(D-1 이내)",IF(J29-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -4255,6 +4633,14 @@
         </is>
       </c>
       <c r="R30" s="7" t="n"/>
+      <c r="S30">
+        <f>IF(L30="회신 완료","",J30-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T30">
+        <f>IF(L30="회신 완료","완료",IF(J30&lt;TODAY(),"지연",IF(J30-TODAY()&lt;=1,"임박(D-1 이내)",IF(J30-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -4325,6 +4711,14 @@
         </is>
       </c>
       <c r="R31" s="7" t="n"/>
+      <c r="S31">
+        <f>IF(L31="회신 완료","",J31-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T31">
+        <f>IF(L31="회신 완료","완료",IF(J31&lt;TODAY(),"지연",IF(J31-TODAY()&lt;=1,"임박(D-1 이내)",IF(J31-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -4395,6 +4789,14 @@
         </is>
       </c>
       <c r="R32" s="7" t="n"/>
+      <c r="S32">
+        <f>IF(L32="회신 완료","",J32-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T32">
+        <f>IF(L32="회신 완료","완료",IF(J32&lt;TODAY(),"지연",IF(J32-TODAY()&lt;=1,"임박(D-1 이내)",IF(J32-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -4465,6 +4867,14 @@
         </is>
       </c>
       <c r="R33" s="7" t="n"/>
+      <c r="S33">
+        <f>IF(L33="회신 완료","",J33-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T33">
+        <f>IF(L33="회신 완료","완료",IF(J33&lt;TODAY(),"지연",IF(J33-TODAY()&lt;=1,"임박(D-1 이내)",IF(J33-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -4535,6 +4945,14 @@
         </is>
       </c>
       <c r="R34" s="7" t="n"/>
+      <c r="S34">
+        <f>IF(L34="회신 완료","",J34-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T34">
+        <f>IF(L34="회신 완료","완료",IF(J34&lt;TODAY(),"지연",IF(J34-TODAY()&lt;=1,"임박(D-1 이내)",IF(J34-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -4605,6 +5023,14 @@
         </is>
       </c>
       <c r="R35" s="7" t="n"/>
+      <c r="S35">
+        <f>IF(L35="회신 완료","",J35-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T35">
+        <f>IF(L35="회신 완료","완료",IF(J35&lt;TODAY(),"지연",IF(J35-TODAY()&lt;=1,"임박(D-1 이내)",IF(J35-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -4675,6 +5101,14 @@
         </is>
       </c>
       <c r="R36" s="7" t="n"/>
+      <c r="S36">
+        <f>IF(L36="회신 완료","",J36-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T36">
+        <f>IF(L36="회신 완료","완료",IF(J36&lt;TODAY(),"지연",IF(J36-TODAY()&lt;=1,"임박(D-1 이내)",IF(J36-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -4745,6 +5179,14 @@
         </is>
       </c>
       <c r="R37" s="7" t="n"/>
+      <c r="S37">
+        <f>IF(L37="회신 완료","",J37-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T37">
+        <f>IF(L37="회신 완료","완료",IF(J37&lt;TODAY(),"지연",IF(J37-TODAY()&lt;=1,"임박(D-1 이내)",IF(J37-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -4815,6 +5257,14 @@
         </is>
       </c>
       <c r="R38" s="7" t="n"/>
+      <c r="S38">
+        <f>IF(L38="회신 완료","",J38-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T38">
+        <f>IF(L38="회신 완료","완료",IF(J38&lt;TODAY(),"지연",IF(J38-TODAY()&lt;=1,"임박(D-1 이내)",IF(J38-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -4885,6 +5335,14 @@
         </is>
       </c>
       <c r="R39" s="7" t="n"/>
+      <c r="S39">
+        <f>IF(L39="회신 완료","",J39-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T39">
+        <f>IF(L39="회신 완료","완료",IF(J39&lt;TODAY(),"지연",IF(J39-TODAY()&lt;=1,"임박(D-1 이내)",IF(J39-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -4955,6 +5413,14 @@
         </is>
       </c>
       <c r="R40" s="7" t="n"/>
+      <c r="S40">
+        <f>IF(L40="회신 완료","",J40-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T40">
+        <f>IF(L40="회신 완료","완료",IF(J40&lt;TODAY(),"지연",IF(J40-TODAY()&lt;=1,"임박(D-1 이내)",IF(J40-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -5025,6 +5491,14 @@
         </is>
       </c>
       <c r="R41" s="7" t="n"/>
+      <c r="S41">
+        <f>IF(L41="회신 완료","",J41-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T41">
+        <f>IF(L41="회신 완료","완료",IF(J41&lt;TODAY(),"지연",IF(J41-TODAY()&lt;=1,"임박(D-1 이내)",IF(J41-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -5095,6 +5569,14 @@
         </is>
       </c>
       <c r="R42" s="7" t="n"/>
+      <c r="S42">
+        <f>IF(L42="회신 완료","",J42-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T42">
+        <f>IF(L42="회신 완료","완료",IF(J42&lt;TODAY(),"지연",IF(J42-TODAY()&lt;=1,"임박(D-1 이내)",IF(J42-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -5165,6 +5647,14 @@
         </is>
       </c>
       <c r="R43" s="7" t="n"/>
+      <c r="S43">
+        <f>IF(L43="회신 완료","",J43-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T43">
+        <f>IF(L43="회신 완료","완료",IF(J43&lt;TODAY(),"지연",IF(J43-TODAY()&lt;=1,"임박(D-1 이내)",IF(J43-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -5235,6 +5725,14 @@
         </is>
       </c>
       <c r="R44" s="7" t="n"/>
+      <c r="S44">
+        <f>IF(L44="회신 완료","",J44-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T44">
+        <f>IF(L44="회신 완료","완료",IF(J44&lt;TODAY(),"지연",IF(J44-TODAY()&lt;=1,"임박(D-1 이내)",IF(J44-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -5305,6 +5803,14 @@
         </is>
       </c>
       <c r="R45" s="7" t="n"/>
+      <c r="S45">
+        <f>IF(L45="회신 완료","",J45-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T45">
+        <f>IF(L45="회신 완료","완료",IF(J45&lt;TODAY(),"지연",IF(J45-TODAY()&lt;=1,"임박(D-1 이내)",IF(J45-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -5375,6 +5881,14 @@
         </is>
       </c>
       <c r="R46" s="7" t="n"/>
+      <c r="S46">
+        <f>IF(L46="회신 완료","",J46-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T46">
+        <f>IF(L46="회신 완료","완료",IF(J46&lt;TODAY(),"지연",IF(J46-TODAY()&lt;=1,"임박(D-1 이내)",IF(J46-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -5445,6 +5959,14 @@
         </is>
       </c>
       <c r="R47" s="7" t="n"/>
+      <c r="S47">
+        <f>IF(L47="회신 완료","",J47-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T47">
+        <f>IF(L47="회신 완료","완료",IF(J47&lt;TODAY(),"지연",IF(J47-TODAY()&lt;=1,"임박(D-1 이내)",IF(J47-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -5515,6 +6037,14 @@
         </is>
       </c>
       <c r="R48" s="7" t="n"/>
+      <c r="S48">
+        <f>IF(L48="회신 완료","",J48-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T48">
+        <f>IF(L48="회신 완료","완료",IF(J48&lt;TODAY(),"지연",IF(J48-TODAY()&lt;=1,"임박(D-1 이내)",IF(J48-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -5585,6 +6115,14 @@
         </is>
       </c>
       <c r="R49" s="7" t="n"/>
+      <c r="S49">
+        <f>IF(L49="회신 완료","",J49-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T49">
+        <f>IF(L49="회신 완료","완료",IF(J49&lt;TODAY(),"지연",IF(J49-TODAY()&lt;=1,"임박(D-1 이내)",IF(J49-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -5655,6 +6193,14 @@
         </is>
       </c>
       <c r="R50" s="7" t="n"/>
+      <c r="S50">
+        <f>IF(L50="회신 완료","",J50-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T50">
+        <f>IF(L50="회신 완료","완료",IF(J50&lt;TODAY(),"지연",IF(J50-TODAY()&lt;=1,"임박(D-1 이내)",IF(J50-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -5725,6 +6271,14 @@
         </is>
       </c>
       <c r="R51" s="7" t="n"/>
+      <c r="S51">
+        <f>IF(L51="회신 완료","",J51-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T51">
+        <f>IF(L51="회신 완료","완료",IF(J51&lt;TODAY(),"지연",IF(J51-TODAY()&lt;=1,"임박(D-1 이내)",IF(J51-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -5795,6 +6349,14 @@
         </is>
       </c>
       <c r="R52" s="7" t="n"/>
+      <c r="S52">
+        <f>IF(L52="회신 완료","",J52-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T52">
+        <f>IF(L52="회신 완료","완료",IF(J52&lt;TODAY(),"지연",IF(J52-TODAY()&lt;=1,"임박(D-1 이내)",IF(J52-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -5865,6 +6427,14 @@
         </is>
       </c>
       <c r="R53" s="7" t="n"/>
+      <c r="S53">
+        <f>IF(L53="회신 완료","",J53-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T53">
+        <f>IF(L53="회신 완료","완료",IF(J53&lt;TODAY(),"지연",IF(J53-TODAY()&lt;=1,"임박(D-1 이내)",IF(J53-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -5935,6 +6505,14 @@
         </is>
       </c>
       <c r="R54" s="7" t="n"/>
+      <c r="S54">
+        <f>IF(L54="회신 완료","",J54-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T54">
+        <f>IF(L54="회신 완료","완료",IF(J54&lt;TODAY(),"지연",IF(J54-TODAY()&lt;=1,"임박(D-1 이내)",IF(J54-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -6005,6 +6583,14 @@
         </is>
       </c>
       <c r="R55" s="7" t="n"/>
+      <c r="S55">
+        <f>IF(L55="회신 완료","",J55-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T55">
+        <f>IF(L55="회신 완료","완료",IF(J55&lt;TODAY(),"지연",IF(J55-TODAY()&lt;=1,"임박(D-1 이내)",IF(J55-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -6075,6 +6661,14 @@
         </is>
       </c>
       <c r="R56" s="7" t="n"/>
+      <c r="S56">
+        <f>IF(L56="회신 완료","",J56-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T56">
+        <f>IF(L56="회신 완료","완료",IF(J56&lt;TODAY(),"지연",IF(J56-TODAY()&lt;=1,"임박(D-1 이내)",IF(J56-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -6145,6 +6739,14 @@
         </is>
       </c>
       <c r="R57" s="7" t="n"/>
+      <c r="S57">
+        <f>IF(L57="회신 완료","",J57-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T57">
+        <f>IF(L57="회신 완료","완료",IF(J57&lt;TODAY(),"지연",IF(J57-TODAY()&lt;=1,"임박(D-1 이내)",IF(J57-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -6215,6 +6817,14 @@
         </is>
       </c>
       <c r="R58" s="7" t="n"/>
+      <c r="S58">
+        <f>IF(L58="회신 완료","",J58-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T58">
+        <f>IF(L58="회신 완료","완료",IF(J58&lt;TODAY(),"지연",IF(J58-TODAY()&lt;=1,"임박(D-1 이내)",IF(J58-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -6285,6 +6895,14 @@
         </is>
       </c>
       <c r="R59" s="7" t="n"/>
+      <c r="S59">
+        <f>IF(L59="회신 완료","",J59-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T59">
+        <f>IF(L59="회신 완료","완료",IF(J59&lt;TODAY(),"지연",IF(J59-TODAY()&lt;=1,"임박(D-1 이내)",IF(J59-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -6355,6 +6973,14 @@
         </is>
       </c>
       <c r="R60" s="7" t="n"/>
+      <c r="S60">
+        <f>IF(L60="회신 완료","",J60-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T60">
+        <f>IF(L60="회신 완료","완료",IF(J60&lt;TODAY(),"지연",IF(J60-TODAY()&lt;=1,"임박(D-1 이내)",IF(J60-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -6425,6 +7051,14 @@
         </is>
       </c>
       <c r="R61" s="7" t="n"/>
+      <c r="S61">
+        <f>IF(L61="회신 완료","",J61-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T61">
+        <f>IF(L61="회신 완료","완료",IF(J61&lt;TODAY(),"지연",IF(J61-TODAY()&lt;=1,"임박(D-1 이내)",IF(J61-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -6495,6 +7129,14 @@
         </is>
       </c>
       <c r="R62" s="7" t="n"/>
+      <c r="S62">
+        <f>IF(L62="회신 완료","",J62-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T62">
+        <f>IF(L62="회신 완료","완료",IF(J62&lt;TODAY(),"지연",IF(J62-TODAY()&lt;=1,"임박(D-1 이내)",IF(J62-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -6565,6 +7207,14 @@
         </is>
       </c>
       <c r="R63" s="7" t="n"/>
+      <c r="S63">
+        <f>IF(L63="회신 완료","",J63-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T63">
+        <f>IF(L63="회신 완료","완료",IF(J63&lt;TODAY(),"지연",IF(J63-TODAY()&lt;=1,"임박(D-1 이내)",IF(J63-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -6635,6 +7285,14 @@
         </is>
       </c>
       <c r="R64" s="7" t="n"/>
+      <c r="S64">
+        <f>IF(L64="회신 완료","",J64-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T64">
+        <f>IF(L64="회신 완료","완료",IF(J64&lt;TODAY(),"지연",IF(J64-TODAY()&lt;=1,"임박(D-1 이내)",IF(J64-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -6705,6 +7363,14 @@
         </is>
       </c>
       <c r="R65" s="7" t="n"/>
+      <c r="S65">
+        <f>IF(L65="회신 완료","",J65-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T65">
+        <f>IF(L65="회신 완료","완료",IF(J65&lt;TODAY(),"지연",IF(J65-TODAY()&lt;=1,"임박(D-1 이내)",IF(J65-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -6775,6 +7441,14 @@
         </is>
       </c>
       <c r="R66" s="7" t="n"/>
+      <c r="S66">
+        <f>IF(L66="회신 완료","",J66-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T66">
+        <f>IF(L66="회신 완료","완료",IF(J66&lt;TODAY(),"지연",IF(J66-TODAY()&lt;=1,"임박(D-1 이내)",IF(J66-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -6845,6 +7519,14 @@
         </is>
       </c>
       <c r="R67" s="7" t="n"/>
+      <c r="S67">
+        <f>IF(L67="회신 완료","",J67-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T67">
+        <f>IF(L67="회신 완료","완료",IF(J67&lt;TODAY(),"지연",IF(J67-TODAY()&lt;=1,"임박(D-1 이내)",IF(J67-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -6915,6 +7597,14 @@
         </is>
       </c>
       <c r="R68" s="7" t="n"/>
+      <c r="S68">
+        <f>IF(L68="회신 완료","",J68-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T68">
+        <f>IF(L68="회신 완료","완료",IF(J68&lt;TODAY(),"지연",IF(J68-TODAY()&lt;=1,"임박(D-1 이내)",IF(J68-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -6985,6 +7675,14 @@
         </is>
       </c>
       <c r="R69" s="7" t="n"/>
+      <c r="S69">
+        <f>IF(L69="회신 완료","",J69-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T69">
+        <f>IF(L69="회신 완료","완료",IF(J69&lt;TODAY(),"지연",IF(J69-TODAY()&lt;=1,"임박(D-1 이내)",IF(J69-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -7055,6 +7753,14 @@
         </is>
       </c>
       <c r="R70" s="7" t="n"/>
+      <c r="S70">
+        <f>IF(L70="회신 완료","",J70-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T70">
+        <f>IF(L70="회신 완료","완료",IF(J70&lt;TODAY(),"지연",IF(J70-TODAY()&lt;=1,"임박(D-1 이내)",IF(J70-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -7125,6 +7831,14 @@
         </is>
       </c>
       <c r="R71" s="7" t="n"/>
+      <c r="S71">
+        <f>IF(L71="회신 완료","",J71-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T71">
+        <f>IF(L71="회신 완료","완료",IF(J71&lt;TODAY(),"지연",IF(J71-TODAY()&lt;=1,"임박(D-1 이내)",IF(J71-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -7195,6 +7909,14 @@
         </is>
       </c>
       <c r="R72" s="7" t="n"/>
+      <c r="S72">
+        <f>IF(L72="회신 완료","",J72-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T72">
+        <f>IF(L72="회신 완료","완료",IF(J72&lt;TODAY(),"지연",IF(J72-TODAY()&lt;=1,"임박(D-1 이내)",IF(J72-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -7265,6 +7987,14 @@
         </is>
       </c>
       <c r="R73" s="7" t="n"/>
+      <c r="S73">
+        <f>IF(L73="회신 완료","",J73-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T73">
+        <f>IF(L73="회신 완료","완료",IF(J73&lt;TODAY(),"지연",IF(J73-TODAY()&lt;=1,"임박(D-1 이내)",IF(J73-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -7335,6 +8065,14 @@
         </is>
       </c>
       <c r="R74" s="7" t="n"/>
+      <c r="S74">
+        <f>IF(L74="회신 완료","",J74-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T74">
+        <f>IF(L74="회신 완료","완료",IF(J74&lt;TODAY(),"지연",IF(J74-TODAY()&lt;=1,"임박(D-1 이내)",IF(J74-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -7405,6 +8143,14 @@
         </is>
       </c>
       <c r="R75" s="7" t="n"/>
+      <c r="S75">
+        <f>IF(L75="회신 완료","",J75-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T75">
+        <f>IF(L75="회신 완료","완료",IF(J75&lt;TODAY(),"지연",IF(J75-TODAY()&lt;=1,"임박(D-1 이내)",IF(J75-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -7475,6 +8221,14 @@
         </is>
       </c>
       <c r="R76" s="7" t="n"/>
+      <c r="S76">
+        <f>IF(L76="회신 완료","",J76-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T76">
+        <f>IF(L76="회신 완료","완료",IF(J76&lt;TODAY(),"지연",IF(J76-TODAY()&lt;=1,"임박(D-1 이내)",IF(J76-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -7545,6 +8299,14 @@
         </is>
       </c>
       <c r="R77" s="7" t="n"/>
+      <c r="S77">
+        <f>IF(L77="회신 완료","",J77-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T77">
+        <f>IF(L77="회신 완료","완료",IF(J77&lt;TODAY(),"지연",IF(J77-TODAY()&lt;=1,"임박(D-1 이내)",IF(J77-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -7615,6 +8377,14 @@
         </is>
       </c>
       <c r="R78" s="7" t="n"/>
+      <c r="S78">
+        <f>IF(L78="회신 완료","",J78-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T78">
+        <f>IF(L78="회신 완료","완료",IF(J78&lt;TODAY(),"지연",IF(J78-TODAY()&lt;=1,"임박(D-1 이내)",IF(J78-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -7685,6 +8455,14 @@
         </is>
       </c>
       <c r="R79" s="7" t="n"/>
+      <c r="S79">
+        <f>IF(L79="회신 완료","",J79-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T79">
+        <f>IF(L79="회신 완료","완료",IF(J79&lt;TODAY(),"지연",IF(J79-TODAY()&lt;=1,"임박(D-1 이내)",IF(J79-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -7755,6 +8533,14 @@
         </is>
       </c>
       <c r="R80" s="7" t="n"/>
+      <c r="S80">
+        <f>IF(L80="회신 완료","",J80-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T80">
+        <f>IF(L80="회신 완료","완료",IF(J80&lt;TODAY(),"지연",IF(J80-TODAY()&lt;=1,"임박(D-1 이내)",IF(J80-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -7825,6 +8611,14 @@
         </is>
       </c>
       <c r="R81" s="7" t="n"/>
+      <c r="S81">
+        <f>IF(L81="회신 완료","",J81-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T81">
+        <f>IF(L81="회신 완료","완료",IF(J81&lt;TODAY(),"지연",IF(J81-TODAY()&lt;=1,"임박(D-1 이내)",IF(J81-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -7895,6 +8689,14 @@
         </is>
       </c>
       <c r="R82" s="7" t="n"/>
+      <c r="S82">
+        <f>IF(L82="회신 완료","",J82-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T82">
+        <f>IF(L82="회신 완료","완료",IF(J82&lt;TODAY(),"지연",IF(J82-TODAY()&lt;=1,"임박(D-1 이내)",IF(J82-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -7965,6 +8767,14 @@
         </is>
       </c>
       <c r="R83" s="7" t="n"/>
+      <c r="S83">
+        <f>IF(L83="회신 완료","",J83-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T83">
+        <f>IF(L83="회신 완료","완료",IF(J83&lt;TODAY(),"지연",IF(J83-TODAY()&lt;=1,"임박(D-1 이내)",IF(J83-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -8035,6 +8845,14 @@
         </is>
       </c>
       <c r="R84" s="7" t="n"/>
+      <c r="S84">
+        <f>IF(L84="회신 완료","",J84-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T84">
+        <f>IF(L84="회신 완료","완료",IF(J84&lt;TODAY(),"지연",IF(J84-TODAY()&lt;=1,"임박(D-1 이내)",IF(J84-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -8105,6 +8923,14 @@
         </is>
       </c>
       <c r="R85" s="7" t="n"/>
+      <c r="S85">
+        <f>IF(L85="회신 완료","",J85-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T85">
+        <f>IF(L85="회신 완료","완료",IF(J85&lt;TODAY(),"지연",IF(J85-TODAY()&lt;=1,"임박(D-1 이내)",IF(J85-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -8175,6 +9001,14 @@
         </is>
       </c>
       <c r="R86" s="7" t="n"/>
+      <c r="S86">
+        <f>IF(L86="회신 완료","",J86-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T86">
+        <f>IF(L86="회신 완료","완료",IF(J86&lt;TODAY(),"지연",IF(J86-TODAY()&lt;=1,"임박(D-1 이내)",IF(J86-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -8245,6 +9079,14 @@
         </is>
       </c>
       <c r="R87" s="7" t="n"/>
+      <c r="S87">
+        <f>IF(L87="회신 완료","",J87-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T87">
+        <f>IF(L87="회신 완료","완료",IF(J87&lt;TODAY(),"지연",IF(J87-TODAY()&lt;=1,"임박(D-1 이내)",IF(J87-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -8315,6 +9157,14 @@
         </is>
       </c>
       <c r="R88" s="7" t="n"/>
+      <c r="S88">
+        <f>IF(L88="회신 완료","",J88-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T88">
+        <f>IF(L88="회신 완료","완료",IF(J88&lt;TODAY(),"지연",IF(J88-TODAY()&lt;=1,"임박(D-1 이내)",IF(J88-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -8385,6 +9235,14 @@
         </is>
       </c>
       <c r="R89" s="7" t="n"/>
+      <c r="S89">
+        <f>IF(L89="회신 완료","",J89-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T89">
+        <f>IF(L89="회신 완료","완료",IF(J89&lt;TODAY(),"지연",IF(J89-TODAY()&lt;=1,"임박(D-1 이내)",IF(J89-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -8455,6 +9313,14 @@
         </is>
       </c>
       <c r="R90" s="7" t="n"/>
+      <c r="S90">
+        <f>IF(L90="회신 완료","",J90-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T90">
+        <f>IF(L90="회신 완료","완료",IF(J90&lt;TODAY(),"지연",IF(J90-TODAY()&lt;=1,"임박(D-1 이내)",IF(J90-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -8525,6 +9391,14 @@
         </is>
       </c>
       <c r="R91" s="7" t="n"/>
+      <c r="S91">
+        <f>IF(L91="회신 완료","",J91-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T91">
+        <f>IF(L91="회신 완료","완료",IF(J91&lt;TODAY(),"지연",IF(J91-TODAY()&lt;=1,"임박(D-1 이내)",IF(J91-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -8595,6 +9469,14 @@
         </is>
       </c>
       <c r="R92" s="7" t="n"/>
+      <c r="S92">
+        <f>IF(L92="회신 완료","",J92-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T92">
+        <f>IF(L92="회신 완료","완료",IF(J92&lt;TODAY(),"지연",IF(J92-TODAY()&lt;=1,"임박(D-1 이내)",IF(J92-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -8665,6 +9547,14 @@
         </is>
       </c>
       <c r="R93" s="7" t="n"/>
+      <c r="S93">
+        <f>IF(L93="회신 완료","",J93-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T93">
+        <f>IF(L93="회신 완료","완료",IF(J93&lt;TODAY(),"지연",IF(J93-TODAY()&lt;=1,"임박(D-1 이내)",IF(J93-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -8735,6 +9625,14 @@
         </is>
       </c>
       <c r="R94" s="7" t="n"/>
+      <c r="S94">
+        <f>IF(L94="회신 완료","",J94-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T94">
+        <f>IF(L94="회신 완료","완료",IF(J94&lt;TODAY(),"지연",IF(J94-TODAY()&lt;=1,"임박(D-1 이내)",IF(J94-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -8805,6 +9703,14 @@
         </is>
       </c>
       <c r="R95" s="7" t="n"/>
+      <c r="S95">
+        <f>IF(L95="회신 완료","",J95-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T95">
+        <f>IF(L95="회신 완료","완료",IF(J95&lt;TODAY(),"지연",IF(J95-TODAY()&lt;=1,"임박(D-1 이내)",IF(J95-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -8875,6 +9781,14 @@
         </is>
       </c>
       <c r="R96" s="7" t="n"/>
+      <c r="S96">
+        <f>IF(L96="회신 완료","",J96-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T96">
+        <f>IF(L96="회신 완료","완료",IF(J96&lt;TODAY(),"지연",IF(J96-TODAY()&lt;=1,"임박(D-1 이내)",IF(J96-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -8945,6 +9859,14 @@
         </is>
       </c>
       <c r="R97" s="7" t="n"/>
+      <c r="S97">
+        <f>IF(L97="회신 완료","",J97-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T97">
+        <f>IF(L97="회신 완료","완료",IF(J97&lt;TODAY(),"지연",IF(J97-TODAY()&lt;=1,"임박(D-1 이내)",IF(J97-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -9015,6 +9937,14 @@
         </is>
       </c>
       <c r="R98" s="7" t="n"/>
+      <c r="S98">
+        <f>IF(L98="회신 완료","",J98-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T98">
+        <f>IF(L98="회신 완료","완료",IF(J98&lt;TODAY(),"지연",IF(J98-TODAY()&lt;=1,"임박(D-1 이내)",IF(J98-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -9085,6 +10015,14 @@
         </is>
       </c>
       <c r="R99" s="7" t="n"/>
+      <c r="S99">
+        <f>IF(L99="회신 완료","",J99-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T99">
+        <f>IF(L99="회신 완료","완료",IF(J99&lt;TODAY(),"지연",IF(J99-TODAY()&lt;=1,"임박(D-1 이내)",IF(J99-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -9155,6 +10093,14 @@
         </is>
       </c>
       <c r="R100" s="7" t="n"/>
+      <c r="S100">
+        <f>IF(L100="회신 완료","",J100-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T100">
+        <f>IF(L100="회신 완료","완료",IF(J100&lt;TODAY(),"지연",IF(J100-TODAY()&lt;=1,"임박(D-1 이내)",IF(J100-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -9225,6 +10171,14 @@
         </is>
       </c>
       <c r="R101" s="7" t="n"/>
+      <c r="S101">
+        <f>IF(L101="회신 완료","",J101-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T101">
+        <f>IF(L101="회신 완료","완료",IF(J101&lt;TODAY(),"지연",IF(J101-TODAY()&lt;=1,"임박(D-1 이내)",IF(J101-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -9295,6 +10249,14 @@
         </is>
       </c>
       <c r="R102" s="7" t="n"/>
+      <c r="S102">
+        <f>IF(L102="회신 완료","",J102-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T102">
+        <f>IF(L102="회신 완료","완료",IF(J102&lt;TODAY(),"지연",IF(J102-TODAY()&lt;=1,"임박(D-1 이내)",IF(J102-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -9365,6 +10327,14 @@
         </is>
       </c>
       <c r="R103" s="7" t="n"/>
+      <c r="S103">
+        <f>IF(L103="회신 완료","",J103-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T103">
+        <f>IF(L103="회신 완료","완료",IF(J103&lt;TODAY(),"지연",IF(J103-TODAY()&lt;=1,"임박(D-1 이내)",IF(J103-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -9435,6 +10405,14 @@
         </is>
       </c>
       <c r="R104" s="7" t="n"/>
+      <c r="S104">
+        <f>IF(L104="회신 완료","",J104-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T104">
+        <f>IF(L104="회신 완료","완료",IF(J104&lt;TODAY(),"지연",IF(J104-TODAY()&lt;=1,"임박(D-1 이내)",IF(J104-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -9505,6 +10483,14 @@
         </is>
       </c>
       <c r="R105" s="7" t="n"/>
+      <c r="S105">
+        <f>IF(L105="회신 완료","",J105-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T105">
+        <f>IF(L105="회신 완료","완료",IF(J105&lt;TODAY(),"지연",IF(J105-TODAY()&lt;=1,"임박(D-1 이내)",IF(J105-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -9575,6 +10561,14 @@
         </is>
       </c>
       <c r="R106" s="7" t="n"/>
+      <c r="S106">
+        <f>IF(L106="회신 완료","",J106-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T106">
+        <f>IF(L106="회신 완료","완료",IF(J106&lt;TODAY(),"지연",IF(J106-TODAY()&lt;=1,"임박(D-1 이내)",IF(J106-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -9645,6 +10639,14 @@
         </is>
       </c>
       <c r="R107" s="7" t="n"/>
+      <c r="S107">
+        <f>IF(L107="회신 완료","",J107-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T107">
+        <f>IF(L107="회신 완료","완료",IF(J107&lt;TODAY(),"지연",IF(J107-TODAY()&lt;=1,"임박(D-1 이내)",IF(J107-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -9715,6 +10717,14 @@
         </is>
       </c>
       <c r="R108" s="7" t="n"/>
+      <c r="S108">
+        <f>IF(L108="회신 완료","",J108-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T108">
+        <f>IF(L108="회신 완료","완료",IF(J108&lt;TODAY(),"지연",IF(J108-TODAY()&lt;=1,"임박(D-1 이내)",IF(J108-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -9785,6 +10795,14 @@
         </is>
       </c>
       <c r="R109" s="7" t="n"/>
+      <c r="S109">
+        <f>IF(L109="회신 완료","",J109-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T109">
+        <f>IF(L109="회신 완료","완료",IF(J109&lt;TODAY(),"지연",IF(J109-TODAY()&lt;=1,"임박(D-1 이내)",IF(J109-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -9855,6 +10873,14 @@
         </is>
       </c>
       <c r="R110" s="7" t="n"/>
+      <c r="S110">
+        <f>IF(L110="회신 완료","",J110-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T110">
+        <f>IF(L110="회신 완료","완료",IF(J110&lt;TODAY(),"지연",IF(J110-TODAY()&lt;=1,"임박(D-1 이내)",IF(J110-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -9925,6 +10951,14 @@
         </is>
       </c>
       <c r="R111" s="7" t="n"/>
+      <c r="S111">
+        <f>IF(L111="회신 완료","",J111-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T111">
+        <f>IF(L111="회신 완료","완료",IF(J111&lt;TODAY(),"지연",IF(J111-TODAY()&lt;=1,"임박(D-1 이내)",IF(J111-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -9995,6 +11029,14 @@
         </is>
       </c>
       <c r="R112" s="7" t="n"/>
+      <c r="S112">
+        <f>IF(L112="회신 완료","",J112-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T112">
+        <f>IF(L112="회신 완료","완료",IF(J112&lt;TODAY(),"지연",IF(J112-TODAY()&lt;=1,"임박(D-1 이내)",IF(J112-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -10065,6 +11107,14 @@
         </is>
       </c>
       <c r="R113" s="7" t="n"/>
+      <c r="S113">
+        <f>IF(L113="회신 완료","",J113-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T113">
+        <f>IF(L113="회신 완료","완료",IF(J113&lt;TODAY(),"지연",IF(J113-TODAY()&lt;=1,"임박(D-1 이내)",IF(J113-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
@@ -10135,6 +11185,14 @@
         </is>
       </c>
       <c r="R114" s="7" t="n"/>
+      <c r="S114">
+        <f>IF(L114="회신 완료","",J114-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T114">
+        <f>IF(L114="회신 완료","완료",IF(J114&lt;TODAY(),"지연",IF(J114-TODAY()&lt;=1,"임박(D-1 이내)",IF(J114-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n">
@@ -10205,6 +11263,14 @@
         </is>
       </c>
       <c r="R115" s="7" t="n"/>
+      <c r="S115">
+        <f>IF(L115="회신 완료","",J115-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T115">
+        <f>IF(L115="회신 완료","완료",IF(J115&lt;TODAY(),"지연",IF(J115-TODAY()&lt;=1,"임박(D-1 이내)",IF(J115-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
@@ -10275,6 +11341,14 @@
         </is>
       </c>
       <c r="R116" s="7" t="n"/>
+      <c r="S116">
+        <f>IF(L116="회신 완료","",J116-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T116">
+        <f>IF(L116="회신 완료","완료",IF(J116&lt;TODAY(),"지연",IF(J116-TODAY()&lt;=1,"임박(D-1 이내)",IF(J116-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n">
@@ -10345,6 +11419,14 @@
         </is>
       </c>
       <c r="R117" s="7" t="n"/>
+      <c r="S117">
+        <f>IF(L117="회신 완료","",J117-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T117">
+        <f>IF(L117="회신 완료","완료",IF(J117&lt;TODAY(),"지연",IF(J117-TODAY()&lt;=1,"임박(D-1 이내)",IF(J117-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
@@ -10415,6 +11497,14 @@
         </is>
       </c>
       <c r="R118" s="7" t="n"/>
+      <c r="S118">
+        <f>IF(L118="회신 완료","",J118-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T118">
+        <f>IF(L118="회신 완료","완료",IF(J118&lt;TODAY(),"지연",IF(J118-TODAY()&lt;=1,"임박(D-1 이내)",IF(J118-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n">
@@ -10485,6 +11575,14 @@
         </is>
       </c>
       <c r="R119" s="7" t="n"/>
+      <c r="S119">
+        <f>IF(L119="회신 완료","",J119-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T119">
+        <f>IF(L119="회신 완료","완료",IF(J119&lt;TODAY(),"지연",IF(J119-TODAY()&lt;=1,"임박(D-1 이내)",IF(J119-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
@@ -10555,6 +11653,14 @@
         </is>
       </c>
       <c r="R120" s="7" t="n"/>
+      <c r="S120">
+        <f>IF(L120="회신 완료","",J120-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T120">
+        <f>IF(L120="회신 완료","완료",IF(J120&lt;TODAY(),"지연",IF(J120-TODAY()&lt;=1,"임박(D-1 이내)",IF(J120-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n">
@@ -10625,6 +11731,14 @@
         </is>
       </c>
       <c r="R121" s="7" t="n"/>
+      <c r="S121">
+        <f>IF(L121="회신 완료","",J121-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T121">
+        <f>IF(L121="회신 완료","완료",IF(J121&lt;TODAY(),"지연",IF(J121-TODAY()&lt;=1,"임박(D-1 이내)",IF(J121-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
@@ -10695,6 +11809,14 @@
         </is>
       </c>
       <c r="R122" s="7" t="n"/>
+      <c r="S122">
+        <f>IF(L122="회신 완료","",J122-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T122">
+        <f>IF(L122="회신 완료","완료",IF(J122&lt;TODAY(),"지연",IF(J122-TODAY()&lt;=1,"임박(D-1 이내)",IF(J122-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n">
@@ -10765,6 +11887,14 @@
         </is>
       </c>
       <c r="R123" s="7" t="n"/>
+      <c r="S123">
+        <f>IF(L123="회신 완료","",J123-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T123">
+        <f>IF(L123="회신 완료","완료",IF(J123&lt;TODAY(),"지연",IF(J123-TODAY()&lt;=1,"임박(D-1 이내)",IF(J123-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
@@ -10835,6 +11965,14 @@
         </is>
       </c>
       <c r="R124" s="7" t="n"/>
+      <c r="S124">
+        <f>IF(L124="회신 완료","",J124-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T124">
+        <f>IF(L124="회신 완료","완료",IF(J124&lt;TODAY(),"지연",IF(J124-TODAY()&lt;=1,"임박(D-1 이내)",IF(J124-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n">
@@ -10905,6 +12043,14 @@
         </is>
       </c>
       <c r="R125" s="7" t="n"/>
+      <c r="S125">
+        <f>IF(L125="회신 완료","",J125-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T125">
+        <f>IF(L125="회신 완료","완료",IF(J125&lt;TODAY(),"지연",IF(J125-TODAY()&lt;=1,"임박(D-1 이내)",IF(J125-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
@@ -10975,6 +12121,14 @@
         </is>
       </c>
       <c r="R126" s="7" t="n"/>
+      <c r="S126">
+        <f>IF(L126="회신 완료","",J126-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T126">
+        <f>IF(L126="회신 완료","완료",IF(J126&lt;TODAY(),"지연",IF(J126-TODAY()&lt;=1,"임박(D-1 이내)",IF(J126-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n">
@@ -11045,6 +12199,14 @@
         </is>
       </c>
       <c r="R127" s="7" t="n"/>
+      <c r="S127">
+        <f>IF(L127="회신 완료","",J127-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T127">
+        <f>IF(L127="회신 완료","완료",IF(J127&lt;TODAY(),"지연",IF(J127-TODAY()&lt;=1,"임박(D-1 이내)",IF(J127-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
@@ -11115,6 +12277,14 @@
         </is>
       </c>
       <c r="R128" s="7" t="n"/>
+      <c r="S128">
+        <f>IF(L128="회신 완료","",J128-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T128">
+        <f>IF(L128="회신 완료","완료",IF(J128&lt;TODAY(),"지연",IF(J128-TODAY()&lt;=1,"임박(D-1 이내)",IF(J128-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n">
@@ -11185,6 +12355,14 @@
         </is>
       </c>
       <c r="R129" s="7" t="n"/>
+      <c r="S129">
+        <f>IF(L129="회신 완료","",J129-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T129">
+        <f>IF(L129="회신 완료","완료",IF(J129&lt;TODAY(),"지연",IF(J129-TODAY()&lt;=1,"임박(D-1 이내)",IF(J129-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
@@ -11255,6 +12433,14 @@
         </is>
       </c>
       <c r="R130" s="7" t="n"/>
+      <c r="S130">
+        <f>IF(L130="회신 완료","",J130-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T130">
+        <f>IF(L130="회신 완료","완료",IF(J130&lt;TODAY(),"지연",IF(J130-TODAY()&lt;=1,"임박(D-1 이내)",IF(J130-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n">
@@ -11325,6 +12511,14 @@
         </is>
       </c>
       <c r="R131" s="7" t="n"/>
+      <c r="S131">
+        <f>IF(L131="회신 완료","",J131-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T131">
+        <f>IF(L131="회신 완료","완료",IF(J131&lt;TODAY(),"지연",IF(J131-TODAY()&lt;=1,"임박(D-1 이내)",IF(J131-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
@@ -11395,6 +12589,14 @@
         </is>
       </c>
       <c r="R132" s="7" t="n"/>
+      <c r="S132">
+        <f>IF(L132="회신 완료","",J132-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T132">
+        <f>IF(L132="회신 완료","완료",IF(J132&lt;TODAY(),"지연",IF(J132-TODAY()&lt;=1,"임박(D-1 이내)",IF(J132-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n">
@@ -11465,6 +12667,14 @@
         </is>
       </c>
       <c r="R133" s="7" t="n"/>
+      <c r="S133">
+        <f>IF(L133="회신 완료","",J133-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T133">
+        <f>IF(L133="회신 완료","완료",IF(J133&lt;TODAY(),"지연",IF(J133-TODAY()&lt;=1,"임박(D-1 이내)",IF(J133-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
@@ -11535,6 +12745,14 @@
         </is>
       </c>
       <c r="R134" s="7" t="n"/>
+      <c r="S134">
+        <f>IF(L134="회신 완료","",J134-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T134">
+        <f>IF(L134="회신 완료","완료",IF(J134&lt;TODAY(),"지연",IF(J134-TODAY()&lt;=1,"임박(D-1 이내)",IF(J134-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n">
@@ -11605,6 +12823,14 @@
         </is>
       </c>
       <c r="R135" s="7" t="n"/>
+      <c r="S135">
+        <f>IF(L135="회신 완료","",J135-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T135">
+        <f>IF(L135="회신 완료","완료",IF(J135&lt;TODAY(),"지연",IF(J135-TODAY()&lt;=1,"임박(D-1 이내)",IF(J135-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
@@ -11675,6 +12901,14 @@
         </is>
       </c>
       <c r="R136" s="7" t="n"/>
+      <c r="S136">
+        <f>IF(L136="회신 완료","",J136-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T136">
+        <f>IF(L136="회신 완료","완료",IF(J136&lt;TODAY(),"지연",IF(J136-TODAY()&lt;=1,"임박(D-1 이내)",IF(J136-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n">
@@ -11745,6 +12979,14 @@
         </is>
       </c>
       <c r="R137" s="7" t="n"/>
+      <c r="S137">
+        <f>IF(L137="회신 완료","",J137-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T137">
+        <f>IF(L137="회신 완료","완료",IF(J137&lt;TODAY(),"지연",IF(J137-TODAY()&lt;=1,"임박(D-1 이내)",IF(J137-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
@@ -11815,6 +13057,14 @@
         </is>
       </c>
       <c r="R138" s="7" t="n"/>
+      <c r="S138">
+        <f>IF(L138="회신 완료","",J138-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T138">
+        <f>IF(L138="회신 완료","완료",IF(J138&lt;TODAY(),"지연",IF(J138-TODAY()&lt;=1,"임박(D-1 이내)",IF(J138-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n">
@@ -11885,6 +13135,14 @@
         </is>
       </c>
       <c r="R139" s="7" t="n"/>
+      <c r="S139">
+        <f>IF(L139="회신 완료","",J139-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T139">
+        <f>IF(L139="회신 완료","완료",IF(J139&lt;TODAY(),"지연",IF(J139-TODAY()&lt;=1,"임박(D-1 이내)",IF(J139-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
@@ -11955,6 +13213,14 @@
         </is>
       </c>
       <c r="R140" s="7" t="n"/>
+      <c r="S140">
+        <f>IF(L140="회신 완료","",J140-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T140">
+        <f>IF(L140="회신 완료","완료",IF(J140&lt;TODAY(),"지연",IF(J140-TODAY()&lt;=1,"임박(D-1 이내)",IF(J140-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n">
@@ -12025,6 +13291,14 @@
         </is>
       </c>
       <c r="R141" s="7" t="n"/>
+      <c r="S141">
+        <f>IF(L141="회신 완료","",J141-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T141">
+        <f>IF(L141="회신 완료","완료",IF(J141&lt;TODAY(),"지연",IF(J141-TODAY()&lt;=1,"임박(D-1 이내)",IF(J141-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
@@ -12095,6 +13369,14 @@
         </is>
       </c>
       <c r="R142" s="7" t="n"/>
+      <c r="S142">
+        <f>IF(L142="회신 완료","",J142-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T142">
+        <f>IF(L142="회신 완료","완료",IF(J142&lt;TODAY(),"지연",IF(J142-TODAY()&lt;=1,"임박(D-1 이내)",IF(J142-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n">
@@ -12165,6 +13447,14 @@
         </is>
       </c>
       <c r="R143" s="7" t="n"/>
+      <c r="S143">
+        <f>IF(L143="회신 완료","",J143-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T143">
+        <f>IF(L143="회신 완료","완료",IF(J143&lt;TODAY(),"지연",IF(J143-TODAY()&lt;=1,"임박(D-1 이내)",IF(J143-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
@@ -12235,6 +13525,14 @@
         </is>
       </c>
       <c r="R144" s="7" t="n"/>
+      <c r="S144">
+        <f>IF(L144="회신 완료","",J144-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T144">
+        <f>IF(L144="회신 완료","완료",IF(J144&lt;TODAY(),"지연",IF(J144-TODAY()&lt;=1,"임박(D-1 이내)",IF(J144-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n">
@@ -12305,6 +13603,14 @@
         </is>
       </c>
       <c r="R145" s="7" t="n"/>
+      <c r="S145">
+        <f>IF(L145="회신 완료","",J145-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T145">
+        <f>IF(L145="회신 완료","완료",IF(J145&lt;TODAY(),"지연",IF(J145-TODAY()&lt;=1,"임박(D-1 이내)",IF(J145-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
@@ -12375,6 +13681,14 @@
         </is>
       </c>
       <c r="R146" s="7" t="n"/>
+      <c r="S146">
+        <f>IF(L146="회신 완료","",J146-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T146">
+        <f>IF(L146="회신 완료","완료",IF(J146&lt;TODAY(),"지연",IF(J146-TODAY()&lt;=1,"임박(D-1 이내)",IF(J146-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n">
@@ -12445,6 +13759,14 @@
         </is>
       </c>
       <c r="R147" s="7" t="n"/>
+      <c r="S147">
+        <f>IF(L147="회신 완료","",J147-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T147">
+        <f>IF(L147="회신 완료","완료",IF(J147&lt;TODAY(),"지연",IF(J147-TODAY()&lt;=1,"임박(D-1 이내)",IF(J147-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
@@ -12515,6 +13837,14 @@
         </is>
       </c>
       <c r="R148" s="7" t="n"/>
+      <c r="S148">
+        <f>IF(L148="회신 완료","",J148-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T148">
+        <f>IF(L148="회신 완료","완료",IF(J148&lt;TODAY(),"지연",IF(J148-TODAY()&lt;=1,"임박(D-1 이내)",IF(J148-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n">
@@ -12585,6 +13915,14 @@
         </is>
       </c>
       <c r="R149" s="7" t="n"/>
+      <c r="S149">
+        <f>IF(L149="회신 완료","",J149-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T149">
+        <f>IF(L149="회신 완료","완료",IF(J149&lt;TODAY(),"지연",IF(J149-TODAY()&lt;=1,"임박(D-1 이내)",IF(J149-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -12655,6 +13993,14 @@
         </is>
       </c>
       <c r="R150" s="7" t="n"/>
+      <c r="S150">
+        <f>IF(L150="회신 완료","",J150-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T150">
+        <f>IF(L150="회신 완료","완료",IF(J150&lt;TODAY(),"지연",IF(J150-TODAY()&lt;=1,"임박(D-1 이내)",IF(J150-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n">
@@ -12725,6 +14071,14 @@
         </is>
       </c>
       <c r="R151" s="7" t="n"/>
+      <c r="S151">
+        <f>IF(L151="회신 완료","",J151-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T151">
+        <f>IF(L151="회신 완료","완료",IF(J151&lt;TODAY(),"지연",IF(J151-TODAY()&lt;=1,"임박(D-1 이내)",IF(J151-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
@@ -12795,6 +14149,14 @@
         </is>
       </c>
       <c r="R152" s="7" t="n"/>
+      <c r="S152">
+        <f>IF(L152="회신 완료","",J152-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T152">
+        <f>IF(L152="회신 완료","완료",IF(J152&lt;TODAY(),"지연",IF(J152-TODAY()&lt;=1,"임박(D-1 이내)",IF(J152-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n">
@@ -12865,6 +14227,14 @@
         </is>
       </c>
       <c r="R153" s="7" t="n"/>
+      <c r="S153">
+        <f>IF(L153="회신 완료","",J153-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T153">
+        <f>IF(L153="회신 완료","완료",IF(J153&lt;TODAY(),"지연",IF(J153-TODAY()&lt;=1,"임박(D-1 이내)",IF(J153-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
@@ -12935,6 +14305,14 @@
         </is>
       </c>
       <c r="R154" s="7" t="n"/>
+      <c r="S154">
+        <f>IF(L154="회신 완료","",J154-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T154">
+        <f>IF(L154="회신 완료","완료",IF(J154&lt;TODAY(),"지연",IF(J154-TODAY()&lt;=1,"임박(D-1 이내)",IF(J154-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n">
@@ -13005,6 +14383,14 @@
         </is>
       </c>
       <c r="R155" s="7" t="n"/>
+      <c r="S155">
+        <f>IF(L155="회신 완료","",J155-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T155">
+        <f>IF(L155="회신 완료","완료",IF(J155&lt;TODAY(),"지연",IF(J155-TODAY()&lt;=1,"임박(D-1 이내)",IF(J155-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
@@ -13075,6 +14461,14 @@
         </is>
       </c>
       <c r="R156" s="7" t="n"/>
+      <c r="S156">
+        <f>IF(L156="회신 완료","",J156-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T156">
+        <f>IF(L156="회신 완료","완료",IF(J156&lt;TODAY(),"지연",IF(J156-TODAY()&lt;=1,"임박(D-1 이내)",IF(J156-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n">
@@ -13145,6 +14539,14 @@
         </is>
       </c>
       <c r="R157" s="7" t="n"/>
+      <c r="S157">
+        <f>IF(L157="회신 완료","",J157-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T157">
+        <f>IF(L157="회신 완료","완료",IF(J157&lt;TODAY(),"지연",IF(J157-TODAY()&lt;=1,"임박(D-1 이내)",IF(J157-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
@@ -13215,6 +14617,14 @@
         </is>
       </c>
       <c r="R158" s="7" t="n"/>
+      <c r="S158">
+        <f>IF(L158="회신 완료","",J158-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T158">
+        <f>IF(L158="회신 완료","완료",IF(J158&lt;TODAY(),"지연",IF(J158-TODAY()&lt;=1,"임박(D-1 이내)",IF(J158-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n">
@@ -13285,6 +14695,14 @@
         </is>
       </c>
       <c r="R159" s="7" t="n"/>
+      <c r="S159">
+        <f>IF(L159="회신 완료","",J159-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T159">
+        <f>IF(L159="회신 완료","완료",IF(J159&lt;TODAY(),"지연",IF(J159-TODAY()&lt;=1,"임박(D-1 이내)",IF(J159-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
@@ -13355,6 +14773,14 @@
         </is>
       </c>
       <c r="R160" s="7" t="n"/>
+      <c r="S160">
+        <f>IF(L160="회신 완료","",J160-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T160">
+        <f>IF(L160="회신 완료","완료",IF(J160&lt;TODAY(),"지연",IF(J160-TODAY()&lt;=1,"임박(D-1 이내)",IF(J160-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n">
@@ -13425,6 +14851,14 @@
         </is>
       </c>
       <c r="R161" s="7" t="n"/>
+      <c r="S161">
+        <f>IF(L161="회신 완료","",J161-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T161">
+        <f>IF(L161="회신 완료","완료",IF(J161&lt;TODAY(),"지연",IF(J161-TODAY()&lt;=1,"임박(D-1 이내)",IF(J161-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
@@ -13495,6 +14929,14 @@
         </is>
       </c>
       <c r="R162" s="7" t="n"/>
+      <c r="S162">
+        <f>IF(L162="회신 완료","",J162-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T162">
+        <f>IF(L162="회신 완료","완료",IF(J162&lt;TODAY(),"지연",IF(J162-TODAY()&lt;=1,"임박(D-1 이내)",IF(J162-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n">
@@ -13565,6 +15007,14 @@
         </is>
       </c>
       <c r="R163" s="7" t="n"/>
+      <c r="S163">
+        <f>IF(L163="회신 완료","",J163-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T163">
+        <f>IF(L163="회신 완료","완료",IF(J163&lt;TODAY(),"지연",IF(J163-TODAY()&lt;=1,"임박(D-1 이내)",IF(J163-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
@@ -13635,6 +15085,14 @@
         </is>
       </c>
       <c r="R164" s="7" t="n"/>
+      <c r="S164">
+        <f>IF(L164="회신 완료","",J164-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T164">
+        <f>IF(L164="회신 완료","완료",IF(J164&lt;TODAY(),"지연",IF(J164-TODAY()&lt;=1,"임박(D-1 이내)",IF(J164-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n">
@@ -13705,6 +15163,14 @@
         </is>
       </c>
       <c r="R165" s="7" t="n"/>
+      <c r="S165">
+        <f>IF(L165="회신 완료","",J165-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T165">
+        <f>IF(L165="회신 완료","완료",IF(J165&lt;TODAY(),"지연",IF(J165-TODAY()&lt;=1,"임박(D-1 이내)",IF(J165-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n">
@@ -13775,6 +15241,14 @@
         </is>
       </c>
       <c r="R166" s="7" t="n"/>
+      <c r="S166">
+        <f>IF(L166="회신 완료","",J166-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T166">
+        <f>IF(L166="회신 완료","완료",IF(J166&lt;TODAY(),"지연",IF(J166-TODAY()&lt;=1,"임박(D-1 이내)",IF(J166-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n">
@@ -13845,6 +15319,14 @@
         </is>
       </c>
       <c r="R167" s="7" t="n"/>
+      <c r="S167">
+        <f>IF(L167="회신 완료","",J167-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T167">
+        <f>IF(L167="회신 완료","완료",IF(J167&lt;TODAY(),"지연",IF(J167-TODAY()&lt;=1,"임박(D-1 이내)",IF(J167-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n">
@@ -13915,6 +15397,14 @@
         </is>
       </c>
       <c r="R168" s="7" t="n"/>
+      <c r="S168">
+        <f>IF(L168="회신 완료","",J168-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T168">
+        <f>IF(L168="회신 완료","완료",IF(J168&lt;TODAY(),"지연",IF(J168-TODAY()&lt;=1,"임박(D-1 이내)",IF(J168-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n">
@@ -13985,6 +15475,14 @@
         </is>
       </c>
       <c r="R169" s="7" t="n"/>
+      <c r="S169">
+        <f>IF(L169="회신 완료","",J169-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T169">
+        <f>IF(L169="회신 완료","완료",IF(J169&lt;TODAY(),"지연",IF(J169-TODAY()&lt;=1,"임박(D-1 이내)",IF(J169-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n">
@@ -14055,6 +15553,14 @@
         </is>
       </c>
       <c r="R170" s="7" t="n"/>
+      <c r="S170">
+        <f>IF(L170="회신 완료","",J170-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T170">
+        <f>IF(L170="회신 완료","완료",IF(J170&lt;TODAY(),"지연",IF(J170-TODAY()&lt;=1,"임박(D-1 이내)",IF(J170-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n">
@@ -14125,6 +15631,14 @@
         </is>
       </c>
       <c r="R171" s="7" t="n"/>
+      <c r="S171">
+        <f>IF(L171="회신 완료","",J171-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T171">
+        <f>IF(L171="회신 완료","완료",IF(J171&lt;TODAY(),"지연",IF(J171-TODAY()&lt;=1,"임박(D-1 이내)",IF(J171-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n">
@@ -14195,6 +15709,14 @@
         </is>
       </c>
       <c r="R172" s="7" t="n"/>
+      <c r="S172">
+        <f>IF(L172="회신 완료","",J172-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T172">
+        <f>IF(L172="회신 완료","완료",IF(J172&lt;TODAY(),"지연",IF(J172-TODAY()&lt;=1,"임박(D-1 이내)",IF(J172-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n">
@@ -14265,6 +15787,14 @@
         </is>
       </c>
       <c r="R173" s="7" t="n"/>
+      <c r="S173">
+        <f>IF(L173="회신 완료","",J173-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T173">
+        <f>IF(L173="회신 완료","완료",IF(J173&lt;TODAY(),"지연",IF(J173-TODAY()&lt;=1,"임박(D-1 이내)",IF(J173-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n">
@@ -14335,6 +15865,14 @@
         </is>
       </c>
       <c r="R174" s="7" t="n"/>
+      <c r="S174">
+        <f>IF(L174="회신 완료","",J174-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T174">
+        <f>IF(L174="회신 완료","완료",IF(J174&lt;TODAY(),"지연",IF(J174-TODAY()&lt;=1,"임박(D-1 이내)",IF(J174-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n">
@@ -14405,6 +15943,14 @@
         </is>
       </c>
       <c r="R175" s="7" t="n"/>
+      <c r="S175">
+        <f>IF(L175="회신 완료","",J175-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T175">
+        <f>IF(L175="회신 완료","완료",IF(J175&lt;TODAY(),"지연",IF(J175-TODAY()&lt;=1,"임박(D-1 이내)",IF(J175-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n">
@@ -14475,6 +16021,14 @@
         </is>
       </c>
       <c r="R176" s="7" t="n"/>
+      <c r="S176">
+        <f>IF(L176="회신 완료","",J176-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T176">
+        <f>IF(L176="회신 완료","완료",IF(J176&lt;TODAY(),"지연",IF(J176-TODAY()&lt;=1,"임박(D-1 이내)",IF(J176-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n">
@@ -14545,6 +16099,14 @@
         </is>
       </c>
       <c r="R177" s="7" t="n"/>
+      <c r="S177">
+        <f>IF(L177="회신 완료","",J177-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T177">
+        <f>IF(L177="회신 완료","완료",IF(J177&lt;TODAY(),"지연",IF(J177-TODAY()&lt;=1,"임박(D-1 이내)",IF(J177-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n">
@@ -14615,6 +16177,14 @@
         </is>
       </c>
       <c r="R178" s="7" t="n"/>
+      <c r="S178">
+        <f>IF(L178="회신 완료","",J178-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T178">
+        <f>IF(L178="회신 완료","완료",IF(J178&lt;TODAY(),"지연",IF(J178-TODAY()&lt;=1,"임박(D-1 이내)",IF(J178-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n">
@@ -14685,6 +16255,14 @@
         </is>
       </c>
       <c r="R179" s="7" t="n"/>
+      <c r="S179">
+        <f>IF(L179="회신 완료","",J179-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T179">
+        <f>IF(L179="회신 완료","완료",IF(J179&lt;TODAY(),"지연",IF(J179-TODAY()&lt;=1,"임박(D-1 이내)",IF(J179-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n">
@@ -14755,6 +16333,14 @@
         </is>
       </c>
       <c r="R180" s="7" t="n"/>
+      <c r="S180">
+        <f>IF(L180="회신 완료","",J180-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T180">
+        <f>IF(L180="회신 완료","완료",IF(J180&lt;TODAY(),"지연",IF(J180-TODAY()&lt;=1,"임박(D-1 이내)",IF(J180-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n">
@@ -14825,6 +16411,14 @@
         </is>
       </c>
       <c r="R181" s="7" t="n"/>
+      <c r="S181">
+        <f>IF(L181="회신 완료","",J181-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T181">
+        <f>IF(L181="회신 완료","완료",IF(J181&lt;TODAY(),"지연",IF(J181-TODAY()&lt;=1,"임박(D-1 이내)",IF(J181-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n">
@@ -14895,6 +16489,14 @@
         </is>
       </c>
       <c r="R182" s="7" t="n"/>
+      <c r="S182">
+        <f>IF(L182="회신 완료","",J182-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T182">
+        <f>IF(L182="회신 완료","완료",IF(J182&lt;TODAY(),"지연",IF(J182-TODAY()&lt;=1,"임박(D-1 이내)",IF(J182-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n">
@@ -14965,6 +16567,14 @@
         </is>
       </c>
       <c r="R183" s="7" t="n"/>
+      <c r="S183">
+        <f>IF(L183="회신 완료","",J183-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T183">
+        <f>IF(L183="회신 완료","완료",IF(J183&lt;TODAY(),"지연",IF(J183-TODAY()&lt;=1,"임박(D-1 이내)",IF(J183-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n">
@@ -15035,6 +16645,14 @@
         </is>
       </c>
       <c r="R184" s="7" t="n"/>
+      <c r="S184">
+        <f>IF(L184="회신 완료","",J184-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T184">
+        <f>IF(L184="회신 완료","완료",IF(J184&lt;TODAY(),"지연",IF(J184-TODAY()&lt;=1,"임박(D-1 이내)",IF(J184-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n">
@@ -15105,6 +16723,14 @@
         </is>
       </c>
       <c r="R185" s="7" t="n"/>
+      <c r="S185">
+        <f>IF(L185="회신 완료","",J185-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T185">
+        <f>IF(L185="회신 완료","완료",IF(J185&lt;TODAY(),"지연",IF(J185-TODAY()&lt;=1,"임박(D-1 이내)",IF(J185-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n">
@@ -15175,6 +16801,14 @@
         </is>
       </c>
       <c r="R186" s="7" t="n"/>
+      <c r="S186">
+        <f>IF(L186="회신 완료","",J186-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T186">
+        <f>IF(L186="회신 완료","완료",IF(J186&lt;TODAY(),"지연",IF(J186-TODAY()&lt;=1,"임박(D-1 이내)",IF(J186-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n">
@@ -15245,6 +16879,14 @@
         </is>
       </c>
       <c r="R187" s="7" t="n"/>
+      <c r="S187">
+        <f>IF(L187="회신 완료","",J187-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T187">
+        <f>IF(L187="회신 완료","완료",IF(J187&lt;TODAY(),"지연",IF(J187-TODAY()&lt;=1,"임박(D-1 이내)",IF(J187-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n">
@@ -15315,6 +16957,14 @@
         </is>
       </c>
       <c r="R188" s="7" t="n"/>
+      <c r="S188">
+        <f>IF(L188="회신 완료","",J188-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T188">
+        <f>IF(L188="회신 완료","완료",IF(J188&lt;TODAY(),"지연",IF(J188-TODAY()&lt;=1,"임박(D-1 이내)",IF(J188-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n">
@@ -15385,6 +17035,14 @@
         </is>
       </c>
       <c r="R189" s="7" t="n"/>
+      <c r="S189">
+        <f>IF(L189="회신 완료","",J189-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T189">
+        <f>IF(L189="회신 완료","완료",IF(J189&lt;TODAY(),"지연",IF(J189-TODAY()&lt;=1,"임박(D-1 이내)",IF(J189-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n">
@@ -15455,6 +17113,14 @@
         </is>
       </c>
       <c r="R190" s="7" t="n"/>
+      <c r="S190">
+        <f>IF(L190="회신 완료","",J190-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T190">
+        <f>IF(L190="회신 완료","완료",IF(J190&lt;TODAY(),"지연",IF(J190-TODAY()&lt;=1,"임박(D-1 이내)",IF(J190-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n">
@@ -15525,6 +17191,14 @@
         </is>
       </c>
       <c r="R191" s="7" t="n"/>
+      <c r="S191">
+        <f>IF(L191="회신 완료","",J191-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T191">
+        <f>IF(L191="회신 완료","완료",IF(J191&lt;TODAY(),"지연",IF(J191-TODAY()&lt;=1,"임박(D-1 이내)",IF(J191-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n">
@@ -15595,6 +17269,14 @@
         </is>
       </c>
       <c r="R192" s="7" t="n"/>
+      <c r="S192">
+        <f>IF(L192="회신 완료","",J192-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T192">
+        <f>IF(L192="회신 완료","완료",IF(J192&lt;TODAY(),"지연",IF(J192-TODAY()&lt;=1,"임박(D-1 이내)",IF(J192-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n">
@@ -15665,6 +17347,14 @@
         </is>
       </c>
       <c r="R193" s="7" t="n"/>
+      <c r="S193">
+        <f>IF(L193="회신 완료","",J193-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T193">
+        <f>IF(L193="회신 완료","완료",IF(J193&lt;TODAY(),"지연",IF(J193-TODAY()&lt;=1,"임박(D-1 이내)",IF(J193-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n">
@@ -15735,6 +17425,14 @@
         </is>
       </c>
       <c r="R194" s="7" t="n"/>
+      <c r="S194">
+        <f>IF(L194="회신 완료","",J194-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T194">
+        <f>IF(L194="회신 완료","완료",IF(J194&lt;TODAY(),"지연",IF(J194-TODAY()&lt;=1,"임박(D-1 이내)",IF(J194-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n">
@@ -15805,6 +17503,14 @@
         </is>
       </c>
       <c r="R195" s="7" t="n"/>
+      <c r="S195">
+        <f>IF(L195="회신 완료","",J195-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T195">
+        <f>IF(L195="회신 완료","완료",IF(J195&lt;TODAY(),"지연",IF(J195-TODAY()&lt;=1,"임박(D-1 이내)",IF(J195-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n">
@@ -15875,6 +17581,14 @@
         </is>
       </c>
       <c r="R196" s="7" t="n"/>
+      <c r="S196">
+        <f>IF(L196="회신 완료","",J196-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T196">
+        <f>IF(L196="회신 완료","완료",IF(J196&lt;TODAY(),"지연",IF(J196-TODAY()&lt;=1,"임박(D-1 이내)",IF(J196-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n">
@@ -15945,6 +17659,14 @@
         </is>
       </c>
       <c r="R197" s="7" t="n"/>
+      <c r="S197">
+        <f>IF(L197="회신 완료","",J197-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T197">
+        <f>IF(L197="회신 완료","완료",IF(J197&lt;TODAY(),"지연",IF(J197-TODAY()&lt;=1,"임박(D-1 이내)",IF(J197-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n">
@@ -16015,6 +17737,14 @@
         </is>
       </c>
       <c r="R198" s="7" t="n"/>
+      <c r="S198">
+        <f>IF(L198="회신 완료","",J198-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T198">
+        <f>IF(L198="회신 완료","완료",IF(J198&lt;TODAY(),"지연",IF(J198-TODAY()&lt;=1,"임박(D-1 이내)",IF(J198-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n">
@@ -16085,6 +17815,14 @@
         </is>
       </c>
       <c r="R199" s="7" t="n"/>
+      <c r="S199">
+        <f>IF(L199="회신 완료","",J199-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T199">
+        <f>IF(L199="회신 완료","완료",IF(J199&lt;TODAY(),"지연",IF(J199-TODAY()&lt;=1,"임박(D-1 이내)",IF(J199-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n">
@@ -16155,6 +17893,14 @@
         </is>
       </c>
       <c r="R200" s="7" t="n"/>
+      <c r="S200">
+        <f>IF(L200="회신 완료","",J200-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T200">
+        <f>IF(L200="회신 완료","완료",IF(J200&lt;TODAY(),"지연",IF(J200-TODAY()&lt;=1,"임박(D-1 이내)",IF(J200-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n">
@@ -16225,6 +17971,14 @@
         </is>
       </c>
       <c r="R201" s="7" t="n"/>
+      <c r="S201">
+        <f>IF(L201="회신 완료","",J201-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T201">
+        <f>IF(L201="회신 완료","완료",IF(J201&lt;TODAY(),"지연",IF(J201-TODAY()&lt;=1,"임박(D-1 이내)",IF(J201-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n">
@@ -16295,6 +18049,14 @@
         </is>
       </c>
       <c r="R202" s="7" t="n"/>
+      <c r="S202">
+        <f>IF(L202="회신 완료","",J202-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T202">
+        <f>IF(L202="회신 완료","완료",IF(J202&lt;TODAY(),"지연",IF(J202-TODAY()&lt;=1,"임박(D-1 이내)",IF(J202-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n">
@@ -16365,6 +18127,14 @@
         </is>
       </c>
       <c r="R203" s="7" t="n"/>
+      <c r="S203">
+        <f>IF(L203="회신 완료","",J203-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T203">
+        <f>IF(L203="회신 완료","완료",IF(J203&lt;TODAY(),"지연",IF(J203-TODAY()&lt;=1,"임박(D-1 이내)",IF(J203-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n">
@@ -16435,6 +18205,14 @@
         </is>
       </c>
       <c r="R204" s="7" t="n"/>
+      <c r="S204">
+        <f>IF(L204="회신 완료","",J204-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T204">
+        <f>IF(L204="회신 완료","완료",IF(J204&lt;TODAY(),"지연",IF(J204-TODAY()&lt;=1,"임박(D-1 이내)",IF(J204-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n">
@@ -16505,6 +18283,14 @@
         </is>
       </c>
       <c r="R205" s="7" t="n"/>
+      <c r="S205">
+        <f>IF(L205="회신 완료","",J205-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T205">
+        <f>IF(L205="회신 완료","완료",IF(J205&lt;TODAY(),"지연",IF(J205-TODAY()&lt;=1,"임박(D-1 이내)",IF(J205-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n">
@@ -16575,6 +18361,14 @@
         </is>
       </c>
       <c r="R206" s="7" t="n"/>
+      <c r="S206">
+        <f>IF(L206="회신 완료","",J206-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T206">
+        <f>IF(L206="회신 완료","완료",IF(J206&lt;TODAY(),"지연",IF(J206-TODAY()&lt;=1,"임박(D-1 이내)",IF(J206-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="7" t="n">
@@ -16645,6 +18439,14 @@
         </is>
       </c>
       <c r="R207" s="7" t="n"/>
+      <c r="S207">
+        <f>IF(L207="회신 완료","",J207-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T207">
+        <f>IF(L207="회신 완료","완료",IF(J207&lt;TODAY(),"지연",IF(J207-TODAY()&lt;=1,"임박(D-1 이내)",IF(J207-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n">
@@ -16715,6 +18517,14 @@
         </is>
       </c>
       <c r="R208" s="7" t="n"/>
+      <c r="S208">
+        <f>IF(L208="회신 완료","",J208-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T208">
+        <f>IF(L208="회신 완료","완료",IF(J208&lt;TODAY(),"지연",IF(J208-TODAY()&lt;=1,"임박(D-1 이내)",IF(J208-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="7" t="n">
@@ -16785,6 +18595,14 @@
         </is>
       </c>
       <c r="R209" s="7" t="n"/>
+      <c r="S209">
+        <f>IF(L209="회신 완료","",J209-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T209">
+        <f>IF(L209="회신 완료","완료",IF(J209&lt;TODAY(),"지연",IF(J209-TODAY()&lt;=1,"임박(D-1 이내)",IF(J209-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="7" t="n">
@@ -16855,6 +18673,14 @@
         </is>
       </c>
       <c r="R210" s="7" t="n"/>
+      <c r="S210">
+        <f>IF(L210="회신 완료","",J210-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T210">
+        <f>IF(L210="회신 완료","완료",IF(J210&lt;TODAY(),"지연",IF(J210-TODAY()&lt;=1,"임박(D-1 이내)",IF(J210-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n">
@@ -16925,6 +18751,14 @@
         </is>
       </c>
       <c r="R211" s="7" t="n"/>
+      <c r="S211">
+        <f>IF(L211="회신 완료","",J211-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T211">
+        <f>IF(L211="회신 완료","완료",IF(J211&lt;TODAY(),"지연",IF(J211-TODAY()&lt;=1,"임박(D-1 이내)",IF(J211-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n">
@@ -16995,6 +18829,14 @@
         </is>
       </c>
       <c r="R212" s="7" t="n"/>
+      <c r="S212">
+        <f>IF(L212="회신 완료","",J212-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T212">
+        <f>IF(L212="회신 완료","완료",IF(J212&lt;TODAY(),"지연",IF(J212-TODAY()&lt;=1,"임박(D-1 이내)",IF(J212-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n">
@@ -17065,6 +18907,14 @@
         </is>
       </c>
       <c r="R213" s="7" t="n"/>
+      <c r="S213">
+        <f>IF(L213="회신 완료","",J213-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T213">
+        <f>IF(L213="회신 완료","완료",IF(J213&lt;TODAY(),"지연",IF(J213-TODAY()&lt;=1,"임박(D-1 이내)",IF(J213-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n">
@@ -17135,6 +18985,14 @@
         </is>
       </c>
       <c r="R214" s="7" t="n"/>
+      <c r="S214">
+        <f>IF(L214="회신 완료","",J214-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T214">
+        <f>IF(L214="회신 완료","완료",IF(J214&lt;TODAY(),"지연",IF(J214-TODAY()&lt;=1,"임박(D-1 이내)",IF(J214-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n">
@@ -17205,6 +19063,14 @@
         </is>
       </c>
       <c r="R215" s="7" t="n"/>
+      <c r="S215">
+        <f>IF(L215="회신 완료","",J215-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T215">
+        <f>IF(L215="회신 완료","완료",IF(J215&lt;TODAY(),"지연",IF(J215-TODAY()&lt;=1,"임박(D-1 이내)",IF(J215-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n">
@@ -17275,6 +19141,14 @@
         </is>
       </c>
       <c r="R216" s="7" t="n"/>
+      <c r="S216">
+        <f>IF(L216="회신 완료","",J216-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T216">
+        <f>IF(L216="회신 완료","완료",IF(J216&lt;TODAY(),"지연",IF(J216-TODAY()&lt;=1,"임박(D-1 이내)",IF(J216-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="7" t="n">
@@ -17345,6 +19219,14 @@
         </is>
       </c>
       <c r="R217" s="7" t="n"/>
+      <c r="S217">
+        <f>IF(L217="회신 완료","",J217-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T217">
+        <f>IF(L217="회신 완료","완료",IF(J217&lt;TODAY(),"지연",IF(J217-TODAY()&lt;=1,"임박(D-1 이내)",IF(J217-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="7" t="n">
@@ -17415,6 +19297,14 @@
         </is>
       </c>
       <c r="R218" s="7" t="n"/>
+      <c r="S218">
+        <f>IF(L218="회신 완료","",J218-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T218">
+        <f>IF(L218="회신 완료","완료",IF(J218&lt;TODAY(),"지연",IF(J218-TODAY()&lt;=1,"임박(D-1 이내)",IF(J218-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="7" t="n">
@@ -17485,6 +19375,14 @@
         </is>
       </c>
       <c r="R219" s="7" t="n"/>
+      <c r="S219">
+        <f>IF(L219="회신 완료","",J219-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T219">
+        <f>IF(L219="회신 완료","완료",IF(J219&lt;TODAY(),"지연",IF(J219-TODAY()&lt;=1,"임박(D-1 이내)",IF(J219-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="7" t="n">
@@ -17555,6 +19453,14 @@
         </is>
       </c>
       <c r="R220" s="7" t="n"/>
+      <c r="S220">
+        <f>IF(L220="회신 완료","",J220-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T220">
+        <f>IF(L220="회신 완료","완료",IF(J220&lt;TODAY(),"지연",IF(J220-TODAY()&lt;=1,"임박(D-1 이내)",IF(J220-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n">
@@ -17625,6 +19531,14 @@
         </is>
       </c>
       <c r="R221" s="7" t="n"/>
+      <c r="S221">
+        <f>IF(L221="회신 완료","",J221-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T221">
+        <f>IF(L221="회신 완료","완료",IF(J221&lt;TODAY(),"지연",IF(J221-TODAY()&lt;=1,"임박(D-1 이내)",IF(J221-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n">
@@ -17695,6 +19609,14 @@
         </is>
       </c>
       <c r="R222" s="7" t="n"/>
+      <c r="S222">
+        <f>IF(L222="회신 완료","",J222-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T222">
+        <f>IF(L222="회신 완료","완료",IF(J222&lt;TODAY(),"지연",IF(J222-TODAY()&lt;=1,"임박(D-1 이내)",IF(J222-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n">
@@ -17765,6 +19687,14 @@
         </is>
       </c>
       <c r="R223" s="7" t="n"/>
+      <c r="S223">
+        <f>IF(L223="회신 완료","",J223-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T223">
+        <f>IF(L223="회신 완료","완료",IF(J223&lt;TODAY(),"지연",IF(J223-TODAY()&lt;=1,"임박(D-1 이내)",IF(J223-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n">
@@ -17835,6 +19765,14 @@
         </is>
       </c>
       <c r="R224" s="7" t="n"/>
+      <c r="S224">
+        <f>IF(L224="회신 완료","",J224-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T224">
+        <f>IF(L224="회신 완료","완료",IF(J224&lt;TODAY(),"지연",IF(J224-TODAY()&lt;=1,"임박(D-1 이내)",IF(J224-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="7" t="n">
@@ -17905,6 +19843,14 @@
         </is>
       </c>
       <c r="R225" s="7" t="n"/>
+      <c r="S225">
+        <f>IF(L225="회신 완료","",J225-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T225">
+        <f>IF(L225="회신 완료","완료",IF(J225&lt;TODAY(),"지연",IF(J225-TODAY()&lt;=1,"임박(D-1 이내)",IF(J225-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="7" t="n">
@@ -17975,6 +19921,14 @@
         </is>
       </c>
       <c r="R226" s="7" t="n"/>
+      <c r="S226">
+        <f>IF(L226="회신 완료","",J226-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T226">
+        <f>IF(L226="회신 완료","완료",IF(J226&lt;TODAY(),"지연",IF(J226-TODAY()&lt;=1,"임박(D-1 이내)",IF(J226-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="7" t="n">
@@ -18045,6 +19999,14 @@
         </is>
       </c>
       <c r="R227" s="7" t="n"/>
+      <c r="S227">
+        <f>IF(L227="회신 완료","",J227-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T227">
+        <f>IF(L227="회신 완료","완료",IF(J227&lt;TODAY(),"지연",IF(J227-TODAY()&lt;=1,"임박(D-1 이내)",IF(J227-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="7" t="n">
@@ -18115,6 +20077,14 @@
         </is>
       </c>
       <c r="R228" s="7" t="n"/>
+      <c r="S228">
+        <f>IF(L228="회신 완료","",J228-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T228">
+        <f>IF(L228="회신 완료","완료",IF(J228&lt;TODAY(),"지연",IF(J228-TODAY()&lt;=1,"임박(D-1 이내)",IF(J228-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n">
@@ -18185,6 +20155,14 @@
         </is>
       </c>
       <c r="R229" s="7" t="n"/>
+      <c r="S229">
+        <f>IF(L229="회신 완료","",J229-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T229">
+        <f>IF(L229="회신 완료","완료",IF(J229&lt;TODAY(),"지연",IF(J229-TODAY()&lt;=1,"임박(D-1 이내)",IF(J229-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n">
@@ -18255,6 +20233,14 @@
         </is>
       </c>
       <c r="R230" s="7" t="n"/>
+      <c r="S230">
+        <f>IF(L230="회신 완료","",J230-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T230">
+        <f>IF(L230="회신 완료","완료",IF(J230&lt;TODAY(),"지연",IF(J230-TODAY()&lt;=1,"임박(D-1 이내)",IF(J230-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n">
@@ -18325,6 +20311,14 @@
         </is>
       </c>
       <c r="R231" s="7" t="n"/>
+      <c r="S231">
+        <f>IF(L231="회신 완료","",J231-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T231">
+        <f>IF(L231="회신 완료","완료",IF(J231&lt;TODAY(),"지연",IF(J231-TODAY()&lt;=1,"임박(D-1 이내)",IF(J231-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="7" t="n">
@@ -18395,6 +20389,14 @@
         </is>
       </c>
       <c r="R232" s="7" t="n"/>
+      <c r="S232">
+        <f>IF(L232="회신 완료","",J232-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T232">
+        <f>IF(L232="회신 완료","완료",IF(J232&lt;TODAY(),"지연",IF(J232-TODAY()&lt;=1,"임박(D-1 이내)",IF(J232-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n">
@@ -18465,6 +20467,14 @@
         </is>
       </c>
       <c r="R233" s="7" t="n"/>
+      <c r="S233">
+        <f>IF(L233="회신 완료","",J233-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T233">
+        <f>IF(L233="회신 완료","완료",IF(J233&lt;TODAY(),"지연",IF(J233-TODAY()&lt;=1,"임박(D-1 이내)",IF(J233-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n">
@@ -18535,6 +20545,14 @@
         </is>
       </c>
       <c r="R234" s="7" t="n"/>
+      <c r="S234">
+        <f>IF(L234="회신 완료","",J234-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T234">
+        <f>IF(L234="회신 완료","완료",IF(J234&lt;TODAY(),"지연",IF(J234-TODAY()&lt;=1,"임박(D-1 이내)",IF(J234-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n">
@@ -18605,6 +20623,14 @@
         </is>
       </c>
       <c r="R235" s="7" t="n"/>
+      <c r="S235">
+        <f>IF(L235="회신 완료","",J235-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T235">
+        <f>IF(L235="회신 완료","완료",IF(J235&lt;TODAY(),"지연",IF(J235-TODAY()&lt;=1,"임박(D-1 이내)",IF(J235-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n">
@@ -18675,6 +20701,14 @@
         </is>
       </c>
       <c r="R236" s="7" t="n"/>
+      <c r="S236">
+        <f>IF(L236="회신 완료","",J236-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T236">
+        <f>IF(L236="회신 완료","완료",IF(J236&lt;TODAY(),"지연",IF(J236-TODAY()&lt;=1,"임박(D-1 이내)",IF(J236-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n">
@@ -18745,6 +20779,14 @@
         </is>
       </c>
       <c r="R237" s="7" t="n"/>
+      <c r="S237">
+        <f>IF(L237="회신 완료","",J237-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T237">
+        <f>IF(L237="회신 완료","완료",IF(J237&lt;TODAY(),"지연",IF(J237-TODAY()&lt;=1,"임박(D-1 이내)",IF(J237-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n">
@@ -18815,6 +20857,14 @@
         </is>
       </c>
       <c r="R238" s="7" t="n"/>
+      <c r="S238">
+        <f>IF(L238="회신 완료","",J238-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T238">
+        <f>IF(L238="회신 완료","완료",IF(J238&lt;TODAY(),"지연",IF(J238-TODAY()&lt;=1,"임박(D-1 이내)",IF(J238-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n">
@@ -18885,6 +20935,14 @@
         </is>
       </c>
       <c r="R239" s="7" t="n"/>
+      <c r="S239">
+        <f>IF(L239="회신 완료","",J239-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T239">
+        <f>IF(L239="회신 완료","완료",IF(J239&lt;TODAY(),"지연",IF(J239-TODAY()&lt;=1,"임박(D-1 이내)",IF(J239-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n">
@@ -18955,6 +21013,14 @@
         </is>
       </c>
       <c r="R240" s="7" t="n"/>
+      <c r="S240">
+        <f>IF(L240="회신 완료","",J240-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T240">
+        <f>IF(L240="회신 완료","완료",IF(J240&lt;TODAY(),"지연",IF(J240-TODAY()&lt;=1,"임박(D-1 이내)",IF(J240-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n">
@@ -19025,15 +21091,31 @@
         </is>
       </c>
       <c r="R241" s="7" t="n"/>
+      <c r="S241">
+        <f>IF(L241="회신 완료","",J241-TODAY())</f>
+        <v/>
+      </c>
+      <c r="T241">
+        <f>IF(L241="회신 완료","완료",IF(J241&lt;TODAY(),"지연",IF(J241-TODAY()&lt;=1,"임박(D-1 이내)",IF(J241-TODAY()&lt;=3,"임박(D-3 이내)","여유"))))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R241"/>
+  <autoFilter ref="A1:T241"/>
   <conditionalFormatting sqref="A2:R241">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($L2&lt;&gt;"회신 완료",$K2&lt;&gt;"",$J2&lt;TODAY())</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>$L2="회신 완료"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:T241">
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>AND($L2&lt;&gt;"회신 완료",$J2&gt;=TODAY(),$J2-TODAY()&lt;=1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>AND($L2&lt;&gt;"회신 완료",$J2&gt;=TODAY(),$J2-TODAY()&lt;=3,$J2-TODAY()&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -19057,7 +21139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -19239,6 +21321,42 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>■ 기한 임박 표시 (2026-10-08 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>- 상세 시트 S열 '기한까지 남은 일수', T열 '기한 상태'(완료 / 지연 / 임박(D-1 이내) / 임박(D-3 이내) / 여유)가 자동 계산됩니다. 회신 완료가 아닌 행만 대상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>- 상세 행 색: 기한 D-3 이내는 노랑, D-1 이내(당일 포함)는 주황, 기한 경과는 빨강, 회신 완료는 초록입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>- 담당자별 현황의 '임박(D-3 이내) 미회신'과 '기한까지 남은 일수(최소)' 열에서 담당자별로 확인합니다. 임박 건이 있는 담당자 행은 노랑으로 표시됩니다(지연이 있으면 빨강 우선).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>- 표시는 파일을 열 때 오늘 날짜로 계산됩니다. 파일을 열지 않으면 알림이 뜨지 않으므로, 별도로 예약 알림(세션 알림)을 2026-10-12·14·15·16 오전 9시(KST)에 설정했습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -21139,7 +21139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -21321,7 +21321,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
@@ -21354,6 +21353,30 @@
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>- 표시는 파일을 열 때 오늘 날짜로 계산됩니다. 파일을 열지 않으면 알림이 뜨지 않으므로, 별도로 예약 알림(세션 알림)을 2026-10-12·14·15·16 오전 9시(KST)에 설정했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>■ 회신 취합 (2026-10-08 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>- 인쇄물은 직접 전달했습니다. 회신이 오면 회신취합/회신수집/ 에 채운 첨부 xlsx 를 넣고 `python3 회신취합.py 회신수집 [--apply]` 로 이 체크리스트의 사본(회신 반영)과 반영 후보 CSV 를 만듭니다. 절차는 회신취합/00_회신취합_안내.md 를 참고하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>- 수신처(메일·메신저) 목록은 사용하지 않아 삭제했습니다.</t>
         </is>
       </c>
     </row>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -546,21 +546,19 @@
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SQ 요청 회신 현황 — 담당자별 (회신 기한 2026-10-15)</t>
+          <t>SQ 요청 회신 현황 — 담당자별 (회신 기한 2026-10-15 경과, 새 기한 미정 · 담당자 정정본3 기준 2026-10-27)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>'상세' 시트의 발송일·회신 상태를 입력하면 자동 집계됩니다. 지연 = 발송했으나 회신 완료가 아니고 기한이 지난 건(오늘 기준). SQ NO 목록은 요청 시점(2026-10-08) 기준이며, 보완 필요 건은 건수가 많아 '상세' 시트에서 확인하세요.</t>
+          <t>'상세' 시트의 발송일·회신 상태를 입력하면 자동 집계됩니다. 지연 = 발송했으나 회신 완료가 아니고 기한이 지난 건(오늘 기준). 담당자는 정정본3 기준이며 인쇄물 전달 당시와 다른 건은 상세 R열에 표시했습니다. SQ NO 목록은 2026-10-27 기준(보완 필요는 상세 참고).</t>
         </is>
       </c>
     </row>
@@ -680,16 +678,6 @@
           <t>한 통 묶음 여부</t>
         </is>
       </c>
-      <c r="X4" s="15" t="inlineStr">
-        <is>
-          <t>임박(D-3 이내) 미회신</t>
-        </is>
-      </c>
-      <c r="Y4" s="15" t="inlineStr">
-        <is>
-          <t>기한까지 남은 일수(최소)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -777,7 +765,7 @@
       </c>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>22, 113</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V5" s="7" t="inlineStr">
@@ -789,14 +777,6 @@
         <is>
           <t>보유 확인 합쳐 한 통</t>
         </is>
-      </c>
-      <c r="X5" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y5" s="18">
-        <f>IF(N5=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A5,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -885,26 +865,18 @@
       </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
-          <t>47, 48, 65, 66, 67, 69, 70, 190</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W6" s="7" t="inlineStr">
         <is>
           <t>보유 확인 합쳐 한 통</t>
         </is>
-      </c>
-      <c r="X6" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="18">
-        <f>IF(N6=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A6,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -988,7 +960,7 @@
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>51, 75, 76, 77, 224</t>
+          <t>51, 75, 76, 224</t>
         </is>
       </c>
       <c r="U7" s="7" t="inlineStr">
@@ -1005,14 +977,6 @@
         <is>
           <t>요청만</t>
         </is>
-      </c>
-      <c r="X7" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="18">
-        <f>IF(N7=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A7,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -1114,14 +1078,6 @@
           <t>보유 확인 합쳐 한 통</t>
         </is>
       </c>
-      <c r="X8" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="18">
-        <f>IF(N8=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A8,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1204,31 +1160,23 @@
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>77, 99</t>
         </is>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
-          <t>25, 26, 106, 107, 108</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W9" s="7" t="inlineStr">
         <is>
           <t>요청만</t>
         </is>
-      </c>
-      <c r="X9" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="18">
-        <f>IF(N9=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A9,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -1322,21 +1270,13 @@
       </c>
       <c r="V10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="W10" s="7" t="inlineStr">
         <is>
           <t>요청만</t>
         </is>
-      </c>
-      <c r="X10" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="18">
-        <f>IF(N10=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A10,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -1438,14 +1378,6 @@
           <t>요청만</t>
         </is>
       </c>
-      <c r="X11" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="18">
-        <f>IF(N11=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A11,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1546,14 +1478,6 @@
           <t>요청만</t>
         </is>
       </c>
-      <c r="X12" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y12" s="18">
-        <f>IF(N12=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A12,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1641,7 +1565,7 @@
       </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
-          <t>100, 101</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V13" s="7" t="inlineStr">
@@ -1653,14 +1577,6 @@
         <is>
           <t>요청만</t>
         </is>
-      </c>
-      <c r="X13" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y13" s="18">
-        <f>IF(N13=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A13,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -1762,14 +1678,6 @@
           <t>요청만</t>
         </is>
       </c>
-      <c r="X14" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y14" s="18">
-        <f>IF(N14=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A14,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1870,103 +1778,185 @@
           <t>요청만</t>
         </is>
       </c>
-      <c r="X15" s="18">
-        <f>COUNTIFS(상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료",상세!$J:$J,"&gt;="&amp;TODAY(),상세!$J:$J,"&lt;="&amp;TODAY()+3)</f>
-        <v/>
-      </c>
-      <c r="Y15" s="18">
-        <f>IF(N15=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A15,상세!$L:$L,"&lt;&gt;회신 완료")-TODAY())</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>(미지정)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>(담당자 미지정)</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$E:$E,"판단 보류")</f>
+        <v/>
+      </c>
+      <c r="E16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$E:$E,"미비")</f>
+        <v/>
+      </c>
+      <c r="F16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$E:$E,"보완 필요")</f>
+        <v/>
+      </c>
+      <c r="G16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$E:$E,"보유 확인")</f>
+        <v/>
+      </c>
+      <c r="H16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$L:$L,"미발송")</f>
+        <v/>
+      </c>
+      <c r="I16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$L:$L,"발송(회신 대기)")</f>
+        <v/>
+      </c>
+      <c r="J16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$L:$L,"일부 회신")</f>
+        <v/>
+      </c>
+      <c r="K16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$L:$L,"재요청")</f>
+        <v/>
+      </c>
+      <c r="L16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$L:$L,"회신 완료")</f>
+        <v/>
+      </c>
+      <c r="M16" s="11">
+        <f>IF(C16=0,0,L16/C16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$L:$L,"&lt;&gt;회신 완료")</f>
+        <v/>
+      </c>
+      <c r="O16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$L:$L,"&lt;&gt;회신 완료",상세!$K:$K,"&lt;&gt;",상세!$J:$J,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="P16" s="7">
+        <f>COUNTIFS(상세!$H:$H,$A16,상세!$Q:$Q,"완료")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="8">
+        <f>IF(COUNTIFS(상세!$H:$H,$A16,상세!$K:$K,"&lt;&gt;")=0,"",_xlfn.MAXIFS(상세!$K:$K,상세!$H:$H,$A16))</f>
+        <v/>
+      </c>
+      <c r="R16" s="8">
+        <f>IF(N16=0,"",_xlfn.MINIFS(상세!$J:$J,상세!$H:$H,$A16,상세!$L:$L,"&lt;&gt;회신 완료"))</f>
+        <v/>
+      </c>
+      <c r="S16" s="7">
+        <f>IF(C16=L16,"회신 완료 — 조치 완료 여부 확인",IF(O16&gt;0,"지연 — 재촉 필요",IF(H16=C16,"발송 필요",IF(H16&gt;0,"일부 미발송 — 확인","회신 대기"))))</f>
+        <v/>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>담당자 지정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="9">
-        <f>SUM(C5:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="9">
-        <f>SUM(D5:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="9">
-        <f>SUM(E5:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="9">
-        <f>SUM(F5:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="9">
-        <f>SUM(G5:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="9">
-        <f>SUM(H5:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="9">
-        <f>SUM(I5:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="9">
-        <f>SUM(J5:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="9">
-        <f>SUM(K5:K15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="9">
-        <f>SUM(L5:L15)</f>
-        <v/>
-      </c>
-      <c r="M16" s="12">
-        <f>IF(C16=0,0,L16/C16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="9">
-        <f>SUM(N5:N15)</f>
-        <v/>
-      </c>
-      <c r="O16" s="9">
-        <f>SUM(O5:O15)</f>
-        <v/>
-      </c>
-      <c r="P16" s="9">
-        <f>SUM(P5:P15)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="10" t="inlineStr"/>
-      <c r="R16" s="10" t="inlineStr"/>
-      <c r="S16" s="9" t="inlineStr"/>
-      <c r="T16" s="9" t="inlineStr"/>
-      <c r="U16" s="9" t="inlineStr"/>
-      <c r="V16" s="9" t="inlineStr"/>
-      <c r="W16" s="9" t="inlineStr"/>
-      <c r="X16" s="19">
-        <f>SUM(X5:X15)</f>
-        <v/>
-      </c>
-      <c r="Y16" s="18" t="n"/>
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="9">
+        <f>SUM(C5:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="9">
+        <f>SUM(D5:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="9">
+        <f>SUM(E5:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="9">
+        <f>SUM(F5:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="9">
+        <f>SUM(G5:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="9">
+        <f>SUM(I5:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="9">
+        <f>SUM(J5:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="9">
+        <f>SUM(K5:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="9">
+        <f>SUM(L5:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="12">
+        <f>IF(C17=0,0,L17/C17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="9">
+        <f>SUM(N5:N16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="9">
+        <f>SUM(O5:O16)</f>
+        <v/>
+      </c>
+      <c r="P17" s="9">
+        <f>SUM(P5:P16)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="10" t="inlineStr"/>
+      <c r="R17" s="10" t="inlineStr"/>
+      <c r="S17" s="9" t="inlineStr"/>
+      <c r="T17" s="9" t="inlineStr"/>
+      <c r="U17" s="9" t="inlineStr"/>
+      <c r="V17" s="9" t="inlineStr"/>
+      <c r="W17" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:W15">
+  <conditionalFormatting sqref="A5:W16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$O5&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($C5&gt;0,$C5=$L5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:Y15">
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>AND($X5&gt;0,$O5=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2650,12 +2640,12 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>김명용</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_최종_20261008/메시지_황지환.txt</t>
         </is>
       </c>
       <c r="J5" s="8" t="n">
@@ -2682,7 +2672,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R5" s="7" t="n"/>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 김명용)</t>
+        </is>
+      </c>
       <c r="S5">
         <f>IF(L5="회신 완료","",J5-TODAY())</f>
         <v/>
@@ -5053,7 +5047,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -5092,7 +5086,7 @@
       <c r="O36" s="7" t="n"/>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
@@ -5131,7 +5125,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -5170,7 +5164,7 @@
       <c r="O37" s="7" t="n"/>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
@@ -6004,12 +5998,12 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>박철호</t>
+          <t>(미지정)</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_박철호.txt</t>
+          <t>(담당자 미지정)</t>
         </is>
       </c>
       <c r="J48" s="8" t="n">
@@ -6036,7 +6030,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R48" s="7" t="n"/>
+      <c r="R48" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 박철호)</t>
+        </is>
+      </c>
       <c r="S48">
         <f>IF(L48="회신 완료","",J48-TODAY())</f>
         <v/>
@@ -6535,7 +6533,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -6574,7 +6572,7 @@
       <c r="O55" s="7" t="n"/>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
@@ -6613,7 +6611,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -6652,7 +6650,7 @@
       <c r="O56" s="7" t="n"/>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
@@ -6691,7 +6689,7 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -6730,7 +6728,7 @@
       <c r="O57" s="7" t="n"/>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
@@ -6769,7 +6767,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -6808,7 +6806,7 @@
       <c r="O58" s="7" t="n"/>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
@@ -6847,7 +6845,7 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -6886,7 +6884,7 @@
       <c r="O59" s="7" t="n"/>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
@@ -6925,7 +6923,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -6964,7 +6962,7 @@
       <c r="O60" s="7" t="n"/>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>대표 양식 작성 선행 → 충족 확인</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
@@ -7003,7 +7001,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -7042,7 +7040,7 @@
       <c r="O61" s="7" t="n"/>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
@@ -7081,7 +7079,7 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -7120,7 +7118,7 @@
       <c r="O62" s="7" t="n"/>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
@@ -9826,12 +9824,12 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>이광재</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_최종_20261008/메시지_황지환.txt</t>
         </is>
       </c>
       <c r="J97" s="8" t="n">
@@ -9858,7 +9856,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R97" s="7" t="n"/>
+      <c r="R97" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 이광재)</t>
+        </is>
+      </c>
       <c r="S97">
         <f>IF(L97="회신 완료","",J97-TODAY())</f>
         <v/>
@@ -13165,7 +13167,7 @@
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
@@ -13204,7 +13206,7 @@
       <c r="O140" s="7" t="n"/>
       <c r="P140" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q140" s="7" t="inlineStr">
@@ -13243,7 +13245,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -13282,7 +13284,7 @@
       <c r="O141" s="7" t="n"/>
       <c r="P141" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q141" s="7" t="inlineStr">
@@ -13492,12 +13494,12 @@
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_최종_20261008/메시지_황지환.txt</t>
         </is>
       </c>
       <c r="J144" s="8" t="n">
@@ -13524,7 +13526,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R144" s="7" t="n"/>
+      <c r="R144" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S144">
         <f>IF(L144="회신 완료","",J144-TODAY())</f>
         <v/>
@@ -13726,12 +13732,12 @@
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="I147" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_최종_20261008/메시지_황지환.txt</t>
         </is>
       </c>
       <c r="J147" s="8" t="n">
@@ -13758,7 +13764,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R147" s="7" t="n"/>
+      <c r="R147" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S147">
         <f>IF(L147="회신 완료","",J147-TODAY())</f>
         <v/>
@@ -13804,12 +13814,12 @@
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="I148" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_최종_20261008/메시지_황지환.txt</t>
         </is>
       </c>
       <c r="J148" s="8" t="n">
@@ -13836,7 +13846,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R148" s="7" t="n"/>
+      <c r="R148" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S148">
         <f>IF(L148="회신 완료","",J148-TODAY())</f>
         <v/>
@@ -13960,12 +13974,12 @@
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="I150" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_최종_20261008/메시지_황지환.txt</t>
         </is>
       </c>
       <c r="J150" s="8" t="n">
@@ -13992,7 +14006,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R150" s="7" t="n"/>
+      <c r="R150" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S150">
         <f>IF(L150="회신 완료","",J150-TODAY())</f>
         <v/>
@@ -14038,12 +14056,12 @@
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_최종_20261008/메시지_황지환.txt</t>
         </is>
       </c>
       <c r="J151" s="8" t="n">
@@ -14070,7 +14088,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R151" s="7" t="n"/>
+      <c r="R151" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S151">
         <f>IF(L151="회신 완료","",J151-TODAY())</f>
         <v/>
@@ -14116,12 +14138,12 @@
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>황지환</t>
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_최종_20261008/메시지_황지환.txt</t>
         </is>
       </c>
       <c r="J152" s="8" t="n">
@@ -14148,7 +14170,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R152" s="7" t="n"/>
+      <c r="R152" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S152">
         <f>IF(L152="회신 완료","",J152-TODAY())</f>
         <v/>
@@ -15364,12 +15390,12 @@
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>(미지정)</t>
         </is>
       </c>
       <c r="I168" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>(담당자 미지정)</t>
         </is>
       </c>
       <c r="J168" s="8" t="n">
@@ -15396,7 +15422,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R168" s="7" t="n"/>
+      <c r="R168" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S168">
         <f>IF(L168="회신 완료","",J168-TODAY())</f>
         <v/>
@@ -15442,12 +15472,12 @@
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>(미지정)</t>
         </is>
       </c>
       <c r="I169" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>(담당자 미지정)</t>
         </is>
       </c>
       <c r="J169" s="8" t="n">
@@ -15474,7 +15504,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R169" s="7" t="n"/>
+      <c r="R169" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S169">
         <f>IF(L169="회신 완료","",J169-TODAY())</f>
         <v/>
@@ -15520,12 +15554,12 @@
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>(미지정)</t>
         </is>
       </c>
       <c r="I170" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>(담당자 미지정)</t>
         </is>
       </c>
       <c r="J170" s="8" t="n">
@@ -15552,7 +15586,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R170" s="7" t="n"/>
+      <c r="R170" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+        </is>
+      </c>
       <c r="S170">
         <f>IF(L170="회신 완료","",J170-TODAY())</f>
         <v/>
@@ -19093,7 +19131,7 @@
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>보완 필요</t>
+          <t>보유 확인</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
@@ -19132,7 +19170,7 @@
       <c r="O216" s="7" t="n"/>
       <c r="P216" s="7" t="inlineStr">
         <is>
-          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
+          <t>4가지 확인 결과 → 문제 없으면 보유 유지, 문제 시 상태 재판정</t>
         </is>
       </c>
       <c r="Q216" s="7" t="inlineStr">
@@ -19483,7 +19521,7 @@
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
@@ -19522,7 +19560,7 @@
       <c r="O221" s="7" t="n"/>
       <c r="P221" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q221" s="7" t="inlineStr">
@@ -19561,7 +19599,7 @@
       </c>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
@@ -19600,7 +19638,7 @@
       <c r="O222" s="7" t="n"/>
       <c r="P222" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q222" s="7" t="inlineStr">
@@ -19639,7 +19677,7 @@
       </c>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
@@ -19678,7 +19716,7 @@
       <c r="O223" s="7" t="n"/>
       <c r="P223" s="7" t="inlineStr">
         <is>
-          <t>대표 양식 작성 선행 → 충족 확인</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q223" s="7" t="inlineStr">
@@ -19717,7 +19755,7 @@
       </c>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
@@ -19756,7 +19794,7 @@
       <c r="O224" s="7" t="n"/>
       <c r="P224" s="7" t="inlineStr">
         <is>
-          <t>대표 양식 작성 선행 → 충족 확인</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q224" s="7" t="inlineStr">
@@ -19795,7 +19833,7 @@
       </c>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>미비</t>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F225" s="7" t="inlineStr">
@@ -19834,7 +19872,7 @@
       <c r="O225" s="7" t="n"/>
       <c r="P225" s="7" t="inlineStr">
         <is>
-          <t>작성 예정일 확정 → 작성 후 새 수정본 recheck → 승인·배포</t>
+          <t>항목·기준 작성 파일 수령 → 같은 Rev.00 재개정(recheck → 승인·배포) → 매핑표 '보유'로 갱신</t>
         </is>
       </c>
       <c r="Q225" s="7" t="inlineStr">
@@ -19966,12 +20004,12 @@
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
-          <t>황지환</t>
+          <t>한상돈</t>
         </is>
       </c>
       <c r="I227" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
         </is>
       </c>
       <c r="J227" s="8" t="n">
@@ -19998,7 +20036,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R227" s="7" t="n"/>
+      <c r="R227" s="7" t="inlineStr">
+        <is>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 황지환)</t>
+        </is>
+      </c>
       <c r="S227">
         <f>IF(L227="회신 완료","",J227-TODAY())</f>
         <v/>
@@ -21139,7 +21181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -21356,9 +21398,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
@@ -21377,6 +21417,30 @@
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>- 수신처(메일·메신저) 목록은 사용하지 않아 삭제했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>■ 담당자 기준 변경 (2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>- 담당자는 주 브랜치 SQ_FM번호_배정대응표_정정본3.csv 기준으로 바꿨습니다(사용자 확인). 인쇄물 전달(2026-10-08) 당시 담당자와 달라진 행은 상세 R열에 이전 담당자를 적었습니다. 요청 유형도 최신 판정(매핑표 v5: 보유 6·보완 필요 205·판단 보류 29·미비 0)으로 갱신했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>- 정정본3 에 담당자가 없는 4건(SQ NO 129·130·131·214)은 '(미지정)'입니다. 담당자 지정 후 상세 H열을 바꾸세요.</t>
         </is>
       </c>
     </row>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -551,7 +551,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SQ 요청 회신 현황 — 담당자별 (회신 기한 2026-10-15 경과, 새 기한 미정 · 담당자 정정본3 기준 2026-10-27)</t>
+          <t>SQ 요청 회신 현황 — 담당자별 (회신 기한 2026-11-05 · 담당자 정정본3 기준 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="J2" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K2" s="8" t="n">
         <v>46303</v>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="J3" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K3" s="8" t="n">
         <v>46303</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="J4" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K4" s="8" t="n">
         <v>46303</v>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="J5" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K5" s="8" t="n">
         <v>46303</v>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="J6" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K6" s="8" t="n">
         <v>46303</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="J7" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>46303</v>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="J8" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>46303</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="J9" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>46303</v>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K10" s="8" t="n">
         <v>46303</v>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="J11" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>46303</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K12" s="8" t="n">
         <v>46303</v>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="J13" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K13" s="8" t="n">
         <v>46303</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="J14" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>46303</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="J15" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K15" s="8" t="n">
         <v>46303</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="J16" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K16" s="8" t="n">
         <v>46303</v>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="J17" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>46303</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="J18" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K18" s="8" t="n">
         <v>46303</v>
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="J19" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K19" s="8" t="n">
         <v>46303</v>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K20" s="8" t="n">
         <v>46303</v>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>46303</v>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="J22" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K22" s="8" t="n">
         <v>46303</v>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="J23" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>46303</v>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="J24" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K24" s="8" t="n">
         <v>46303</v>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K25" s="8" t="n">
         <v>46303</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K26" s="8" t="n">
         <v>46303</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K27" s="8" t="n">
         <v>46303</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="J28" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K28" s="8" t="n">
         <v>46303</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K29" s="8" t="n">
         <v>46303</v>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K30" s="8" t="n">
         <v>46303</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="J31" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K31" s="8" t="n">
         <v>46303</v>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="J32" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K32" s="8" t="n">
         <v>46303</v>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="J33" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K33" s="8" t="n">
         <v>46303</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K34" s="8" t="n">
         <v>46303</v>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="J35" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>46303</v>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K36" s="8" t="n">
         <v>46303</v>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="J37" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K37" s="8" t="n">
         <v>46303</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="J38" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K38" s="8" t="n">
         <v>46303</v>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="J39" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K39" s="8" t="n">
         <v>46303</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="J40" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K40" s="8" t="n">
         <v>46303</v>
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="J41" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>46303</v>
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K42" s="8" t="n">
         <v>46303</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="J43" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K43" s="8" t="n">
         <v>46303</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K44" s="8" t="n">
         <v>46303</v>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K45" s="8" t="n">
         <v>46303</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="J46" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K46" s="8" t="n">
         <v>46303</v>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="J47" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K47" s="8" t="n">
         <v>46303</v>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K48" s="8" t="n">
         <v>46303</v>
@@ -6089,7 +6089,7 @@
         </is>
       </c>
       <c r="J49" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K49" s="8" t="n">
         <v>46303</v>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="J50" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K50" s="8" t="n">
         <v>46303</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="J51" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K51" s="8" t="n">
         <v>46303</v>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="J52" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K52" s="8" t="n">
         <v>46303</v>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="J53" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K53" s="8" t="n">
         <v>46303</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="J54" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K54" s="8" t="n">
         <v>46303</v>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K55" s="8" t="n">
         <v>46303</v>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="J56" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K56" s="8" t="n">
         <v>46303</v>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="J57" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K57" s="8" t="n">
         <v>46303</v>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="J58" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K58" s="8" t="n">
         <v>46303</v>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="J59" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K59" s="8" t="n">
         <v>46303</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="J60" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K60" s="8" t="n">
         <v>46303</v>
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="J61" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K61" s="8" t="n">
         <v>46303</v>
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K62" s="8" t="n">
         <v>46303</v>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="J63" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K63" s="8" t="n">
         <v>46303</v>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K64" s="8" t="n">
         <v>46303</v>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="J65" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K65" s="8" t="n">
         <v>46303</v>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="J66" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K66" s="8" t="n">
         <v>46303</v>
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="J67" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K67" s="8" t="n">
         <v>46303</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="J68" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K68" s="8" t="n">
         <v>46303</v>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="J69" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K69" s="8" t="n">
         <v>46303</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="J70" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K70" s="8" t="n">
         <v>46303</v>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="J71" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K71" s="8" t="n">
         <v>46303</v>
@@ -7883,7 +7883,7 @@
         </is>
       </c>
       <c r="J72" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K72" s="8" t="n">
         <v>46303</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="J73" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K73" s="8" t="n">
         <v>46303</v>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="J74" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K74" s="8" t="n">
         <v>46303</v>
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="J75" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K75" s="8" t="n">
         <v>46303</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="J76" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K76" s="8" t="n">
         <v>46303</v>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="J77" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K77" s="8" t="n">
         <v>46303</v>
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="J78" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K78" s="8" t="n">
         <v>46303</v>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="J79" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K79" s="8" t="n">
         <v>46303</v>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="J80" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K80" s="8" t="n">
         <v>46303</v>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="J81" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K81" s="8" t="n">
         <v>46303</v>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="J82" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K82" s="8" t="n">
         <v>46303</v>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="J83" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K83" s="8" t="n">
         <v>46303</v>
@@ -8819,7 +8819,7 @@
         </is>
       </c>
       <c r="J84" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K84" s="8" t="n">
         <v>46303</v>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="J85" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K85" s="8" t="n">
         <v>46303</v>
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="J86" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K86" s="8" t="n">
         <v>46303</v>
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="J87" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K87" s="8" t="n">
         <v>46303</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="J88" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K88" s="8" t="n">
         <v>46303</v>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="J89" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K89" s="8" t="n">
         <v>46303</v>
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="J90" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K90" s="8" t="n">
         <v>46303</v>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="J91" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K91" s="8" t="n">
         <v>46303</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="J92" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K92" s="8" t="n">
         <v>46303</v>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="J93" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K93" s="8" t="n">
         <v>46303</v>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="J94" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K94" s="8" t="n">
         <v>46303</v>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="J95" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K95" s="8" t="n">
         <v>46303</v>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="J96" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K96" s="8" t="n">
         <v>46303</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="J97" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K97" s="8" t="n">
         <v>46303</v>
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="J98" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K98" s="8" t="n">
         <v>46303</v>
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="J99" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K99" s="8" t="n">
         <v>46303</v>
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="J100" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K100" s="8" t="n">
         <v>46303</v>
@@ -10149,7 +10149,7 @@
         </is>
       </c>
       <c r="J101" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K101" s="8" t="n">
         <v>46303</v>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="J102" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K102" s="8" t="n">
         <v>46303</v>
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="J103" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K103" s="8" t="n">
         <v>46303</v>
@@ -10383,7 +10383,7 @@
         </is>
       </c>
       <c r="J104" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K104" s="8" t="n">
         <v>46303</v>
@@ -10461,7 +10461,7 @@
         </is>
       </c>
       <c r="J105" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K105" s="8" t="n">
         <v>46303</v>
@@ -10539,7 +10539,7 @@
         </is>
       </c>
       <c r="J106" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K106" s="8" t="n">
         <v>46303</v>
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="J107" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K107" s="8" t="n">
         <v>46303</v>
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="J108" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K108" s="8" t="n">
         <v>46303</v>
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="J109" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K109" s="8" t="n">
         <v>46303</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="J110" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K110" s="8" t="n">
         <v>46303</v>
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="J111" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K111" s="8" t="n">
         <v>46303</v>
@@ -11007,7 +11007,7 @@
         </is>
       </c>
       <c r="J112" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K112" s="8" t="n">
         <v>46303</v>
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="J113" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K113" s="8" t="n">
         <v>46303</v>
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="J114" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K114" s="8" t="n">
         <v>46303</v>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="J115" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K115" s="8" t="n">
         <v>46303</v>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="J116" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K116" s="8" t="n">
         <v>46303</v>
@@ -11397,7 +11397,7 @@
         </is>
       </c>
       <c r="J117" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K117" s="8" t="n">
         <v>46303</v>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="J118" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K118" s="8" t="n">
         <v>46303</v>
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="J119" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K119" s="8" t="n">
         <v>46303</v>
@@ -11631,7 +11631,7 @@
         </is>
       </c>
       <c r="J120" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K120" s="8" t="n">
         <v>46303</v>
@@ -11709,7 +11709,7 @@
         </is>
       </c>
       <c r="J121" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K121" s="8" t="n">
         <v>46303</v>
@@ -11787,7 +11787,7 @@
         </is>
       </c>
       <c r="J122" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K122" s="8" t="n">
         <v>46303</v>
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="J123" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K123" s="8" t="n">
         <v>46303</v>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="J124" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K124" s="8" t="n">
         <v>46303</v>
@@ -12021,7 +12021,7 @@
         </is>
       </c>
       <c r="J125" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K125" s="8" t="n">
         <v>46303</v>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="J126" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K126" s="8" t="n">
         <v>46303</v>
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="J127" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K127" s="8" t="n">
         <v>46303</v>
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="J128" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K128" s="8" t="n">
         <v>46303</v>
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="J129" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K129" s="8" t="n">
         <v>46303</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="J130" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K130" s="8" t="n">
         <v>46303</v>
@@ -12489,7 +12489,7 @@
         </is>
       </c>
       <c r="J131" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K131" s="8" t="n">
         <v>46303</v>
@@ -12567,7 +12567,7 @@
         </is>
       </c>
       <c r="J132" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K132" s="8" t="n">
         <v>46303</v>
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="J133" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K133" s="8" t="n">
         <v>46303</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="J134" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K134" s="8" t="n">
         <v>46303</v>
@@ -12801,7 +12801,7 @@
         </is>
       </c>
       <c r="J135" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K135" s="8" t="n">
         <v>46303</v>
@@ -12879,7 +12879,7 @@
         </is>
       </c>
       <c r="J136" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K136" s="8" t="n">
         <v>46303</v>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="J137" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K137" s="8" t="n">
         <v>46303</v>
@@ -13035,7 +13035,7 @@
         </is>
       </c>
       <c r="J138" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K138" s="8" t="n">
         <v>46303</v>
@@ -13113,7 +13113,7 @@
         </is>
       </c>
       <c r="J139" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K139" s="8" t="n">
         <v>46303</v>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="J140" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K140" s="8" t="n">
         <v>46303</v>
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="J141" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K141" s="8" t="n">
         <v>46303</v>
@@ -13347,7 +13347,7 @@
         </is>
       </c>
       <c r="J142" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K142" s="8" t="n">
         <v>46303</v>
@@ -13425,7 +13425,7 @@
         </is>
       </c>
       <c r="J143" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K143" s="8" t="n">
         <v>46303</v>
@@ -13503,7 +13503,7 @@
         </is>
       </c>
       <c r="J144" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K144" s="8" t="n">
         <v>46303</v>
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="J145" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K145" s="8" t="n">
         <v>46303</v>
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="J146" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K146" s="8" t="n">
         <v>46303</v>
@@ -13741,7 +13741,7 @@
         </is>
       </c>
       <c r="J147" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K147" s="8" t="n">
         <v>46303</v>
@@ -13823,7 +13823,7 @@
         </is>
       </c>
       <c r="J148" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K148" s="8" t="n">
         <v>46303</v>
@@ -13905,7 +13905,7 @@
         </is>
       </c>
       <c r="J149" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K149" s="8" t="n">
         <v>46303</v>
@@ -13983,7 +13983,7 @@
         </is>
       </c>
       <c r="J150" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K150" s="8" t="n">
         <v>46303</v>
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="J151" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K151" s="8" t="n">
         <v>46303</v>
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="J152" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K152" s="8" t="n">
         <v>46303</v>
@@ -14229,7 +14229,7 @@
         </is>
       </c>
       <c r="J153" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K153" s="8" t="n">
         <v>46303</v>
@@ -14307,7 +14307,7 @@
         </is>
       </c>
       <c r="J154" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K154" s="8" t="n">
         <v>46303</v>
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="J155" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K155" s="8" t="n">
         <v>46303</v>
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="J156" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K156" s="8" t="n">
         <v>46303</v>
@@ -14541,7 +14541,7 @@
         </is>
       </c>
       <c r="J157" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K157" s="8" t="n">
         <v>46303</v>
@@ -14619,7 +14619,7 @@
         </is>
       </c>
       <c r="J158" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K158" s="8" t="n">
         <v>46303</v>
@@ -14697,7 +14697,7 @@
         </is>
       </c>
       <c r="J159" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K159" s="8" t="n">
         <v>46303</v>
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="J160" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K160" s="8" t="n">
         <v>46303</v>
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="J161" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K161" s="8" t="n">
         <v>46303</v>
@@ -14931,7 +14931,7 @@
         </is>
       </c>
       <c r="J162" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K162" s="8" t="n">
         <v>46303</v>
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="J163" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K163" s="8" t="n">
         <v>46303</v>
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="J164" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K164" s="8" t="n">
         <v>46303</v>
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="J165" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K165" s="8" t="n">
         <v>46303</v>
@@ -15243,7 +15243,7 @@
         </is>
       </c>
       <c r="J166" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K166" s="8" t="n">
         <v>46303</v>
@@ -15321,7 +15321,7 @@
         </is>
       </c>
       <c r="J167" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K167" s="8" t="n">
         <v>46303</v>
@@ -15399,7 +15399,7 @@
         </is>
       </c>
       <c r="J168" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K168" s="8" t="n">
         <v>46303</v>
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="J169" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K169" s="8" t="n">
         <v>46303</v>
@@ -15563,7 +15563,7 @@
         </is>
       </c>
       <c r="J170" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K170" s="8" t="n">
         <v>46303</v>
@@ -15645,7 +15645,7 @@
         </is>
       </c>
       <c r="J171" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K171" s="8" t="n">
         <v>46303</v>
@@ -15723,7 +15723,7 @@
         </is>
       </c>
       <c r="J172" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K172" s="8" t="n">
         <v>46303</v>
@@ -15801,7 +15801,7 @@
         </is>
       </c>
       <c r="J173" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K173" s="8" t="n">
         <v>46303</v>
@@ -15879,7 +15879,7 @@
         </is>
       </c>
       <c r="J174" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K174" s="8" t="n">
         <v>46303</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="J175" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K175" s="8" t="n">
         <v>46303</v>
@@ -16035,7 +16035,7 @@
         </is>
       </c>
       <c r="J176" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K176" s="8" t="n">
         <v>46303</v>
@@ -16113,7 +16113,7 @@
         </is>
       </c>
       <c r="J177" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K177" s="8" t="n">
         <v>46303</v>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="J178" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K178" s="8" t="n">
         <v>46303</v>
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="J179" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K179" s="8" t="n">
         <v>46303</v>
@@ -16347,7 +16347,7 @@
         </is>
       </c>
       <c r="J180" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K180" s="8" t="n">
         <v>46303</v>
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="J181" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K181" s="8" t="n">
         <v>46303</v>
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="J182" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K182" s="8" t="n">
         <v>46303</v>
@@ -16581,7 +16581,7 @@
         </is>
       </c>
       <c r="J183" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K183" s="8" t="n">
         <v>46303</v>
@@ -16659,7 +16659,7 @@
         </is>
       </c>
       <c r="J184" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K184" s="8" t="n">
         <v>46303</v>
@@ -16737,7 +16737,7 @@
         </is>
       </c>
       <c r="J185" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K185" s="8" t="n">
         <v>46303</v>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="J186" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K186" s="8" t="n">
         <v>46303</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="J187" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K187" s="8" t="n">
         <v>46303</v>
@@ -16971,7 +16971,7 @@
         </is>
       </c>
       <c r="J188" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K188" s="8" t="n">
         <v>46303</v>
@@ -17049,7 +17049,7 @@
         </is>
       </c>
       <c r="J189" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K189" s="8" t="n">
         <v>46303</v>
@@ -17127,7 +17127,7 @@
         </is>
       </c>
       <c r="J190" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K190" s="8" t="n">
         <v>46303</v>
@@ -17205,7 +17205,7 @@
         </is>
       </c>
       <c r="J191" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K191" s="8" t="n">
         <v>46303</v>
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="J192" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K192" s="8" t="n">
         <v>46303</v>
@@ -17361,7 +17361,7 @@
         </is>
       </c>
       <c r="J193" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K193" s="8" t="n">
         <v>46303</v>
@@ -17439,7 +17439,7 @@
         </is>
       </c>
       <c r="J194" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K194" s="8" t="n">
         <v>46303</v>
@@ -17517,7 +17517,7 @@
         </is>
       </c>
       <c r="J195" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K195" s="8" t="n">
         <v>46303</v>
@@ -17595,7 +17595,7 @@
         </is>
       </c>
       <c r="J196" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K196" s="8" t="n">
         <v>46303</v>
@@ -17673,7 +17673,7 @@
         </is>
       </c>
       <c r="J197" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K197" s="8" t="n">
         <v>46303</v>
@@ -17751,7 +17751,7 @@
         </is>
       </c>
       <c r="J198" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K198" s="8" t="n">
         <v>46303</v>
@@ -17829,7 +17829,7 @@
         </is>
       </c>
       <c r="J199" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K199" s="8" t="n">
         <v>46303</v>
@@ -17907,7 +17907,7 @@
         </is>
       </c>
       <c r="J200" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K200" s="8" t="n">
         <v>46303</v>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="J201" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K201" s="8" t="n">
         <v>46303</v>
@@ -18063,7 +18063,7 @@
         </is>
       </c>
       <c r="J202" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K202" s="8" t="n">
         <v>46303</v>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="J203" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K203" s="8" t="n">
         <v>46303</v>
@@ -18219,7 +18219,7 @@
         </is>
       </c>
       <c r="J204" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K204" s="8" t="n">
         <v>46303</v>
@@ -18297,7 +18297,7 @@
         </is>
       </c>
       <c r="J205" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K205" s="8" t="n">
         <v>46303</v>
@@ -18375,7 +18375,7 @@
         </is>
       </c>
       <c r="J206" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K206" s="8" t="n">
         <v>46303</v>
@@ -18453,7 +18453,7 @@
         </is>
       </c>
       <c r="J207" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K207" s="8" t="n">
         <v>46303</v>
@@ -18531,7 +18531,7 @@
         </is>
       </c>
       <c r="J208" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K208" s="8" t="n">
         <v>46303</v>
@@ -18609,7 +18609,7 @@
         </is>
       </c>
       <c r="J209" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K209" s="8" t="n">
         <v>46303</v>
@@ -18687,7 +18687,7 @@
         </is>
       </c>
       <c r="J210" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K210" s="8" t="n">
         <v>46303</v>
@@ -18765,7 +18765,7 @@
         </is>
       </c>
       <c r="J211" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K211" s="8" t="n">
         <v>46303</v>
@@ -18843,7 +18843,7 @@
         </is>
       </c>
       <c r="J212" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K212" s="8" t="n">
         <v>46303</v>
@@ -18921,7 +18921,7 @@
         </is>
       </c>
       <c r="J213" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K213" s="8" t="n">
         <v>46303</v>
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="J214" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K214" s="8" t="n">
         <v>46303</v>
@@ -19077,7 +19077,7 @@
         </is>
       </c>
       <c r="J215" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K215" s="8" t="n">
         <v>46303</v>
@@ -19155,7 +19155,7 @@
         </is>
       </c>
       <c r="J216" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K216" s="8" t="n">
         <v>46303</v>
@@ -19233,7 +19233,7 @@
         </is>
       </c>
       <c r="J217" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K217" s="8" t="n">
         <v>46303</v>
@@ -19311,7 +19311,7 @@
         </is>
       </c>
       <c r="J218" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K218" s="8" t="n">
         <v>46303</v>
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="J219" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K219" s="8" t="n">
         <v>46303</v>
@@ -19467,7 +19467,7 @@
         </is>
       </c>
       <c r="J220" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K220" s="8" t="n">
         <v>46303</v>
@@ -19545,7 +19545,7 @@
         </is>
       </c>
       <c r="J221" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K221" s="8" t="n">
         <v>46303</v>
@@ -19623,7 +19623,7 @@
         </is>
       </c>
       <c r="J222" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K222" s="8" t="n">
         <v>46303</v>
@@ -19701,7 +19701,7 @@
         </is>
       </c>
       <c r="J223" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K223" s="8" t="n">
         <v>46303</v>
@@ -19779,7 +19779,7 @@
         </is>
       </c>
       <c r="J224" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K224" s="8" t="n">
         <v>46303</v>
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="J225" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K225" s="8" t="n">
         <v>46303</v>
@@ -19935,7 +19935,7 @@
         </is>
       </c>
       <c r="J226" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K226" s="8" t="n">
         <v>46303</v>
@@ -20013,7 +20013,7 @@
         </is>
       </c>
       <c r="J227" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K227" s="8" t="n">
         <v>46303</v>
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="J228" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K228" s="8" t="n">
         <v>46303</v>
@@ -20173,7 +20173,7 @@
         </is>
       </c>
       <c r="J229" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K229" s="8" t="n">
         <v>46303</v>
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="J230" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K230" s="8" t="n">
         <v>46303</v>
@@ -20329,7 +20329,7 @@
         </is>
       </c>
       <c r="J231" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K231" s="8" t="n">
         <v>46303</v>
@@ -20407,7 +20407,7 @@
         </is>
       </c>
       <c r="J232" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K232" s="8" t="n">
         <v>46303</v>
@@ -20485,7 +20485,7 @@
         </is>
       </c>
       <c r="J233" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K233" s="8" t="n">
         <v>46303</v>
@@ -20563,7 +20563,7 @@
         </is>
       </c>
       <c r="J234" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K234" s="8" t="n">
         <v>46303</v>
@@ -20641,7 +20641,7 @@
         </is>
       </c>
       <c r="J235" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K235" s="8" t="n">
         <v>46303</v>
@@ -20719,7 +20719,7 @@
         </is>
       </c>
       <c r="J236" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K236" s="8" t="n">
         <v>46303</v>
@@ -20797,7 +20797,7 @@
         </is>
       </c>
       <c r="J237" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K237" s="8" t="n">
         <v>46303</v>
@@ -20875,7 +20875,7 @@
         </is>
       </c>
       <c r="J238" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K238" s="8" t="n">
         <v>46303</v>
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="J239" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K239" s="8" t="n">
         <v>46303</v>
@@ -21031,7 +21031,7 @@
         </is>
       </c>
       <c r="J240" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K240" s="8" t="n">
         <v>46303</v>
@@ -21109,7 +21109,7 @@
         </is>
       </c>
       <c r="J241" s="8" t="n">
-        <v>46310</v>
+        <v>46331</v>
       </c>
       <c r="K241" s="8" t="n">
         <v>46303</v>
@@ -21221,7 +21221,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>회신 기한: 2026-10-15 (사용자 지정, 보유 확인에도 같은 날짜 적용).</t>
+          <t>회신 기한: 2026-11-05 (사용자 지정 2026-10-27, 기존 2026-10-15 에서 변경. 보유 확인에도 같은 날짜 적용). 담당자가 바뀐 6명의 재안내(발송용_담당자변경_20261027)는 발송 후 상세 시트의 발송일·상태를 갱신하세요.</t>
         </is>
       </c>
     </row>
@@ -21398,7 +21398,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
@@ -21419,9 +21418,6 @@
           <t>- 수신처(메일·메신저) 목록은 사용하지 않아 삭제했습니다.</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -2411,14 +2411,14 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J2" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -2438,7 +2438,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R2" s="7" t="n"/>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S2">
         <f>IF(L2="회신 완료","",J2-TODAY())</f>
         <v/>
@@ -2489,14 +2493,14 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J3" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -2516,7 +2520,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R3" s="7" t="n"/>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S3">
         <f>IF(L3="회신 완료","",J3-TODAY())</f>
         <v/>
@@ -2567,14 +2575,14 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J4" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -2594,7 +2602,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R4" s="7" t="n"/>
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S4">
         <f>IF(L4="회신 완료","",J4-TODAY())</f>
         <v/>
@@ -2645,14 +2657,14 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J5" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -2674,7 +2686,7 @@
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 김명용)</t>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 김명용); 담당자 변경 재안내 발송 2026-10-27</t>
         </is>
       </c>
       <c r="S5">
@@ -2727,14 +2739,14 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J6" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -2754,7 +2766,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R6" s="7" t="n"/>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S6">
         <f>IF(L6="회신 완료","",J6-TODAY())</f>
         <v/>
@@ -2805,14 +2821,14 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J7" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -2832,7 +2848,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R7" s="7" t="n"/>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S7">
         <f>IF(L7="회신 완료","",J7-TODAY())</f>
         <v/>
@@ -2883,14 +2903,14 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J8" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -2910,7 +2930,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R8" s="7" t="n"/>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S8">
         <f>IF(L8="회신 완료","",J8-TODAY())</f>
         <v/>
@@ -2961,14 +2985,14 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J9" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -2988,7 +3012,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R9" s="7" t="n"/>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S9">
         <f>IF(L9="회신 완료","",J9-TODAY())</f>
         <v/>
@@ -3039,14 +3067,14 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J10" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -3066,7 +3094,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R10" s="7" t="n"/>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S10">
         <f>IF(L10="회신 완료","",J10-TODAY())</f>
         <v/>
@@ -3117,14 +3149,14 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J11" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -3144,7 +3176,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R11" s="7" t="n"/>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S11">
         <f>IF(L11="회신 완료","",J11-TODAY())</f>
         <v/>
@@ -3195,14 +3231,14 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J12" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -3222,7 +3258,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R12" s="7" t="n"/>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S12">
         <f>IF(L12="회신 완료","",J12-TODAY())</f>
         <v/>
@@ -3273,14 +3313,14 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J13" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -3300,7 +3340,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R13" s="7" t="n"/>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S13">
         <f>IF(L13="회신 완료","",J13-TODAY())</f>
         <v/>
@@ -3351,14 +3395,14 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J14" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -3378,7 +3422,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R14" s="7" t="n"/>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S14">
         <f>IF(L14="회신 완료","",J14-TODAY())</f>
         <v/>
@@ -3429,14 +3477,14 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J15" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -3456,7 +3504,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R15" s="7" t="n"/>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S15">
         <f>IF(L15="회신 완료","",J15-TODAY())</f>
         <v/>
@@ -3507,14 +3559,14 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J16" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -3534,7 +3586,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R16" s="7" t="n"/>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S16">
         <f>IF(L16="회신 완료","",J16-TODAY())</f>
         <v/>
@@ -3585,14 +3641,14 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J17" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -3612,7 +3668,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R17" s="7" t="n"/>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S17">
         <f>IF(L17="회신 완료","",J17-TODAY())</f>
         <v/>
@@ -3663,14 +3723,14 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J18" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -3690,7 +3750,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R18" s="7" t="n"/>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S18">
         <f>IF(L18="회신 완료","",J18-TODAY())</f>
         <v/>
@@ -3741,14 +3805,14 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J19" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -3768,7 +3832,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R19" s="7" t="n"/>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S19">
         <f>IF(L19="회신 완료","",J19-TODAY())</f>
         <v/>
@@ -3819,14 +3887,14 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J20" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -3846,7 +3914,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R20" s="7" t="n"/>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S20">
         <f>IF(L20="회신 완료","",J20-TODAY())</f>
         <v/>
@@ -3897,14 +3969,14 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J21" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -3924,7 +3996,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R21" s="7" t="n"/>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S21">
         <f>IF(L21="회신 완료","",J21-TODAY())</f>
         <v/>
@@ -3975,14 +4051,14 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J22" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -4002,7 +4078,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R22" s="7" t="n"/>
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S22">
         <f>IF(L22="회신 완료","",J22-TODAY())</f>
         <v/>
@@ -4053,14 +4133,14 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J23" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -4080,7 +4160,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R23" s="7" t="n"/>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S23">
         <f>IF(L23="회신 완료","",J23-TODAY())</f>
         <v/>
@@ -4131,14 +4215,14 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J24" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -4158,7 +4242,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R24" s="7" t="n"/>
+      <c r="R24" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S24">
         <f>IF(L24="회신 완료","",J24-TODAY())</f>
         <v/>
@@ -4209,14 +4297,14 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J25" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -4236,7 +4324,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R25" s="7" t="n"/>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S25">
         <f>IF(L25="회신 완료","",J25-TODAY())</f>
         <v/>
@@ -4287,14 +4379,14 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J26" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -4314,7 +4406,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R26" s="7" t="n"/>
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S26">
         <f>IF(L26="회신 완료","",J26-TODAY())</f>
         <v/>
@@ -4365,14 +4461,14 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J27" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -4392,7 +4488,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R27" s="7" t="n"/>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S27">
         <f>IF(L27="회신 완료","",J27-TODAY())</f>
         <v/>
@@ -4443,14 +4543,14 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J28" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -4470,7 +4570,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R28" s="7" t="n"/>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S28">
         <f>IF(L28="회신 완료","",J28-TODAY())</f>
         <v/>
@@ -4521,14 +4625,14 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J29" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -4548,7 +4652,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R29" s="7" t="n"/>
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S29">
         <f>IF(L29="회신 완료","",J29-TODAY())</f>
         <v/>
@@ -4599,14 +4707,14 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J30" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -4626,7 +4734,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R30" s="7" t="n"/>
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S30">
         <f>IF(L30="회신 완료","",J30-TODAY())</f>
         <v/>
@@ -4677,14 +4789,14 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J31" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4704,7 +4816,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R31" s="7" t="n"/>
+      <c r="R31" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S31">
         <f>IF(L31="회신 완료","",J31-TODAY())</f>
         <v/>
@@ -4755,14 +4871,14 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4782,7 +4898,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R32" s="7" t="n"/>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S32">
         <f>IF(L32="회신 완료","",J32-TODAY())</f>
         <v/>
@@ -4833,14 +4953,14 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J33" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4860,7 +4980,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R33" s="7" t="n"/>
+      <c r="R33" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S33">
         <f>IF(L33="회신 완료","",J33-TODAY())</f>
         <v/>
@@ -4911,14 +5035,14 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_김명용.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_김명용_20261027.txt</t>
         </is>
       </c>
       <c r="J34" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4938,7 +5062,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R34" s="7" t="n"/>
+      <c r="R34" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S34">
         <f>IF(L34="회신 완료","",J34-TODAY())</f>
         <v/>
@@ -5691,14 +5819,14 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_박철호.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_박철호_20261027.txt</t>
         </is>
       </c>
       <c r="J44" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5718,7 +5846,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R44" s="7" t="n"/>
+      <c r="R44" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S44">
         <f>IF(L44="회신 완료","",J44-TODAY())</f>
         <v/>
@@ -5769,14 +5901,14 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_박철호.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_박철호_20261027.txt</t>
         </is>
       </c>
       <c r="J45" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5796,7 +5928,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R45" s="7" t="n"/>
+      <c r="R45" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S45">
         <f>IF(L45="회신 완료","",J45-TODAY())</f>
         <v/>
@@ -5847,14 +5983,14 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_박철호.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_박철호_20261027.txt</t>
         </is>
       </c>
       <c r="J46" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5874,7 +6010,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R46" s="7" t="n"/>
+      <c r="R46" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S46">
         <f>IF(L46="회신 완료","",J46-TODAY())</f>
         <v/>
@@ -5925,14 +6065,14 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_박철호.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_박철호_20261027.txt</t>
         </is>
       </c>
       <c r="J47" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5952,7 +6092,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R47" s="7" t="n"/>
+      <c r="R47" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S47">
         <f>IF(L47="회신 완료","",J47-TODAY())</f>
         <v/>
@@ -6241,14 +6385,14 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J51" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6268,7 +6412,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R51" s="7" t="n"/>
+      <c r="R51" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S51">
         <f>IF(L51="회신 완료","",J51-TODAY())</f>
         <v/>
@@ -6319,14 +6467,14 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J52" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6346,7 +6494,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R52" s="7" t="n"/>
+      <c r="R52" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S52">
         <f>IF(L52="회신 완료","",J52-TODAY())</f>
         <v/>
@@ -6397,14 +6549,14 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J53" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6424,7 +6576,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R53" s="7" t="n"/>
+      <c r="R53" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S53">
         <f>IF(L53="회신 완료","",J53-TODAY())</f>
         <v/>
@@ -6475,14 +6631,14 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J54" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6502,7 +6658,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R54" s="7" t="n"/>
+      <c r="R54" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S54">
         <f>IF(L54="회신 완료","",J54-TODAY())</f>
         <v/>
@@ -6553,14 +6713,14 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J55" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6580,7 +6740,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R55" s="7" t="n"/>
+      <c r="R55" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S55">
         <f>IF(L55="회신 완료","",J55-TODAY())</f>
         <v/>
@@ -6631,14 +6795,14 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J56" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6658,7 +6822,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R56" s="7" t="n"/>
+      <c r="R56" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S56">
         <f>IF(L56="회신 완료","",J56-TODAY())</f>
         <v/>
@@ -6709,14 +6877,14 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J57" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6736,7 +6904,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R57" s="7" t="n"/>
+      <c r="R57" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S57">
         <f>IF(L57="회신 완료","",J57-TODAY())</f>
         <v/>
@@ -6787,14 +6959,14 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J58" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6814,7 +6986,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R58" s="7" t="n"/>
+      <c r="R58" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S58">
         <f>IF(L58="회신 완료","",J58-TODAY())</f>
         <v/>
@@ -6865,14 +7041,14 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J59" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6892,7 +7068,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R59" s="7" t="n"/>
+      <c r="R59" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S59">
         <f>IF(L59="회신 완료","",J59-TODAY())</f>
         <v/>
@@ -6943,14 +7123,14 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J60" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6970,7 +7150,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R60" s="7" t="n"/>
+      <c r="R60" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S60">
         <f>IF(L60="회신 완료","",J60-TODAY())</f>
         <v/>
@@ -7021,14 +7205,14 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J61" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7048,7 +7232,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R61" s="7" t="n"/>
+      <c r="R61" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S61">
         <f>IF(L61="회신 완료","",J61-TODAY())</f>
         <v/>
@@ -7099,14 +7287,14 @@
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J62" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7126,7 +7314,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R62" s="7" t="n"/>
+      <c r="R62" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S62">
         <f>IF(L62="회신 완료","",J62-TODAY())</f>
         <v/>
@@ -7177,14 +7369,14 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J63" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7204,7 +7396,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R63" s="7" t="n"/>
+      <c r="R63" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S63">
         <f>IF(L63="회신 완료","",J63-TODAY())</f>
         <v/>
@@ -7255,14 +7451,14 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J64" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7282,7 +7478,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R64" s="7" t="n"/>
+      <c r="R64" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S64">
         <f>IF(L64="회신 완료","",J64-TODAY())</f>
         <v/>
@@ -7333,14 +7533,14 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J65" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7360,7 +7560,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R65" s="7" t="n"/>
+      <c r="R65" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S65">
         <f>IF(L65="회신 완료","",J65-TODAY())</f>
         <v/>
@@ -7411,14 +7615,14 @@
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J66" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7438,7 +7642,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R66" s="7" t="n"/>
+      <c r="R66" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S66">
         <f>IF(L66="회신 완료","",J66-TODAY())</f>
         <v/>
@@ -7489,14 +7697,14 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J67" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K67" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7516,7 +7724,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R67" s="7" t="n"/>
+      <c r="R67" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S67">
         <f>IF(L67="회신 완료","",J67-TODAY())</f>
         <v/>
@@ -7567,14 +7779,14 @@
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J68" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7594,7 +7806,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R68" s="7" t="n"/>
+      <c r="R68" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S68">
         <f>IF(L68="회신 완료","",J68-TODAY())</f>
         <v/>
@@ -7645,14 +7861,14 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J69" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7672,7 +7888,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R69" s="7" t="n"/>
+      <c r="R69" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S69">
         <f>IF(L69="회신 완료","",J69-TODAY())</f>
         <v/>
@@ -7723,14 +7943,14 @@
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J70" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7750,7 +7970,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R70" s="7" t="n"/>
+      <c r="R70" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S70">
         <f>IF(L70="회신 완료","",J70-TODAY())</f>
         <v/>
@@ -7801,14 +8025,14 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J71" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7828,7 +8052,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R71" s="7" t="n"/>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S71">
         <f>IF(L71="회신 완료","",J71-TODAY())</f>
         <v/>
@@ -7879,14 +8107,14 @@
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J72" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7906,7 +8134,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R72" s="7" t="n"/>
+      <c r="R72" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S72">
         <f>IF(L72="회신 완료","",J72-TODAY())</f>
         <v/>
@@ -7957,14 +8189,14 @@
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J73" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7984,7 +8216,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R73" s="7" t="n"/>
+      <c r="R73" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S73">
         <f>IF(L73="회신 완료","",J73-TODAY())</f>
         <v/>
@@ -8035,14 +8271,14 @@
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J74" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8062,7 +8298,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R74" s="7" t="n"/>
+      <c r="R74" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S74">
         <f>IF(L74="회신 완료","",J74-TODAY())</f>
         <v/>
@@ -8113,14 +8353,14 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J75" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8140,7 +8380,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R75" s="7" t="n"/>
+      <c r="R75" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S75">
         <f>IF(L75="회신 완료","",J75-TODAY())</f>
         <v/>
@@ -8191,14 +8435,14 @@
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J76" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8218,7 +8462,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R76" s="7" t="n"/>
+      <c r="R76" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S76">
         <f>IF(L76="회신 완료","",J76-TODAY())</f>
         <v/>
@@ -8269,14 +8517,14 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J77" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K77" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8296,7 +8544,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R77" s="7" t="n"/>
+      <c r="R77" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S77">
         <f>IF(L77="회신 완료","",J77-TODAY())</f>
         <v/>
@@ -8347,14 +8599,14 @@
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J78" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K78" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8374,7 +8626,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R78" s="7" t="n"/>
+      <c r="R78" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S78">
         <f>IF(L78="회신 완료","",J78-TODAY())</f>
         <v/>
@@ -8425,14 +8681,14 @@
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J79" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K79" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8452,7 +8708,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R79" s="7" t="n"/>
+      <c r="R79" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S79">
         <f>IF(L79="회신 완료","",J79-TODAY())</f>
         <v/>
@@ -8503,14 +8763,14 @@
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J80" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K80" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8530,7 +8790,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R80" s="7" t="n"/>
+      <c r="R80" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S80">
         <f>IF(L80="회신 완료","",J80-TODAY())</f>
         <v/>
@@ -8581,14 +8845,14 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J81" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K81" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8608,7 +8872,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R81" s="7" t="n"/>
+      <c r="R81" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S81">
         <f>IF(L81="회신 완료","",J81-TODAY())</f>
         <v/>
@@ -8659,14 +8927,14 @@
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J82" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K82" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8686,7 +8954,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R82" s="7" t="n"/>
+      <c r="R82" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S82">
         <f>IF(L82="회신 완료","",J82-TODAY())</f>
         <v/>
@@ -8737,14 +9009,14 @@
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J83" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K83" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8764,7 +9036,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R83" s="7" t="n"/>
+      <c r="R83" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S83">
         <f>IF(L83="회신 완료","",J83-TODAY())</f>
         <v/>
@@ -8815,14 +9091,14 @@
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J84" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K84" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8842,7 +9118,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R84" s="7" t="n"/>
+      <c r="R84" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S84">
         <f>IF(L84="회신 완료","",J84-TODAY())</f>
         <v/>
@@ -8893,14 +9173,14 @@
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J85" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K85" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8920,7 +9200,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R85" s="7" t="n"/>
+      <c r="R85" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S85">
         <f>IF(L85="회신 완료","",J85-TODAY())</f>
         <v/>
@@ -8971,14 +9255,14 @@
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J86" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K86" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -8998,7 +9282,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R86" s="7" t="n"/>
+      <c r="R86" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S86">
         <f>IF(L86="회신 완료","",J86-TODAY())</f>
         <v/>
@@ -9049,14 +9337,14 @@
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J87" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K87" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9076,7 +9364,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R87" s="7" t="n"/>
+      <c r="R87" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S87">
         <f>IF(L87="회신 완료","",J87-TODAY())</f>
         <v/>
@@ -9127,14 +9419,14 @@
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J88" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K88" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9154,7 +9446,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R88" s="7" t="n"/>
+      <c r="R88" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S88">
         <f>IF(L88="회신 완료","",J88-TODAY())</f>
         <v/>
@@ -9205,14 +9501,14 @@
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J89" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K89" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9232,7 +9528,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R89" s="7" t="n"/>
+      <c r="R89" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S89">
         <f>IF(L89="회신 완료","",J89-TODAY())</f>
         <v/>
@@ -9283,14 +9583,14 @@
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J90" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K90" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9310,7 +9610,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R90" s="7" t="n"/>
+      <c r="R90" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S90">
         <f>IF(L90="회신 완료","",J90-TODAY())</f>
         <v/>
@@ -9361,14 +9665,14 @@
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J91" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K91" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9388,7 +9692,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R91" s="7" t="n"/>
+      <c r="R91" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S91">
         <f>IF(L91="회신 완료","",J91-TODAY())</f>
         <v/>
@@ -9439,14 +9747,14 @@
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J92" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K92" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9466,7 +9774,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R92" s="7" t="n"/>
+      <c r="R92" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S92">
         <f>IF(L92="회신 완료","",J92-TODAY())</f>
         <v/>
@@ -9517,14 +9829,14 @@
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J93" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K93" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9544,7 +9856,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R93" s="7" t="n"/>
+      <c r="R93" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S93">
         <f>IF(L93="회신 완료","",J93-TODAY())</f>
         <v/>
@@ -9595,14 +9911,14 @@
       </c>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J94" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K94" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9622,7 +9938,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R94" s="7" t="n"/>
+      <c r="R94" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S94">
         <f>IF(L94="회신 완료","",J94-TODAY())</f>
         <v/>
@@ -9673,14 +9993,14 @@
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J95" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K95" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9700,7 +10020,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R95" s="7" t="n"/>
+      <c r="R95" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S95">
         <f>IF(L95="회신 완료","",J95-TODAY())</f>
         <v/>
@@ -9751,14 +10075,14 @@
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_이광재.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_이광재_20261027.txt</t>
         </is>
       </c>
       <c r="J96" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K96" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -9778,7 +10102,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R96" s="7" t="n"/>
+      <c r="R96" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S96">
         <f>IF(L96="회신 완료","",J96-TODAY())</f>
         <v/>
@@ -12407,14 +12735,14 @@
       </c>
       <c r="I130" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J130" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K130" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -12434,7 +12762,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R130" s="7" t="n"/>
+      <c r="R130" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S130">
         <f>IF(L130="회신 완료","",J130-TODAY())</f>
         <v/>
@@ -12485,14 +12817,14 @@
       </c>
       <c r="I131" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J131" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K131" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -12512,7 +12844,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R131" s="7" t="n"/>
+      <c r="R131" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S131">
         <f>IF(L131="회신 완료","",J131-TODAY())</f>
         <v/>
@@ -12563,14 +12899,14 @@
       </c>
       <c r="I132" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J132" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K132" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -12590,7 +12926,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R132" s="7" t="n"/>
+      <c r="R132" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S132">
         <f>IF(L132="회신 완료","",J132-TODAY())</f>
         <v/>
@@ -12641,14 +12981,14 @@
       </c>
       <c r="I133" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J133" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K133" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -12668,7 +13008,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R133" s="7" t="n"/>
+      <c r="R133" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S133">
         <f>IF(L133="회신 완료","",J133-TODAY())</f>
         <v/>
@@ -12719,14 +13063,14 @@
       </c>
       <c r="I134" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J134" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K134" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -12746,7 +13090,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R134" s="7" t="n"/>
+      <c r="R134" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S134">
         <f>IF(L134="회신 완료","",J134-TODAY())</f>
         <v/>
@@ -12797,14 +13145,14 @@
       </c>
       <c r="I135" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J135" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K135" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -12824,7 +13172,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R135" s="7" t="n"/>
+      <c r="R135" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S135">
         <f>IF(L135="회신 완료","",J135-TODAY())</f>
         <v/>
@@ -12875,14 +13227,14 @@
       </c>
       <c r="I136" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J136" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K136" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -12902,7 +13254,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R136" s="7" t="n"/>
+      <c r="R136" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S136">
         <f>IF(L136="회신 완료","",J136-TODAY())</f>
         <v/>
@@ -12953,14 +13309,14 @@
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J137" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K137" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -12980,7 +13336,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R137" s="7" t="n"/>
+      <c r="R137" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S137">
         <f>IF(L137="회신 완료","",J137-TODAY())</f>
         <v/>
@@ -13031,14 +13391,14 @@
       </c>
       <c r="I138" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J138" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K138" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -13058,7 +13418,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R138" s="7" t="n"/>
+      <c r="R138" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S138">
         <f>IF(L138="회신 완료","",J138-TODAY())</f>
         <v/>
@@ -13109,14 +13473,14 @@
       </c>
       <c r="I139" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J139" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K139" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -13136,7 +13500,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R139" s="7" t="n"/>
+      <c r="R139" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S139">
         <f>IF(L139="회신 완료","",J139-TODAY())</f>
         <v/>
@@ -13187,14 +13555,14 @@
       </c>
       <c r="I140" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J140" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K140" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -13214,7 +13582,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R140" s="7" t="n"/>
+      <c r="R140" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S140">
         <f>IF(L140="회신 완료","",J140-TODAY())</f>
         <v/>
@@ -13265,14 +13637,14 @@
       </c>
       <c r="I141" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J141" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K141" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -13292,7 +13664,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R141" s="7" t="n"/>
+      <c r="R141" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S141">
         <f>IF(L141="회신 완료","",J141-TODAY())</f>
         <v/>
@@ -13343,14 +13719,14 @@
       </c>
       <c r="I142" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J142" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K142" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -13370,7 +13746,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R142" s="7" t="n"/>
+      <c r="R142" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S142">
         <f>IF(L142="회신 완료","",J142-TODAY())</f>
         <v/>
@@ -13421,14 +13801,14 @@
       </c>
       <c r="I143" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J143" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K143" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -13448,7 +13828,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R143" s="7" t="n"/>
+      <c r="R143" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S143">
         <f>IF(L143="회신 완료","",J143-TODAY())</f>
         <v/>
@@ -13499,14 +13883,14 @@
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J144" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K144" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -13528,7 +13912,7 @@
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규); 담당자 변경 재안내 발송 2026-10-27</t>
         </is>
       </c>
       <c r="S144">
@@ -13581,14 +13965,14 @@
       </c>
       <c r="I145" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J145" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K145" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -13608,7 +13992,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R145" s="7" t="n"/>
+      <c r="R145" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S145">
         <f>IF(L145="회신 완료","",J145-TODAY())</f>
         <v/>
@@ -13659,14 +14047,14 @@
       </c>
       <c r="I146" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J146" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K146" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -13686,7 +14074,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R146" s="7" t="n"/>
+      <c r="R146" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S146">
         <f>IF(L146="회신 완료","",J146-TODAY())</f>
         <v/>
@@ -13737,14 +14129,14 @@
       </c>
       <c r="I147" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J147" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K147" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -13766,7 +14158,7 @@
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규); 담당자 변경 재안내 발송 2026-10-27</t>
         </is>
       </c>
       <c r="S147">
@@ -13819,14 +14211,14 @@
       </c>
       <c r="I148" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J148" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K148" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -13848,7 +14240,7 @@
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규); 담당자 변경 재안내 발송 2026-10-27</t>
         </is>
       </c>
       <c r="S148">
@@ -13901,14 +14293,14 @@
       </c>
       <c r="I149" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J149" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K149" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -13928,7 +14320,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R149" s="7" t="n"/>
+      <c r="R149" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S149">
         <f>IF(L149="회신 완료","",J149-TODAY())</f>
         <v/>
@@ -13979,14 +14375,14 @@
       </c>
       <c r="I150" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J150" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K150" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -14008,7 +14404,7 @@
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규); 담당자 변경 재안내 발송 2026-10-27</t>
         </is>
       </c>
       <c r="S150">
@@ -14061,14 +14457,14 @@
       </c>
       <c r="I151" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J151" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K151" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -14090,7 +14486,7 @@
       </c>
       <c r="R151" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규); 담당자 변경 재안내 발송 2026-10-27</t>
         </is>
       </c>
       <c r="S151">
@@ -14143,14 +14539,14 @@
       </c>
       <c r="I152" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J152" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K152" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -14172,7 +14568,7 @@
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규); 담당자 변경 재안내 발송 2026-10-27</t>
         </is>
       </c>
       <c r="S152">
@@ -14225,14 +14621,14 @@
       </c>
       <c r="I153" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J153" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K153" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -14252,7 +14648,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R153" s="7" t="n"/>
+      <c r="R153" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S153">
         <f>IF(L153="회신 완료","",J153-TODAY())</f>
         <v/>
@@ -14303,14 +14703,14 @@
       </c>
       <c r="I154" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J154" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K154" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -14330,7 +14730,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R154" s="7" t="n"/>
+      <c r="R154" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S154">
         <f>IF(L154="회신 완료","",J154-TODAY())</f>
         <v/>
@@ -14381,14 +14785,14 @@
       </c>
       <c r="I155" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J155" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K155" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -14408,7 +14812,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R155" s="7" t="n"/>
+      <c r="R155" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S155">
         <f>IF(L155="회신 완료","",J155-TODAY())</f>
         <v/>
@@ -14459,14 +14867,14 @@
       </c>
       <c r="I156" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J156" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K156" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -14486,7 +14894,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R156" s="7" t="n"/>
+      <c r="R156" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S156">
         <f>IF(L156="회신 완료","",J156-TODAY())</f>
         <v/>
@@ -14537,14 +14949,14 @@
       </c>
       <c r="I157" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J157" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K157" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -14564,7 +14976,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R157" s="7" t="n"/>
+      <c r="R157" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S157">
         <f>IF(L157="회신 완료","",J157-TODAY())</f>
         <v/>
@@ -14615,14 +15031,14 @@
       </c>
       <c r="I158" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J158" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K158" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -14642,7 +15058,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R158" s="7" t="n"/>
+      <c r="R158" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S158">
         <f>IF(L158="회신 완료","",J158-TODAY())</f>
         <v/>
@@ -14693,14 +15113,14 @@
       </c>
       <c r="I159" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J159" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K159" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -14720,7 +15140,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R159" s="7" t="n"/>
+      <c r="R159" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S159">
         <f>IF(L159="회신 완료","",J159-TODAY())</f>
         <v/>
@@ -14771,14 +15195,14 @@
       </c>
       <c r="I160" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J160" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K160" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -14798,7 +15222,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R160" s="7" t="n"/>
+      <c r="R160" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S160">
         <f>IF(L160="회신 완료","",J160-TODAY())</f>
         <v/>
@@ -14849,14 +15277,14 @@
       </c>
       <c r="I161" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J161" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K161" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -14876,7 +15304,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R161" s="7" t="n"/>
+      <c r="R161" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S161">
         <f>IF(L161="회신 완료","",J161-TODAY())</f>
         <v/>
@@ -14927,14 +15359,14 @@
       </c>
       <c r="I162" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J162" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K162" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -14954,7 +15386,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R162" s="7" t="n"/>
+      <c r="R162" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S162">
         <f>IF(L162="회신 완료","",J162-TODAY())</f>
         <v/>
@@ -15005,14 +15441,14 @@
       </c>
       <c r="I163" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J163" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K163" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -15032,7 +15468,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R163" s="7" t="n"/>
+      <c r="R163" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S163">
         <f>IF(L163="회신 완료","",J163-TODAY())</f>
         <v/>
@@ -15083,14 +15523,14 @@
       </c>
       <c r="I164" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J164" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K164" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -15110,7 +15550,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R164" s="7" t="n"/>
+      <c r="R164" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S164">
         <f>IF(L164="회신 완료","",J164-TODAY())</f>
         <v/>
@@ -15161,14 +15605,14 @@
       </c>
       <c r="I165" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J165" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K165" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -15188,7 +15632,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R165" s="7" t="n"/>
+      <c r="R165" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S165">
         <f>IF(L165="회신 완료","",J165-TODAY())</f>
         <v/>
@@ -15239,14 +15687,14 @@
       </c>
       <c r="I166" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J166" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K166" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -15266,7 +15714,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R166" s="7" t="n"/>
+      <c r="R166" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S166">
         <f>IF(L166="회신 완료","",J166-TODAY())</f>
         <v/>
@@ -15317,14 +15769,14 @@
       </c>
       <c r="I167" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J167" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K167" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -15344,7 +15796,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R167" s="7" t="n"/>
+      <c r="R167" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S167">
         <f>IF(L167="회신 완료","",J167-TODAY())</f>
         <v/>
@@ -15641,14 +16097,14 @@
       </c>
       <c r="I171" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J171" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K171" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -15668,7 +16124,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R171" s="7" t="n"/>
+      <c r="R171" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S171">
         <f>IF(L171="회신 완료","",J171-TODAY())</f>
         <v/>
@@ -15719,14 +16179,14 @@
       </c>
       <c r="I172" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J172" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K172" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -15746,7 +16206,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R172" s="7" t="n"/>
+      <c r="R172" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S172">
         <f>IF(L172="회신 완료","",J172-TODAY())</f>
         <v/>
@@ -15797,14 +16261,14 @@
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J173" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K173" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -15824,7 +16288,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R173" s="7" t="n"/>
+      <c r="R173" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S173">
         <f>IF(L173="회신 완료","",J173-TODAY())</f>
         <v/>
@@ -15875,14 +16343,14 @@
       </c>
       <c r="I174" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J174" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K174" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -15902,7 +16370,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R174" s="7" t="n"/>
+      <c r="R174" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S174">
         <f>IF(L174="회신 완료","",J174-TODAY())</f>
         <v/>
@@ -15953,14 +16425,14 @@
       </c>
       <c r="I175" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J175" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K175" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -15980,7 +16452,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R175" s="7" t="n"/>
+      <c r="R175" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S175">
         <f>IF(L175="회신 완료","",J175-TODAY())</f>
         <v/>
@@ -16031,14 +16507,14 @@
       </c>
       <c r="I176" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J176" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K176" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -16058,7 +16534,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R176" s="7" t="n"/>
+      <c r="R176" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S176">
         <f>IF(L176="회신 완료","",J176-TODAY())</f>
         <v/>
@@ -16109,14 +16589,14 @@
       </c>
       <c r="I177" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J177" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K177" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -16136,7 +16616,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R177" s="7" t="n"/>
+      <c r="R177" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S177">
         <f>IF(L177="회신 완료","",J177-TODAY())</f>
         <v/>
@@ -16187,14 +16671,14 @@
       </c>
       <c r="I178" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J178" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K178" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -16214,7 +16698,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R178" s="7" t="n"/>
+      <c r="R178" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S178">
         <f>IF(L178="회신 완료","",J178-TODAY())</f>
         <v/>
@@ -16265,14 +16753,14 @@
       </c>
       <c r="I179" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J179" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K179" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -16292,7 +16780,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R179" s="7" t="n"/>
+      <c r="R179" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S179">
         <f>IF(L179="회신 완료","",J179-TODAY())</f>
         <v/>
@@ -16343,14 +16835,14 @@
       </c>
       <c r="I180" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J180" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K180" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -16370,7 +16862,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R180" s="7" t="n"/>
+      <c r="R180" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S180">
         <f>IF(L180="회신 완료","",J180-TODAY())</f>
         <v/>
@@ -16421,14 +16917,14 @@
       </c>
       <c r="I181" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J181" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K181" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -16448,7 +16944,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R181" s="7" t="n"/>
+      <c r="R181" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S181">
         <f>IF(L181="회신 완료","",J181-TODAY())</f>
         <v/>
@@ -16499,14 +16999,14 @@
       </c>
       <c r="I182" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J182" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K182" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -16526,7 +17026,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R182" s="7" t="n"/>
+      <c r="R182" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S182">
         <f>IF(L182="회신 완료","",J182-TODAY())</f>
         <v/>
@@ -16577,14 +17081,14 @@
       </c>
       <c r="I183" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J183" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K183" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
@@ -16604,7 +17108,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R183" s="7" t="n"/>
+      <c r="R183" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S183">
         <f>IF(L183="회신 완료","",J183-TODAY())</f>
         <v/>
@@ -16655,14 +17163,14 @@
       </c>
       <c r="I184" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J184" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K184" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -16682,7 +17190,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R184" s="7" t="n"/>
+      <c r="R184" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S184">
         <f>IF(L184="회신 완료","",J184-TODAY())</f>
         <v/>
@@ -16733,14 +17245,14 @@
       </c>
       <c r="I185" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J185" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K185" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -16760,7 +17272,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R185" s="7" t="n"/>
+      <c r="R185" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S185">
         <f>IF(L185="회신 완료","",J185-TODAY())</f>
         <v/>
@@ -16811,14 +17327,14 @@
       </c>
       <c r="I186" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J186" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K186" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -16838,7 +17354,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R186" s="7" t="n"/>
+      <c r="R186" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S186">
         <f>IF(L186="회신 완료","",J186-TODAY())</f>
         <v/>
@@ -16889,14 +17409,14 @@
       </c>
       <c r="I187" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J187" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K187" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
@@ -16916,7 +17436,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R187" s="7" t="n"/>
+      <c r="R187" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S187">
         <f>IF(L187="회신 완료","",J187-TODAY())</f>
         <v/>
@@ -16967,14 +17491,14 @@
       </c>
       <c r="I188" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J188" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K188" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
@@ -16994,7 +17518,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R188" s="7" t="n"/>
+      <c r="R188" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S188">
         <f>IF(L188="회신 완료","",J188-TODAY())</f>
         <v/>
@@ -17045,14 +17573,14 @@
       </c>
       <c r="I189" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J189" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K189" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -17072,7 +17600,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R189" s="7" t="n"/>
+      <c r="R189" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S189">
         <f>IF(L189="회신 완료","",J189-TODAY())</f>
         <v/>
@@ -17123,14 +17655,14 @@
       </c>
       <c r="I190" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J190" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K190" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -17150,7 +17682,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R190" s="7" t="n"/>
+      <c r="R190" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S190">
         <f>IF(L190="회신 완료","",J190-TODAY())</f>
         <v/>
@@ -17201,14 +17737,14 @@
       </c>
       <c r="I191" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J191" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K191" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -17228,7 +17764,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R191" s="7" t="n"/>
+      <c r="R191" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S191">
         <f>IF(L191="회신 완료","",J191-TODAY())</f>
         <v/>
@@ -17279,14 +17819,14 @@
       </c>
       <c r="I192" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J192" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K192" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -17306,7 +17846,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R192" s="7" t="n"/>
+      <c r="R192" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S192">
         <f>IF(L192="회신 완료","",J192-TODAY())</f>
         <v/>
@@ -17357,14 +17901,14 @@
       </c>
       <c r="I193" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J193" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K193" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
@@ -17384,7 +17928,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R193" s="7" t="n"/>
+      <c r="R193" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S193">
         <f>IF(L193="회신 완료","",J193-TODAY())</f>
         <v/>
@@ -17435,14 +17983,14 @@
       </c>
       <c r="I194" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J194" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K194" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -17462,7 +18010,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R194" s="7" t="n"/>
+      <c r="R194" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S194">
         <f>IF(L194="회신 완료","",J194-TODAY())</f>
         <v/>
@@ -17513,14 +18065,14 @@
       </c>
       <c r="I195" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J195" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K195" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
@@ -17540,7 +18092,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R195" s="7" t="n"/>
+      <c r="R195" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S195">
         <f>IF(L195="회신 완료","",J195-TODAY())</f>
         <v/>
@@ -17591,14 +18147,14 @@
       </c>
       <c r="I196" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J196" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K196" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -17618,7 +18174,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R196" s="7" t="n"/>
+      <c r="R196" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S196">
         <f>IF(L196="회신 완료","",J196-TODAY())</f>
         <v/>
@@ -17669,14 +18229,14 @@
       </c>
       <c r="I197" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J197" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K197" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
@@ -17696,7 +18256,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R197" s="7" t="n"/>
+      <c r="R197" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S197">
         <f>IF(L197="회신 완료","",J197-TODAY())</f>
         <v/>
@@ -17747,14 +18311,14 @@
       </c>
       <c r="I198" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J198" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K198" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -17774,7 +18338,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R198" s="7" t="n"/>
+      <c r="R198" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S198">
         <f>IF(L198="회신 완료","",J198-TODAY())</f>
         <v/>
@@ -17825,14 +18393,14 @@
       </c>
       <c r="I199" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J199" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K199" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -17852,7 +18420,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R199" s="7" t="n"/>
+      <c r="R199" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S199">
         <f>IF(L199="회신 완료","",J199-TODAY())</f>
         <v/>
@@ -17903,14 +18475,14 @@
       </c>
       <c r="I200" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J200" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K200" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
@@ -17930,7 +18502,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R200" s="7" t="n"/>
+      <c r="R200" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S200">
         <f>IF(L200="회신 완료","",J200-TODAY())</f>
         <v/>
@@ -17981,14 +18557,14 @@
       </c>
       <c r="I201" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J201" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K201" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
@@ -18008,7 +18584,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R201" s="7" t="n"/>
+      <c r="R201" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S201">
         <f>IF(L201="회신 완료","",J201-TODAY())</f>
         <v/>
@@ -18059,14 +18639,14 @@
       </c>
       <c r="I202" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J202" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K202" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L202" s="7" t="inlineStr">
         <is>
@@ -18086,7 +18666,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R202" s="7" t="n"/>
+      <c r="R202" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S202">
         <f>IF(L202="회신 완료","",J202-TODAY())</f>
         <v/>
@@ -18137,14 +18721,14 @@
       </c>
       <c r="I203" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J203" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K203" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
@@ -18164,7 +18748,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R203" s="7" t="n"/>
+      <c r="R203" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S203">
         <f>IF(L203="회신 완료","",J203-TODAY())</f>
         <v/>
@@ -18215,14 +18803,14 @@
       </c>
       <c r="I204" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J204" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K204" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
@@ -18242,7 +18830,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R204" s="7" t="n"/>
+      <c r="R204" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S204">
         <f>IF(L204="회신 완료","",J204-TODAY())</f>
         <v/>
@@ -18293,14 +18885,14 @@
       </c>
       <c r="I205" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_지성규.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_지성규_20261027.txt</t>
         </is>
       </c>
       <c r="J205" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K205" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
@@ -18320,7 +18912,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R205" s="7" t="n"/>
+      <c r="R205" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S205">
         <f>IF(L205="회신 완료","",J205-TODAY())</f>
         <v/>
@@ -18605,14 +19201,14 @@
       </c>
       <c r="I209" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J209" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K209" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
@@ -18632,7 +19228,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R209" s="7" t="n"/>
+      <c r="R209" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S209">
         <f>IF(L209="회신 완료","",J209-TODAY())</f>
         <v/>
@@ -18683,14 +19283,14 @@
       </c>
       <c r="I210" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J210" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K210" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L210" s="7" t="inlineStr">
         <is>
@@ -18710,7 +19310,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R210" s="7" t="n"/>
+      <c r="R210" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S210">
         <f>IF(L210="회신 완료","",J210-TODAY())</f>
         <v/>
@@ -18761,14 +19365,14 @@
       </c>
       <c r="I211" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J211" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K211" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
@@ -18788,7 +19392,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R211" s="7" t="n"/>
+      <c r="R211" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S211">
         <f>IF(L211="회신 완료","",J211-TODAY())</f>
         <v/>
@@ -18839,14 +19447,14 @@
       </c>
       <c r="I212" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J212" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K212" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L212" s="7" t="inlineStr">
         <is>
@@ -18866,7 +19474,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R212" s="7" t="n"/>
+      <c r="R212" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S212">
         <f>IF(L212="회신 완료","",J212-TODAY())</f>
         <v/>
@@ -18917,14 +19529,14 @@
       </c>
       <c r="I213" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J213" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K213" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
@@ -18944,7 +19556,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R213" s="7" t="n"/>
+      <c r="R213" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S213">
         <f>IF(L213="회신 완료","",J213-TODAY())</f>
         <v/>
@@ -18995,14 +19611,14 @@
       </c>
       <c r="I214" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J214" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K214" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L214" s="7" t="inlineStr">
         <is>
@@ -19022,7 +19638,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R214" s="7" t="n"/>
+      <c r="R214" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S214">
         <f>IF(L214="회신 완료","",J214-TODAY())</f>
         <v/>
@@ -19073,14 +19693,14 @@
       </c>
       <c r="I215" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J215" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K215" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
@@ -19100,7 +19720,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R215" s="7" t="n"/>
+      <c r="R215" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S215">
         <f>IF(L215="회신 완료","",J215-TODAY())</f>
         <v/>
@@ -19229,14 +19853,14 @@
       </c>
       <c r="I217" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J217" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K217" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
@@ -19256,7 +19880,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R217" s="7" t="n"/>
+      <c r="R217" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S217">
         <f>IF(L217="회신 완료","",J217-TODAY())</f>
         <v/>
@@ -19307,14 +19935,14 @@
       </c>
       <c r="I218" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J218" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K218" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L218" s="7" t="inlineStr">
         <is>
@@ -19334,7 +19962,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R218" s="7" t="n"/>
+      <c r="R218" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S218">
         <f>IF(L218="회신 완료","",J218-TODAY())</f>
         <v/>
@@ -19385,14 +20017,14 @@
       </c>
       <c r="I219" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J219" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K219" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
@@ -19412,7 +20044,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R219" s="7" t="n"/>
+      <c r="R219" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S219">
         <f>IF(L219="회신 완료","",J219-TODAY())</f>
         <v/>
@@ -19463,14 +20099,14 @@
       </c>
       <c r="I220" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J220" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K220" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L220" s="7" t="inlineStr">
         <is>
@@ -19490,7 +20126,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R220" s="7" t="n"/>
+      <c r="R220" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S220">
         <f>IF(L220="회신 완료","",J220-TODAY())</f>
         <v/>
@@ -19541,14 +20181,14 @@
       </c>
       <c r="I221" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J221" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K221" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
@@ -19568,7 +20208,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R221" s="7" t="n"/>
+      <c r="R221" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S221">
         <f>IF(L221="회신 완료","",J221-TODAY())</f>
         <v/>
@@ -19619,14 +20263,14 @@
       </c>
       <c r="I222" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J222" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K222" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L222" s="7" t="inlineStr">
         <is>
@@ -19646,7 +20290,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R222" s="7" t="n"/>
+      <c r="R222" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S222">
         <f>IF(L222="회신 완료","",J222-TODAY())</f>
         <v/>
@@ -19697,14 +20345,14 @@
       </c>
       <c r="I223" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J223" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K223" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
@@ -19724,7 +20372,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R223" s="7" t="n"/>
+      <c r="R223" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S223">
         <f>IF(L223="회신 완료","",J223-TODAY())</f>
         <v/>
@@ -19775,14 +20427,14 @@
       </c>
       <c r="I224" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J224" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K224" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L224" s="7" t="inlineStr">
         <is>
@@ -19802,7 +20454,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R224" s="7" t="n"/>
+      <c r="R224" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S224">
         <f>IF(L224="회신 완료","",J224-TODAY())</f>
         <v/>
@@ -19853,14 +20509,14 @@
       </c>
       <c r="I225" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J225" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K225" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
@@ -19880,7 +20536,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R225" s="7" t="n"/>
+      <c r="R225" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S225">
         <f>IF(L225="회신 완료","",J225-TODAY())</f>
         <v/>
@@ -19931,14 +20591,14 @@
       </c>
       <c r="I226" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J226" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K226" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L226" s="7" t="inlineStr">
         <is>
@@ -19958,7 +20618,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R226" s="7" t="n"/>
+      <c r="R226" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S226">
         <f>IF(L226="회신 완료","",J226-TODAY())</f>
         <v/>
@@ -20009,14 +20673,14 @@
       </c>
       <c r="I227" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_한상돈.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_한상돈_20261027.txt</t>
         </is>
       </c>
       <c r="J227" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K227" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
@@ -20038,7 +20702,7 @@
       </c>
       <c r="R227" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 황지환)</t>
+          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 황지환); 담당자 변경 재안내 발송 2026-10-27</t>
         </is>
       </c>
       <c r="S227">
@@ -20091,14 +20755,14 @@
       </c>
       <c r="I228" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J228" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K228" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L228" s="7" t="inlineStr">
         <is>
@@ -20118,7 +20782,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R228" s="7" t="n"/>
+      <c r="R228" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S228">
         <f>IF(L228="회신 완료","",J228-TODAY())</f>
         <v/>
@@ -20169,14 +20837,14 @@
       </c>
       <c r="I229" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J229" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K229" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
@@ -20196,7 +20864,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R229" s="7" t="n"/>
+      <c r="R229" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S229">
         <f>IF(L229="회신 완료","",J229-TODAY())</f>
         <v/>
@@ -20247,14 +20919,14 @@
       </c>
       <c r="I230" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J230" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K230" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L230" s="7" t="inlineStr">
         <is>
@@ -20274,7 +20946,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R230" s="7" t="n"/>
+      <c r="R230" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S230">
         <f>IF(L230="회신 완료","",J230-TODAY())</f>
         <v/>
@@ -20325,14 +21001,14 @@
       </c>
       <c r="I231" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J231" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K231" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
@@ -20352,7 +21028,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R231" s="7" t="n"/>
+      <c r="R231" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S231">
         <f>IF(L231="회신 완료","",J231-TODAY())</f>
         <v/>
@@ -20403,14 +21083,14 @@
       </c>
       <c r="I232" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J232" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K232" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L232" s="7" t="inlineStr">
         <is>
@@ -20430,7 +21110,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R232" s="7" t="n"/>
+      <c r="R232" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S232">
         <f>IF(L232="회신 완료","",J232-TODAY())</f>
         <v/>
@@ -20481,14 +21165,14 @@
       </c>
       <c r="I233" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J233" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K233" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
@@ -20508,7 +21192,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R233" s="7" t="n"/>
+      <c r="R233" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S233">
         <f>IF(L233="회신 완료","",J233-TODAY())</f>
         <v/>
@@ -20559,14 +21247,14 @@
       </c>
       <c r="I234" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J234" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K234" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L234" s="7" t="inlineStr">
         <is>
@@ -20586,7 +21274,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R234" s="7" t="n"/>
+      <c r="R234" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S234">
         <f>IF(L234="회신 완료","",J234-TODAY())</f>
         <v/>
@@ -20637,14 +21329,14 @@
       </c>
       <c r="I235" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J235" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K235" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
@@ -20664,7 +21356,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R235" s="7" t="n"/>
+      <c r="R235" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S235">
         <f>IF(L235="회신 완료","",J235-TODAY())</f>
         <v/>
@@ -20715,14 +21411,14 @@
       </c>
       <c r="I236" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J236" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K236" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L236" s="7" t="inlineStr">
         <is>
@@ -20742,7 +21438,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R236" s="7" t="n"/>
+      <c r="R236" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S236">
         <f>IF(L236="회신 완료","",J236-TODAY())</f>
         <v/>
@@ -20793,14 +21493,14 @@
       </c>
       <c r="I237" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J237" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K237" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
@@ -20820,7 +21520,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R237" s="7" t="n"/>
+      <c r="R237" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S237">
         <f>IF(L237="회신 완료","",J237-TODAY())</f>
         <v/>
@@ -20871,14 +21575,14 @@
       </c>
       <c r="I238" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J238" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K238" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L238" s="7" t="inlineStr">
         <is>
@@ -20898,7 +21602,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R238" s="7" t="n"/>
+      <c r="R238" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S238">
         <f>IF(L238="회신 완료","",J238-TODAY())</f>
         <v/>
@@ -20949,14 +21657,14 @@
       </c>
       <c r="I239" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J239" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K239" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
@@ -20976,7 +21684,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R239" s="7" t="n"/>
+      <c r="R239" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S239">
         <f>IF(L239="회신 완료","",J239-TODAY())</f>
         <v/>
@@ -21027,14 +21739,14 @@
       </c>
       <c r="I240" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J240" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K240" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L240" s="7" t="inlineStr">
         <is>
@@ -21054,7 +21766,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R240" s="7" t="n"/>
+      <c r="R240" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S240">
         <f>IF(L240="회신 완료","",J240-TODAY())</f>
         <v/>
@@ -21105,14 +21821,14 @@
       </c>
       <c r="I241" s="7" t="inlineStr">
         <is>
-          <t>발송용_최종_20261008/메시지_황지환.txt</t>
+          <t>발송용_담당자변경_20261027/메시지_황지환_20261027.txt</t>
         </is>
       </c>
       <c r="J241" s="8" t="n">
         <v>46331</v>
       </c>
       <c r="K241" s="8" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
@@ -21132,7 +21848,11 @@
           <t>미완료</t>
         </is>
       </c>
-      <c r="R241" s="7" t="n"/>
+      <c r="R241" s="7" t="inlineStr">
+        <is>
+          <t>담당자 변경 재안내 발송 2026-10-27</t>
+        </is>
+      </c>
       <c r="S241">
         <f>IF(L241="회신 완료","",J241-TODAY())</f>
         <v/>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -551,7 +551,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SQ 요청 회신 현황 — 담당자별 (회신 기한 2026-11-05 · 담당자 정정본3 기준 2026-10-27)</t>
+          <t>SQ 요청 회신 현황 — 담당자별 (회신 기한 2026-11-05 · 한온 SQ 심사 2026-12-10 · 담당자 정정본3 기준 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -21901,7 +21901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -22160,6 +22160,41 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>SQ 준비 일정 (한온 SQ 심사 2026-12-10 기준, 제안 — 3개심사_통합달력_20261027_v2.xlsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>10/30 M1 기준 확정 · 11/05 담당자 회신 기한(사용자 지정) · 11/10 M2 문서 정합성·매핑표 갱신 · 11/13 M3 현장 증빙·현물 18건 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>11/25 M4 MSA·SPC·LOT 모의추적 · 11/27 양식 본문 작성·재개정 완료 목표 및 M5 자체점검 · 12/01 M6 미흡 종결 · 12/03 M7 모의심사</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>12/07 M8 최종검토 · 12/08 M9 준비완료 판정 · 12/09 예비일 · 12/10 한온 SQ 심사</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>11/16~11/20은 ISO 14001 갱신심사(NQA) 주간이라 SQ 마일스톤을 두지 않았습니다. 확정된 날짜는 회신 11/05·SQ 심사 12/10(사용자 지정), 나머지는 담당자 협의 후 확정합니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_회신현황_체크리스트_20261008.xlsx
@@ -551,14 +551,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SQ 요청 회신 현황 — 담당자별 (회신 기한 2026-11-05 · 한온 SQ 심사 2026-12-10 · 담당자 정정본3 기준 2026-10-27)</t>
+          <t>SQ 요청 회신 현황 — 담당자별 (회신 기한 2026-11-05 · 한온 SQ 심사 2026-12-10 · 담당자 정정본4 기준 2026-10-28)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>'상세' 시트의 발송일·회신 상태를 입력하면 자동 집계됩니다. 지연 = 발송했으나 회신 완료가 아니고 기한이 지난 건(오늘 기준). 담당자는 정정본3 기준이며 인쇄물 전달 당시와 다른 건은 상세 R열에 표시했습니다. SQ NO 목록은 2026-10-27 기준(보완 필요는 상세 참고).</t>
+          <t>'상세' 시트의 발송일·회신 상태를 입력하면 자동 집계됩니다. 지연 = 발송했으나 회신 완료가 아니고 기한이 지난 건(오늘 기준). 담당자는 정정본4 기준(미지정 4건은 2026-10-28 지성규·이광재로 확정)이며 인쇄물 전달 당시와 다른 건은 상세 R열에 표시했습니다. SQ NO 목록은 2026-10-27 기준(보완 필요는 상세 참고).</t>
         </is>
       </c>
     </row>
@@ -6142,23 +6142,21 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>(미지정)</t>
+          <t>이광재</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>(담당자 미지정)</t>
+          <t>발송용_담당자정정_20261028/메시지_이광재_20261028_정정.txt</t>
         </is>
       </c>
       <c r="J48" s="8" t="n">
         <v>46331</v>
       </c>
-      <c r="K48" s="8" t="n">
-        <v>46303</v>
-      </c>
+      <c r="K48" s="8" t="n"/>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>발송(회신 대기)</t>
+          <t>미발송</t>
         </is>
       </c>
       <c r="M48" s="8" t="n"/>
@@ -6176,7 +6174,7 @@
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 박철호)</t>
+          <t>담당자 정정본4 기준 이광재 확정(2026-10-28, 인쇄물 전달 당시: 박철호). 정정 메시지 발송 후 발송일·상태 갱신</t>
         </is>
       </c>
       <c r="S48">
@@ -15846,12 +15844,12 @@
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>(미지정)</t>
+          <t>지성규</t>
         </is>
       </c>
       <c r="I168" s="7" t="inlineStr">
         <is>
-          <t>(담당자 미지정)</t>
+          <t>발송용_담당자정정_20261028/메시지_지성규_20261028_정정.txt</t>
         </is>
       </c>
       <c r="J168" s="8" t="n">
@@ -15880,7 +15878,7 @@
       </c>
       <c r="R168" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본4 기준 지성규 확정(2026-10-28, 인쇄물 전달 당시 담당과 같음). 10-27 재안내의 "빠진 건" 문구는 정정 메시지로 취소</t>
         </is>
       </c>
       <c r="S168">
@@ -15928,12 +15926,12 @@
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>(미지정)</t>
+          <t>지성규</t>
         </is>
       </c>
       <c r="I169" s="7" t="inlineStr">
         <is>
-          <t>(담당자 미지정)</t>
+          <t>발송용_담당자정정_20261028/메시지_지성규_20261028_정정.txt</t>
         </is>
       </c>
       <c r="J169" s="8" t="n">
@@ -15962,7 +15960,7 @@
       </c>
       <c r="R169" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본4 기준 지성규 확정(2026-10-28, 인쇄물 전달 당시 담당과 같음). 10-27 재안내의 "빠진 건" 문구는 정정 메시지로 취소</t>
         </is>
       </c>
       <c r="S169">
@@ -16010,12 +16008,12 @@
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>(미지정)</t>
+          <t>지성규</t>
         </is>
       </c>
       <c r="I170" s="7" t="inlineStr">
         <is>
-          <t>(담당자 미지정)</t>
+          <t>발송용_담당자정정_20261028/메시지_지성규_20261028_정정.txt</t>
         </is>
       </c>
       <c r="J170" s="8" t="n">
@@ -16044,7 +16042,7 @@
       </c>
       <c r="R170" s="7" t="inlineStr">
         <is>
-          <t>담당자 정정본3 기준 변경(인쇄물 전달 당시: 지성규)</t>
+          <t>담당자 정정본4 기준 지성규 확정(2026-10-28, 인쇄물 전달 당시 담당과 같음). 10-27 재안내의 "빠진 건" 문구는 정정 메시지로 취소</t>
         </is>
       </c>
       <c r="S170">
